--- a/半导体全产业链标的.xlsx
+++ b/半导体全产业链标的.xlsx
@@ -283,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -402,12 +402,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3883,22 +3877,22 @@
       </c>
       <c r="E58" s="17" t="inlineStr">
         <is>
-          <t>洛阳股份</t>
+          <t>洛阳钼业 China Moly</t>
         </is>
       </c>
       <c r="F58" s="18" t="inlineStr">
         <is>
-          <t>000537.SZ</t>
+          <t>603993.SH</t>
         </is>
       </c>
       <c r="G58" s="19" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H58" s="19" t="inlineStr">
         <is>
-          <t>钼铜靶材</t>
+          <t>钼/铜靶材/有色金属</t>
         </is>
       </c>
       <c r="I58" s="20" t="inlineStr">
@@ -8459,22 +8453,22 @@
       </c>
       <c r="D142" s="36" t="inlineStr">
         <is>
-          <t>GPU架构芯片（非上市）</t>
-        </is>
-      </c>
-      <c r="E142" s="42" t="inlineStr">
+          <t>GPU架构芯片，2024年登陆科创板</t>
+        </is>
+      </c>
+      <c r="E142" s="37" t="inlineStr">
         <is>
           <t>沐曦股份</t>
         </is>
       </c>
-      <c r="F142" s="43" t="inlineStr">
-        <is>
-          <t>非上市</t>
+      <c r="F142" s="38" t="inlineStr">
+        <is>
+          <t>688802.SH</t>
         </is>
       </c>
       <c r="G142" s="39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H142" s="39" t="inlineStr">
@@ -8512,22 +8506,22 @@
       </c>
       <c r="D143" s="36" t="inlineStr">
         <is>
-          <t>GPU芯片（非上市）</t>
-        </is>
-      </c>
-      <c r="E143" s="42" t="inlineStr">
+          <t>GPU芯片，2024年登陆科创板</t>
+        </is>
+      </c>
+      <c r="E143" s="37" t="inlineStr">
         <is>
           <t>摩尔线程</t>
         </is>
       </c>
-      <c r="F143" s="43" t="inlineStr">
-        <is>
-          <t>非上市</t>
+      <c r="F143" s="38" t="inlineStr">
+        <is>
+          <t>688795.SH</t>
         </is>
       </c>
       <c r="G143" s="39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H143" s="39" t="inlineStr">

--- a/半导体全产业链标的.xlsx
+++ b/半导体全产业链标的.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="①半导体全产业链标的" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="②数据中心基础设施" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="③人形机器人·无人机·其他科技" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'①半导体全产业链标的'!$A$3:$V$3</definedName>
@@ -322,7 +323,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -459,6 +460,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -826,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V240"/>
+  <dimension ref="A1:V246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11440,8 +11444,8 @@
       <c r="V174" s="13" t="inlineStr"/>
     </row>
     <row r="175" ht="16" customHeight="1">
-      <c r="A175" s="16" t="n"/>
-      <c r="B175" s="16" t="n"/>
+      <c r="A175" s="15" t="n"/>
+      <c r="B175" s="15" t="n"/>
       <c r="C175" s="17" t="inlineStr">
         <is>
           <t>材料</t>
@@ -11496,55 +11500,46 @@
       <c r="V175" s="13" t="inlineStr"/>
     </row>
     <row r="176" ht="16" customHeight="1">
-      <c r="A176" s="3" t="inlineStr">
-        <is>
-          <t>5. AI算力
-应用层</t>
-        </is>
-      </c>
-      <c r="B176" s="36" t="inlineStr">
-        <is>
-          <t>光模块设备</t>
-        </is>
-      </c>
-      <c r="C176" s="37" t="inlineStr">
-        <is>
-          <t>AI算力</t>
-        </is>
-      </c>
-      <c r="D176" s="38" t="inlineStr">
-        <is>
-          <t>光模块/光芯片封装测试设备，AI数据中心必需</t>
-        </is>
-      </c>
-      <c r="E176" s="39" t="inlineStr">
-        <is>
-          <t>罗博特科</t>
-        </is>
-      </c>
-      <c r="F176" s="40" t="inlineStr">
-        <is>
-          <t>688062.SH</t>
-        </is>
-      </c>
-      <c r="G176" s="41" t="inlineStr">
-        <is>
-          <t>上交所科创板</t>
-        </is>
-      </c>
-      <c r="H176" s="41" t="inlineStr">
-        <is>
-          <t>光模块封装测试设备</t>
-        </is>
-      </c>
-      <c r="I176" s="42" t="inlineStr">
+      <c r="A176" s="15" t="n"/>
+      <c r="B176" s="15" t="n"/>
+      <c r="C176" s="17" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="D176" s="18" t="inlineStr">
+        <is>
+          <t>人工金刚石/军工超硬材料</t>
+        </is>
+      </c>
+      <c r="E176" s="19" t="inlineStr">
+        <is>
+          <t>中兵红箭</t>
+        </is>
+      </c>
+      <c r="F176" s="20" t="inlineStr">
+        <is>
+          <t>000519.SZ</t>
+        </is>
+      </c>
+      <c r="G176" s="21" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="H176" s="21" t="inlineStr">
+        <is>
+          <t>人工金刚石/军工超硬</t>
+        </is>
+      </c>
+      <c r="I176" s="22" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="J176" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J176" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K176" s="13" t="inlineStr"/>
@@ -11561,46 +11556,46 @@
       <c r="V176" s="13" t="inlineStr"/>
     </row>
     <row r="177" ht="16" customHeight="1">
-      <c r="A177" s="15" t="n"/>
-      <c r="B177" s="15" t="n"/>
-      <c r="C177" s="37" t="inlineStr">
-        <is>
-          <t>AI算力</t>
-        </is>
-      </c>
-      <c r="D177" s="38" t="inlineStr">
-        <is>
-          <t>光模块自动化生产设备</t>
-        </is>
-      </c>
-      <c r="E177" s="39" t="inlineStr">
-        <is>
-          <t>科瑞技术</t>
-        </is>
-      </c>
-      <c r="F177" s="40" t="inlineStr">
-        <is>
-          <t>002957.SZ</t>
-        </is>
-      </c>
-      <c r="G177" s="41" t="inlineStr">
+      <c r="A177" s="16" t="n"/>
+      <c r="B177" s="16" t="n"/>
+      <c r="C177" s="17" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="D177" s="18" t="inlineStr">
+        <is>
+          <t>精密轴承/金刚石工具</t>
+        </is>
+      </c>
+      <c r="E177" s="19" t="inlineStr">
+        <is>
+          <t>国机精工</t>
+        </is>
+      </c>
+      <c r="F177" s="20" t="inlineStr">
+        <is>
+          <t>002046.SZ</t>
+        </is>
+      </c>
+      <c r="G177" s="21" t="inlineStr">
         <is>
           <t>深交所</t>
         </is>
       </c>
-      <c r="H177" s="41" t="inlineStr">
-        <is>
-          <t>光模块生产设备</t>
-        </is>
-      </c>
-      <c r="I177" s="42" t="inlineStr">
+      <c r="H177" s="21" t="inlineStr">
+        <is>
+          <t>精密轴承/超硬材料</t>
+        </is>
+      </c>
+      <c r="I177" s="22" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="J177" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J177" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K177" s="13" t="inlineStr"/>
@@ -11617,8 +11612,17 @@
       <c r="V177" s="13" t="inlineStr"/>
     </row>
     <row r="178" ht="16" customHeight="1">
-      <c r="A178" s="15" t="n"/>
-      <c r="B178" s="15" t="n"/>
+      <c r="A178" s="3" t="inlineStr">
+        <is>
+          <t>5. AI算力
+应用层</t>
+        </is>
+      </c>
+      <c r="B178" s="36" t="inlineStr">
+        <is>
+          <t>光模块设备</t>
+        </is>
+      </c>
       <c r="C178" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -11626,27 +11630,27 @@
       </c>
       <c r="D178" s="38" t="inlineStr">
         <is>
-          <t>光模块组装/测试设备</t>
+          <t>光模块/光芯片封装测试设备，AI数据中心必需</t>
         </is>
       </c>
       <c r="E178" s="39" t="inlineStr">
         <is>
-          <t>博杰股份</t>
+          <t>罗博特科</t>
         </is>
       </c>
       <c r="F178" s="40" t="inlineStr">
         <is>
-          <t>300784.SZ</t>
+          <t>688062.SH</t>
         </is>
       </c>
       <c r="G178" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H178" s="41" t="inlineStr">
         <is>
-          <t>光模块组装设备</t>
+          <t>光模块封装测试设备</t>
         </is>
       </c>
       <c r="I178" s="42" t="inlineStr">
@@ -11654,9 +11658,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J178" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J178" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K178" s="13" t="inlineStr"/>
@@ -11674,7 +11678,7 @@
     </row>
     <row r="179" ht="16" customHeight="1">
       <c r="A179" s="15" t="n"/>
-      <c r="B179" s="16" t="n"/>
+      <c r="B179" s="15" t="n"/>
       <c r="C179" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -11682,27 +11686,27 @@
       </c>
       <c r="D179" s="38" t="inlineStr">
         <is>
-          <t>激光/光模块加工设备</t>
+          <t>光模块自动化生产设备</t>
         </is>
       </c>
       <c r="E179" s="39" t="inlineStr">
         <is>
-          <t>德龙激光</t>
+          <t>科瑞技术</t>
         </is>
       </c>
       <c r="F179" s="40" t="inlineStr">
         <is>
-          <t>688170.SH</t>
+          <t>002957.SZ</t>
         </is>
       </c>
       <c r="G179" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H179" s="41" t="inlineStr">
         <is>
-          <t>激光加工/光模块设备</t>
+          <t>光模块生产设备</t>
         </is>
       </c>
       <c r="I179" s="42" t="inlineStr">
@@ -11710,9 +11714,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J179" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J179" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K179" s="13" t="inlineStr"/>
@@ -11730,11 +11734,7 @@
     </row>
     <row r="180" ht="16" customHeight="1">
       <c r="A180" s="15" t="n"/>
-      <c r="B180" s="36" t="inlineStr">
-        <is>
-          <t>CPO 共封装光学</t>
-        </is>
-      </c>
+      <c r="B180" s="15" t="n"/>
       <c r="C180" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -11742,27 +11742,27 @@
       </c>
       <c r="D180" s="38" t="inlineStr">
         <is>
-          <t>数据中心光电共封装，AI算力核心互连技术</t>
+          <t>光模块组装/测试设备</t>
         </is>
       </c>
       <c r="E180" s="39" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>博杰股份</t>
         </is>
       </c>
       <c r="F180" s="40" t="inlineStr">
         <is>
-          <t>300308.SZ</t>
+          <t>300784.SZ</t>
         </is>
       </c>
       <c r="G180" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H180" s="41" t="inlineStr">
         <is>
-          <t>CPO/光模块</t>
+          <t>光模块组装设备</t>
         </is>
       </c>
       <c r="I180" s="42" t="inlineStr">
@@ -11770,9 +11770,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J180" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K180" s="13" t="inlineStr"/>
@@ -11790,7 +11790,7 @@
     </row>
     <row r="181" ht="16" customHeight="1">
       <c r="A181" s="15" t="n"/>
-      <c r="B181" s="15" t="n"/>
+      <c r="B181" s="16" t="n"/>
       <c r="C181" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -11798,27 +11798,27 @@
       </c>
       <c r="D181" s="38" t="inlineStr">
         <is>
-          <t>数据中心光电共封装</t>
+          <t>激光/光模块加工设备</t>
         </is>
       </c>
       <c r="E181" s="39" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>德龙激光</t>
         </is>
       </c>
       <c r="F181" s="40" t="inlineStr">
         <is>
-          <t>300502.SZ</t>
+          <t>688170.SH</t>
         </is>
       </c>
       <c r="G181" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H181" s="41" t="inlineStr">
         <is>
-          <t>CPO/光模块</t>
+          <t>激光加工/光模块设备</t>
         </is>
       </c>
       <c r="I181" s="42" t="inlineStr">
@@ -11826,9 +11826,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J181" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J181" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K181" s="13" t="inlineStr"/>
@@ -11846,7 +11846,11 @@
     </row>
     <row r="182" ht="16" customHeight="1">
       <c r="A182" s="15" t="n"/>
-      <c r="B182" s="15" t="n"/>
+      <c r="B182" s="36" t="inlineStr">
+        <is>
+          <t>CPO 共封装光学</t>
+        </is>
+      </c>
       <c r="C182" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -11854,27 +11858,27 @@
       </c>
       <c r="D182" s="38" t="inlineStr">
         <is>
-          <t>CPO光互连组件</t>
+          <t>数据中心光电共封装，AI算力核心互连技术</t>
         </is>
       </c>
       <c r="E182" s="39" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="F182" s="40" t="inlineStr">
         <is>
-          <t>300394.SZ</t>
+          <t>300308.SZ</t>
         </is>
       </c>
       <c r="G182" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H182" s="41" t="inlineStr">
         <is>
-          <t>CPO光互连组件</t>
+          <t>CPO/光模块</t>
         </is>
       </c>
       <c r="I182" s="42" t="inlineStr">
@@ -11882,9 +11886,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J182" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J182" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K182" s="13" t="inlineStr"/>
@@ -11902,7 +11906,7 @@
     </row>
     <row r="183" ht="16" customHeight="1">
       <c r="A183" s="15" t="n"/>
-      <c r="B183" s="16" t="n"/>
+      <c r="B183" s="15" t="n"/>
       <c r="C183" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -11910,27 +11914,27 @@
       </c>
       <c r="D183" s="38" t="inlineStr">
         <is>
-          <t>激光/光通信器件</t>
+          <t>数据中心光电共封装</t>
         </is>
       </c>
       <c r="E183" s="39" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="F183" s="40" t="inlineStr">
         <is>
-          <t>000988.SZ</t>
+          <t>300502.SZ</t>
         </is>
       </c>
       <c r="G183" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H183" s="41" t="inlineStr">
         <is>
-          <t>激光/光通信器件</t>
+          <t>CPO/光模块</t>
         </is>
       </c>
       <c r="I183" s="42" t="inlineStr">
@@ -11938,9 +11942,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J183" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J183" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K183" s="13" t="inlineStr"/>
@@ -11958,11 +11962,7 @@
     </row>
     <row r="184" ht="16" customHeight="1">
       <c r="A184" s="15" t="n"/>
-      <c r="B184" s="36" t="inlineStr">
-        <is>
-          <t>OCS 光交换</t>
-        </is>
-      </c>
+      <c r="B184" s="15" t="n"/>
       <c r="C184" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -11970,27 +11970,27 @@
       </c>
       <c r="D184" s="38" t="inlineStr">
         <is>
-          <t>光学交换技术，替代电交换降低数据中心能耗</t>
+          <t>CPO光互连组件</t>
         </is>
       </c>
       <c r="E184" s="39" t="inlineStr">
         <is>
-          <t>腾景科技</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="F184" s="40" t="inlineStr">
         <is>
-          <t>688195.SH</t>
+          <t>300394.SZ</t>
         </is>
       </c>
       <c r="G184" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H184" s="41" t="inlineStr">
         <is>
-          <t>光开关/OCS器件</t>
+          <t>CPO光互连组件</t>
         </is>
       </c>
       <c r="I184" s="42" t="inlineStr">
@@ -11998,9 +11998,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J184" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J184" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K184" s="13" t="inlineStr"/>
@@ -12018,7 +12018,7 @@
     </row>
     <row r="185" ht="16" customHeight="1">
       <c r="A185" s="15" t="n"/>
-      <c r="B185" s="15" t="n"/>
+      <c r="B185" s="16" t="n"/>
       <c r="C185" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12026,17 +12026,17 @@
       </c>
       <c r="D185" s="38" t="inlineStr">
         <is>
-          <t>晶体光学/激光器件</t>
+          <t>激光/光通信器件</t>
         </is>
       </c>
       <c r="E185" s="39" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="F185" s="40" t="inlineStr">
         <is>
-          <t>002222.SZ</t>
+          <t>000988.SZ</t>
         </is>
       </c>
       <c r="G185" s="41" t="inlineStr">
@@ -12046,7 +12046,7 @@
       </c>
       <c r="H185" s="41" t="inlineStr">
         <is>
-          <t>晶体光学/激光器件</t>
+          <t>激光/光通信器件</t>
         </is>
       </c>
       <c r="I185" s="42" t="inlineStr">
@@ -12054,9 +12054,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J185" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J185" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K185" s="13" t="inlineStr"/>
@@ -12074,7 +12074,11 @@
     </row>
     <row r="186" ht="16" customHeight="1">
       <c r="A186" s="15" t="n"/>
-      <c r="B186" s="15" t="n"/>
+      <c r="B186" s="36" t="inlineStr">
+        <is>
+          <t>OCS 光交换</t>
+        </is>
+      </c>
       <c r="C186" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12082,27 +12086,27 @@
       </c>
       <c r="D186" s="38" t="inlineStr">
         <is>
-          <t>OCS光学组件</t>
+          <t>光学交换技术，替代电交换降低数据中心能耗</t>
         </is>
       </c>
       <c r="E186" s="39" t="inlineStr">
         <is>
-          <t>光库科技</t>
+          <t>腾景科技</t>
         </is>
       </c>
       <c r="F186" s="40" t="inlineStr">
         <is>
-          <t>300620.SZ</t>
+          <t>688195.SH</t>
         </is>
       </c>
       <c r="G186" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H186" s="41" t="inlineStr">
         <is>
-          <t>OCS光学组件</t>
+          <t>光开关/OCS器件</t>
         </is>
       </c>
       <c r="I186" s="42" t="inlineStr">
@@ -12110,9 +12114,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J186" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J186" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K186" s="13" t="inlineStr"/>
@@ -12130,7 +12134,7 @@
     </row>
     <row r="187" ht="16" customHeight="1">
       <c r="A187" s="15" t="n"/>
-      <c r="B187" s="16" t="n"/>
+      <c r="B187" s="15" t="n"/>
       <c r="C187" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12138,27 +12142,27 @@
       </c>
       <c r="D187" s="38" t="inlineStr">
         <is>
-          <t>光模块/相干光器件</t>
+          <t>晶体光学/激光器件</t>
         </is>
       </c>
       <c r="E187" s="39" t="inlineStr">
         <is>
-          <t>德科立</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="F187" s="40" t="inlineStr">
         <is>
-          <t>688205.SH</t>
+          <t>002222.SZ</t>
         </is>
       </c>
       <c r="G187" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H187" s="41" t="inlineStr">
         <is>
-          <t>光模块/相干光器件</t>
+          <t>晶体光学/激光器件</t>
         </is>
       </c>
       <c r="I187" s="42" t="inlineStr">
@@ -12166,9 +12170,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J187" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J187" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K187" s="13" t="inlineStr"/>
@@ -12186,11 +12190,7 @@
     </row>
     <row r="188" ht="16" customHeight="1">
       <c r="A188" s="15" t="n"/>
-      <c r="B188" s="36" t="inlineStr">
-        <is>
-          <t>光芯片 Photonic Chip</t>
-        </is>
-      </c>
+      <c r="B188" s="15" t="n"/>
       <c r="C188" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12198,27 +12198,27 @@
       </c>
       <c r="D188" s="38" t="inlineStr">
         <is>
-          <t>AI算力光互连核心芯片</t>
+          <t>OCS光学组件</t>
         </is>
       </c>
       <c r="E188" s="39" t="inlineStr">
         <is>
-          <t>源杰科技</t>
+          <t>光库科技</t>
         </is>
       </c>
       <c r="F188" s="40" t="inlineStr">
         <is>
-          <t>688498.SH</t>
+          <t>300620.SZ</t>
         </is>
       </c>
       <c r="G188" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H188" s="41" t="inlineStr">
         <is>
-          <t>激光/光芯片</t>
+          <t>OCS光学组件</t>
         </is>
       </c>
       <c r="I188" s="42" t="inlineStr">
@@ -12226,9 +12226,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J188" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J188" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K188" s="13" t="inlineStr"/>
@@ -12237,24 +12237,16 @@
       <c r="N188" s="13" t="inlineStr"/>
       <c r="O188" s="13" t="inlineStr"/>
       <c r="P188" s="13" t="inlineStr"/>
-      <c r="Q188" s="14" t="inlineStr">
-        <is>
-          <t>增持</t>
-        </is>
-      </c>
+      <c r="Q188" s="13" t="inlineStr"/>
       <c r="R188" s="13" t="inlineStr"/>
-      <c r="S188" s="14" t="inlineStr">
-        <is>
-          <t>增持</t>
-        </is>
-      </c>
+      <c r="S188" s="13" t="inlineStr"/>
       <c r="T188" s="13" t="inlineStr"/>
       <c r="U188" s="13" t="inlineStr"/>
       <c r="V188" s="13" t="inlineStr"/>
     </row>
     <row r="189" ht="16" customHeight="1">
       <c r="A189" s="15" t="n"/>
-      <c r="B189" s="15" t="n"/>
+      <c r="B189" s="16" t="n"/>
       <c r="C189" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12262,17 +12254,17 @@
       </c>
       <c r="D189" s="38" t="inlineStr">
         <is>
-          <t>光芯片/PLC分路器</t>
+          <t>光模块/相干光器件</t>
         </is>
       </c>
       <c r="E189" s="39" t="inlineStr">
         <is>
-          <t>仕佳光子</t>
+          <t>德科立</t>
         </is>
       </c>
       <c r="F189" s="40" t="inlineStr">
         <is>
-          <t>688313.SH</t>
+          <t>688205.SH</t>
         </is>
       </c>
       <c r="G189" s="41" t="inlineStr">
@@ -12282,7 +12274,7 @@
       </c>
       <c r="H189" s="41" t="inlineStr">
         <is>
-          <t>光芯片/PLC</t>
+          <t>光模块/相干光器件</t>
         </is>
       </c>
       <c r="I189" s="42" t="inlineStr">
@@ -12290,9 +12282,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J189" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J189" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K189" s="13" t="inlineStr"/>
@@ -12310,7 +12302,11 @@
     </row>
     <row r="190" ht="16" customHeight="1">
       <c r="A190" s="15" t="n"/>
-      <c r="B190" s="15" t="n"/>
+      <c r="B190" s="36" t="inlineStr">
+        <is>
+          <t>光芯片 Photonic Chip</t>
+        </is>
+      </c>
       <c r="C190" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12318,27 +12314,27 @@
       </c>
       <c r="D190" s="38" t="inlineStr">
         <is>
-          <t>光芯片/光模块</t>
+          <t>AI算力光互连核心芯片</t>
         </is>
       </c>
       <c r="E190" s="39" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>源杰科技</t>
         </is>
       </c>
       <c r="F190" s="40" t="inlineStr">
         <is>
-          <t>002281.SZ</t>
+          <t>688498.SH</t>
         </is>
       </c>
       <c r="G190" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H190" s="41" t="inlineStr">
         <is>
-          <t>光芯片/光模块</t>
+          <t>激光/光芯片</t>
         </is>
       </c>
       <c r="I190" s="42" t="inlineStr">
@@ -12346,9 +12342,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J190" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J190" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K190" s="13" t="inlineStr"/>
@@ -12357,9 +12353,17 @@
       <c r="N190" s="13" t="inlineStr"/>
       <c r="O190" s="13" t="inlineStr"/>
       <c r="P190" s="13" t="inlineStr"/>
-      <c r="Q190" s="13" t="inlineStr"/>
+      <c r="Q190" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="R190" s="13" t="inlineStr"/>
-      <c r="S190" s="13" t="inlineStr"/>
+      <c r="S190" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="T190" s="13" t="inlineStr"/>
       <c r="U190" s="13" t="inlineStr"/>
       <c r="V190" s="13" t="inlineStr"/>
@@ -12374,17 +12378,17 @@
       </c>
       <c r="D191" s="38" t="inlineStr">
         <is>
-          <t>高功率激光芯片</t>
+          <t>光芯片/PLC分路器</t>
         </is>
       </c>
       <c r="E191" s="39" t="inlineStr">
         <is>
-          <t>长光华芯</t>
+          <t>仕佳光子</t>
         </is>
       </c>
       <c r="F191" s="40" t="inlineStr">
         <is>
-          <t>688048.SH</t>
+          <t>688313.SH</t>
         </is>
       </c>
       <c r="G191" s="41" t="inlineStr">
@@ -12394,7 +12398,7 @@
       </c>
       <c r="H191" s="41" t="inlineStr">
         <is>
-          <t>高功率激光芯片</t>
+          <t>光芯片/PLC</t>
         </is>
       </c>
       <c r="I191" s="42" t="inlineStr">
@@ -12402,9 +12406,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J191" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J191" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K191" s="13" t="inlineStr"/>
@@ -12430,37 +12434,37 @@
       </c>
       <c r="D192" s="38" t="inlineStr">
         <is>
-          <t>硅光/相干光芯片，全球领先</t>
+          <t>光芯片/光模块</t>
         </is>
       </c>
       <c r="E192" s="39" t="inlineStr">
         <is>
-          <t>相干公司 Coherent</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="F192" s="40" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>002281.SZ</t>
         </is>
       </c>
       <c r="G192" s="41" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H192" s="41" t="inlineStr">
         <is>
-          <t>硅光/相干光芯片</t>
+          <t>光芯片/光模块</t>
         </is>
       </c>
       <c r="I192" s="42" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J192" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J192" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K192" s="13" t="inlineStr"/>
@@ -12469,28 +12473,16 @@
       <c r="N192" s="13" t="inlineStr"/>
       <c r="O192" s="13" t="inlineStr"/>
       <c r="P192" s="13" t="inlineStr"/>
-      <c r="Q192" s="14" t="inlineStr">
-        <is>
-          <t>持有,330</t>
-        </is>
-      </c>
+      <c r="Q192" s="13" t="inlineStr"/>
       <c r="R192" s="13" t="inlineStr"/>
-      <c r="S192" s="14" t="inlineStr">
-        <is>
-          <t>增持,300</t>
-        </is>
-      </c>
+      <c r="S192" s="13" t="inlineStr"/>
       <c r="T192" s="13" t="inlineStr"/>
-      <c r="U192" s="14" t="inlineStr">
-        <is>
-          <t>买入,400</t>
-        </is>
-      </c>
+      <c r="U192" s="13" t="inlineStr"/>
       <c r="V192" s="13" t="inlineStr"/>
     </row>
     <row r="193" ht="16" customHeight="1">
       <c r="A193" s="15" t="n"/>
-      <c r="B193" s="16" t="n"/>
+      <c r="B193" s="15" t="n"/>
       <c r="C193" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12498,37 +12490,37 @@
       </c>
       <c r="D193" s="38" t="inlineStr">
         <is>
-          <t>光通信芯片/VCSEL/硅光，数据中心高速互连</t>
+          <t>高功率激光芯片</t>
         </is>
       </c>
       <c r="E193" s="39" t="inlineStr">
         <is>
-          <t>鲁门特姆 Lumentum</t>
+          <t>长光华芯</t>
         </is>
       </c>
       <c r="F193" s="40" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>688048.SH</t>
         </is>
       </c>
       <c r="G193" s="41" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H193" s="41" t="inlineStr">
         <is>
-          <t>光通信芯片/VCSEL</t>
+          <t>高功率激光芯片</t>
         </is>
       </c>
       <c r="I193" s="42" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J193" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J193" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K193" s="13" t="inlineStr"/>
@@ -12537,36 +12529,16 @@
       <c r="N193" s="13" t="inlineStr"/>
       <c r="O193" s="13" t="inlineStr"/>
       <c r="P193" s="13" t="inlineStr"/>
-      <c r="Q193" s="14" t="inlineStr">
-        <is>
-          <t>持有,上调900</t>
-        </is>
-      </c>
+      <c r="Q193" s="13" t="inlineStr"/>
       <c r="R193" s="13" t="inlineStr"/>
-      <c r="S193" s="14" t="inlineStr">
-        <is>
-          <t>增持,1130</t>
-        </is>
-      </c>
-      <c r="T193" s="14" t="inlineStr">
-        <is>
-          <t>买入,960</t>
-        </is>
-      </c>
+      <c r="S193" s="13" t="inlineStr"/>
+      <c r="T193" s="13" t="inlineStr"/>
       <c r="U193" s="13" t="inlineStr"/>
-      <c r="V193" s="14" t="inlineStr">
-        <is>
-          <t>持有,1000</t>
-        </is>
-      </c>
+      <c r="V193" s="13" t="inlineStr"/>
     </row>
     <row r="194" ht="16" customHeight="1">
       <c r="A194" s="15" t="n"/>
-      <c r="B194" s="36" t="inlineStr">
-        <is>
-          <t>AI服务器 PCB</t>
-        </is>
-      </c>
+      <c r="B194" s="15" t="n"/>
       <c r="C194" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12574,37 +12546,37 @@
       </c>
       <c r="D194" s="38" t="inlineStr">
         <is>
-          <t>AI服务器PCB，算力硬件关键基材，今年大涨60%</t>
+          <t>硅光/相干光芯片，全球领先</t>
         </is>
       </c>
       <c r="E194" s="39" t="inlineStr">
         <is>
-          <t>胜宏科技</t>
+          <t>相干公司 Coherent</t>
         </is>
       </c>
       <c r="F194" s="40" t="inlineStr">
         <is>
-          <t>300476.SZ</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="G194" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="H194" s="41" t="inlineStr">
         <is>
-          <t>AI服务器PCB</t>
+          <t>硅光/相干光芯片</t>
         </is>
       </c>
       <c r="I194" s="42" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="J194" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J194" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K194" s="13" t="inlineStr"/>
@@ -12613,16 +12585,28 @@
       <c r="N194" s="13" t="inlineStr"/>
       <c r="O194" s="13" t="inlineStr"/>
       <c r="P194" s="13" t="inlineStr"/>
-      <c r="Q194" s="13" t="inlineStr"/>
+      <c r="Q194" s="14" t="inlineStr">
+        <is>
+          <t>持有,330</t>
+        </is>
+      </c>
       <c r="R194" s="13" t="inlineStr"/>
-      <c r="S194" s="13" t="inlineStr"/>
+      <c r="S194" s="14" t="inlineStr">
+        <is>
+          <t>增持,300</t>
+        </is>
+      </c>
       <c r="T194" s="13" t="inlineStr"/>
-      <c r="U194" s="13" t="inlineStr"/>
+      <c r="U194" s="14" t="inlineStr">
+        <is>
+          <t>买入,400</t>
+        </is>
+      </c>
       <c r="V194" s="13" t="inlineStr"/>
     </row>
     <row r="195" ht="16" customHeight="1">
       <c r="A195" s="15" t="n"/>
-      <c r="B195" s="15" t="n"/>
+      <c r="B195" s="16" t="n"/>
       <c r="C195" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12630,37 +12614,37 @@
       </c>
       <c r="D195" s="38" t="inlineStr">
         <is>
-          <t>高端PCB/FPC</t>
+          <t>光通信芯片/VCSEL/硅光，数据中心高速互连</t>
         </is>
       </c>
       <c r="E195" s="39" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>鲁门特姆 Lumentum</t>
         </is>
       </c>
       <c r="F195" s="40" t="inlineStr">
         <is>
-          <t>002384.SZ</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G195" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="H195" s="41" t="inlineStr">
         <is>
-          <t>高端PCB/FPC</t>
+          <t>光通信芯片/VCSEL</t>
         </is>
       </c>
       <c r="I195" s="42" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="J195" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J195" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K195" s="13" t="inlineStr"/>
@@ -12671,22 +12655,34 @@
       <c r="P195" s="13" t="inlineStr"/>
       <c r="Q195" s="14" t="inlineStr">
         <is>
-          <t>增持</t>
+          <t>持有,上调900</t>
         </is>
       </c>
       <c r="R195" s="13" t="inlineStr"/>
       <c r="S195" s="14" t="inlineStr">
         <is>
-          <t>增持</t>
-        </is>
-      </c>
-      <c r="T195" s="13" t="inlineStr"/>
+          <t>增持,1130</t>
+        </is>
+      </c>
+      <c r="T195" s="14" t="inlineStr">
+        <is>
+          <t>买入,960</t>
+        </is>
+      </c>
       <c r="U195" s="13" t="inlineStr"/>
-      <c r="V195" s="13" t="inlineStr"/>
+      <c r="V195" s="14" t="inlineStr">
+        <is>
+          <t>持有,1000</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="16" customHeight="1">
       <c r="A196" s="15" t="n"/>
-      <c r="B196" s="15" t="n"/>
+      <c r="B196" s="36" t="inlineStr">
+        <is>
+          <t>AI服务器 PCB</t>
+        </is>
+      </c>
       <c r="C196" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12694,27 +12690,27 @@
       </c>
       <c r="D196" s="38" t="inlineStr">
         <is>
-          <t>AI服务器/封装基板</t>
+          <t>AI服务器PCB，算力硬件关键基材，今年大涨60%</t>
         </is>
       </c>
       <c r="E196" s="39" t="inlineStr">
         <is>
-          <t>深南电路</t>
+          <t>胜宏科技</t>
         </is>
       </c>
       <c r="F196" s="40" t="inlineStr">
         <is>
-          <t>002916.SZ</t>
+          <t>300476.SZ</t>
         </is>
       </c>
       <c r="G196" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H196" s="41" t="inlineStr">
         <is>
-          <t>AI服务器/封装基板</t>
+          <t>AI服务器PCB</t>
         </is>
       </c>
       <c r="I196" s="42" t="inlineStr">
@@ -12722,9 +12718,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J196" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J196" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K196" s="13" t="inlineStr"/>
@@ -12742,7 +12738,7 @@
     </row>
     <row r="197" ht="16" customHeight="1">
       <c r="A197" s="15" t="n"/>
-      <c r="B197" s="16" t="n"/>
+      <c r="B197" s="15" t="n"/>
       <c r="C197" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12750,17 +12746,17 @@
       </c>
       <c r="D197" s="38" t="inlineStr">
         <is>
-          <t>高速高频PCB</t>
+          <t>高端PCB/FPC</t>
         </is>
       </c>
       <c r="E197" s="39" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="F197" s="40" t="inlineStr">
         <is>
-          <t>002463.SZ</t>
+          <t>002384.SZ</t>
         </is>
       </c>
       <c r="G197" s="41" t="inlineStr">
@@ -12770,7 +12766,7 @@
       </c>
       <c r="H197" s="41" t="inlineStr">
         <is>
-          <t>高速高频PCB</t>
+          <t>高端PCB/FPC</t>
         </is>
       </c>
       <c r="I197" s="42" t="inlineStr">
@@ -12778,9 +12774,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J197" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J197" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K197" s="13" t="inlineStr"/>
@@ -12789,20 +12785,24 @@
       <c r="N197" s="13" t="inlineStr"/>
       <c r="O197" s="13" t="inlineStr"/>
       <c r="P197" s="13" t="inlineStr"/>
-      <c r="Q197" s="13" t="inlineStr"/>
+      <c r="Q197" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="R197" s="13" t="inlineStr"/>
-      <c r="S197" s="13" t="inlineStr"/>
+      <c r="S197" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="T197" s="13" t="inlineStr"/>
       <c r="U197" s="13" t="inlineStr"/>
       <c r="V197" s="13" t="inlineStr"/>
     </row>
     <row r="198" ht="16" customHeight="1">
       <c r="A198" s="15" t="n"/>
-      <c r="B198" s="36" t="inlineStr">
-        <is>
-          <t>AI服务器整机</t>
-        </is>
-      </c>
+      <c r="B198" s="15" t="n"/>
       <c r="C198" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12810,27 +12810,27 @@
       </c>
       <c r="D198" s="38" t="inlineStr">
         <is>
-          <t>AI服务器代工/组装</t>
+          <t>AI服务器/封装基板</t>
         </is>
       </c>
       <c r="E198" s="39" t="inlineStr">
         <is>
-          <t>工业富联</t>
+          <t>深南电路</t>
         </is>
       </c>
       <c r="F198" s="40" t="inlineStr">
         <is>
-          <t>601138.SH</t>
+          <t>002916.SZ</t>
         </is>
       </c>
       <c r="G198" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H198" s="41" t="inlineStr">
         <is>
-          <t>AI服务器代工/组装</t>
+          <t>AI服务器/封装基板</t>
         </is>
       </c>
       <c r="I198" s="42" t="inlineStr">
@@ -12838,9 +12838,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J198" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J198" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K198" s="13" t="inlineStr"/>
@@ -12849,11 +12849,7 @@
       <c r="N198" s="13" t="inlineStr"/>
       <c r="O198" s="13" t="inlineStr"/>
       <c r="P198" s="13" t="inlineStr"/>
-      <c r="Q198" s="14" t="inlineStr">
-        <is>
-          <t>增持</t>
-        </is>
-      </c>
+      <c r="Q198" s="13" t="inlineStr"/>
       <c r="R198" s="13" t="inlineStr"/>
       <c r="S198" s="13" t="inlineStr"/>
       <c r="T198" s="13" t="inlineStr"/>
@@ -12862,7 +12858,7 @@
     </row>
     <row r="199" ht="16" customHeight="1">
       <c r="A199" s="15" t="n"/>
-      <c r="B199" s="15" t="n"/>
+      <c r="B199" s="16" t="n"/>
       <c r="C199" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12870,17 +12866,17 @@
       </c>
       <c r="D199" s="38" t="inlineStr">
         <is>
-          <t>AI服务器整机</t>
+          <t>高速高频PCB</t>
         </is>
       </c>
       <c r="E199" s="39" t="inlineStr">
         <is>
-          <t>浪潮信息</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="F199" s="40" t="inlineStr">
         <is>
-          <t>000977.SZ</t>
+          <t>002463.SZ</t>
         </is>
       </c>
       <c r="G199" s="41" t="inlineStr">
@@ -12890,7 +12886,7 @@
       </c>
       <c r="H199" s="41" t="inlineStr">
         <is>
-          <t>AI服务器整机</t>
+          <t>高速高频PCB</t>
         </is>
       </c>
       <c r="I199" s="42" t="inlineStr">
@@ -12898,9 +12894,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J199" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J199" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K199" s="13" t="inlineStr"/>
@@ -12918,7 +12914,11 @@
     </row>
     <row r="200" ht="16" customHeight="1">
       <c r="A200" s="15" t="n"/>
-      <c r="B200" s="15" t="n"/>
+      <c r="B200" s="36" t="inlineStr">
+        <is>
+          <t>AI服务器整机</t>
+        </is>
+      </c>
       <c r="C200" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12926,27 +12926,27 @@
       </c>
       <c r="D200" s="38" t="inlineStr">
         <is>
-          <t>AI服务器/网络设备</t>
+          <t>AI服务器代工/组装</t>
         </is>
       </c>
       <c r="E200" s="39" t="inlineStr">
         <is>
-          <t>紫光股份</t>
+          <t>工业富联</t>
         </is>
       </c>
       <c r="F200" s="40" t="inlineStr">
         <is>
-          <t>000938.SZ</t>
+          <t>601138.SH</t>
         </is>
       </c>
       <c r="G200" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H200" s="41" t="inlineStr">
         <is>
-          <t>AI服务器/网络设备</t>
+          <t>AI服务器代工/组装</t>
         </is>
       </c>
       <c r="I200" s="42" t="inlineStr">
@@ -12954,9 +12954,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J200" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J200" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K200" s="13" t="inlineStr"/>
@@ -12965,7 +12965,11 @@
       <c r="N200" s="13" t="inlineStr"/>
       <c r="O200" s="13" t="inlineStr"/>
       <c r="P200" s="13" t="inlineStr"/>
-      <c r="Q200" s="13" t="inlineStr"/>
+      <c r="Q200" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="R200" s="13" t="inlineStr"/>
       <c r="S200" s="13" t="inlineStr"/>
       <c r="T200" s="13" t="inlineStr"/>
@@ -12982,27 +12986,27 @@
       </c>
       <c r="D201" s="38" t="inlineStr">
         <is>
-          <t>AI服务器/超算</t>
+          <t>AI服务器整机</t>
         </is>
       </c>
       <c r="E201" s="39" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>浪潮信息</t>
         </is>
       </c>
       <c r="F201" s="40" t="inlineStr">
         <is>
-          <t>603019.SH</t>
+          <t>000977.SZ</t>
         </is>
       </c>
       <c r="G201" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H201" s="41" t="inlineStr">
         <is>
-          <t>AI服务器/超算</t>
+          <t>AI服务器整机</t>
         </is>
       </c>
       <c r="I201" s="42" t="inlineStr">
@@ -13010,9 +13014,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J201" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J201" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K201" s="13" t="inlineStr"/>
@@ -13030,7 +13034,7 @@
     </row>
     <row r="202" ht="16" customHeight="1">
       <c r="A202" s="15" t="n"/>
-      <c r="B202" s="16" t="n"/>
+      <c r="B202" s="15" t="n"/>
       <c r="C202" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13038,37 +13042,37 @@
       </c>
       <c r="D202" s="38" t="inlineStr">
         <is>
-          <t>AI服务器/机柜，台湾云端服务器龙头</t>
+          <t>AI服务器/网络设备</t>
         </is>
       </c>
       <c r="E202" s="39" t="inlineStr">
         <is>
-          <t>纬颖科技 Wiwynn</t>
+          <t>紫光股份</t>
         </is>
       </c>
       <c r="F202" s="40" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>000938.SZ</t>
         </is>
       </c>
       <c r="G202" s="41" t="inlineStr">
         <is>
-          <t>台湾证交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H202" s="41" t="inlineStr">
         <is>
-          <t>AI服务器/机柜</t>
+          <t>AI服务器/网络设备</t>
         </is>
       </c>
       <c r="I202" s="42" t="inlineStr">
         <is>
-          <t>TWD</t>
-        </is>
-      </c>
-      <c r="J202" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J202" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K202" s="13" t="inlineStr"/>
@@ -13086,11 +13090,7 @@
     </row>
     <row r="203" ht="16" customHeight="1">
       <c r="A203" s="15" t="n"/>
-      <c r="B203" s="36" t="inlineStr">
-        <is>
-          <t>AI芯片</t>
-        </is>
-      </c>
+      <c r="B203" s="15" t="n"/>
       <c r="C203" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13098,27 +13098,27 @@
       </c>
       <c r="D203" s="38" t="inlineStr">
         <is>
-          <t>国产GPU/DCU芯片，AI训练推理</t>
+          <t>AI服务器/超算</t>
         </is>
       </c>
       <c r="E203" s="39" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="F203" s="40" t="inlineStr">
         <is>
-          <t>688041.SH</t>
+          <t>603019.SH</t>
         </is>
       </c>
       <c r="G203" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H203" s="41" t="inlineStr">
         <is>
-          <t>GPU/DCU芯片</t>
+          <t>AI服务器/超算</t>
         </is>
       </c>
       <c r="I203" s="42" t="inlineStr">
@@ -13126,9 +13126,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J203" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J203" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K203" s="13" t="inlineStr"/>
@@ -13146,7 +13146,7 @@
     </row>
     <row r="204" ht="16" customHeight="1">
       <c r="A204" s="15" t="n"/>
-      <c r="B204" s="15" t="n"/>
+      <c r="B204" s="16" t="n"/>
       <c r="C204" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13154,37 +13154,37 @@
       </c>
       <c r="D204" s="38" t="inlineStr">
         <is>
-          <t>AI推理/训练芯片</t>
+          <t>AI服务器/机柜，台湾云端服务器龙头</t>
         </is>
       </c>
       <c r="E204" s="39" t="inlineStr">
         <is>
-          <t>寒武纪</t>
+          <t>纬颖科技 Wiwynn</t>
         </is>
       </c>
       <c r="F204" s="40" t="inlineStr">
         <is>
-          <t>688256.SH</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="G204" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>台湾证交所</t>
         </is>
       </c>
       <c r="H204" s="41" t="inlineStr">
         <is>
-          <t>AI推理/训练芯片</t>
+          <t>AI服务器/机柜</t>
         </is>
       </c>
       <c r="I204" s="42" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="J204" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="J204" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K204" s="13" t="inlineStr"/>
@@ -13202,7 +13202,11 @@
     </row>
     <row r="205" ht="16" customHeight="1">
       <c r="A205" s="15" t="n"/>
-      <c r="B205" s="15" t="n"/>
+      <c r="B205" s="36" t="inlineStr">
+        <is>
+          <t>AI芯片</t>
+        </is>
+      </c>
       <c r="C205" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13210,17 +13214,17 @@
       </c>
       <c r="D205" s="38" t="inlineStr">
         <is>
-          <t>GPU架构芯片，2024年登陆科创板</t>
+          <t>国产GPU/DCU芯片，AI训练推理</t>
         </is>
       </c>
       <c r="E205" s="39" t="inlineStr">
         <is>
-          <t>沐曦股份</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="F205" s="40" t="inlineStr">
         <is>
-          <t>688802.SH</t>
+          <t>688041.SH</t>
         </is>
       </c>
       <c r="G205" s="41" t="inlineStr">
@@ -13230,7 +13234,7 @@
       </c>
       <c r="H205" s="41" t="inlineStr">
         <is>
-          <t>GPU架构芯片</t>
+          <t>GPU/DCU芯片</t>
         </is>
       </c>
       <c r="I205" s="42" t="inlineStr">
@@ -13238,9 +13242,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J205" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J205" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K205" s="13" t="inlineStr"/>
@@ -13258,7 +13262,7 @@
     </row>
     <row r="206" ht="16" customHeight="1">
       <c r="A206" s="15" t="n"/>
-      <c r="B206" s="16" t="n"/>
+      <c r="B206" s="15" t="n"/>
       <c r="C206" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13266,17 +13270,17 @@
       </c>
       <c r="D206" s="38" t="inlineStr">
         <is>
-          <t>GPU芯片，2024年登陆科创板</t>
+          <t>AI推理/训练芯片</t>
         </is>
       </c>
       <c r="E206" s="39" t="inlineStr">
         <is>
-          <t>摩尔线程</t>
+          <t>寒武纪</t>
         </is>
       </c>
       <c r="F206" s="40" t="inlineStr">
         <is>
-          <t>688795.SH</t>
+          <t>688256.SH</t>
         </is>
       </c>
       <c r="G206" s="41" t="inlineStr">
@@ -13286,7 +13290,7 @@
       </c>
       <c r="H206" s="41" t="inlineStr">
         <is>
-          <t>GPU芯片</t>
+          <t>AI推理/训练芯片</t>
         </is>
       </c>
       <c r="I206" s="42" t="inlineStr">
@@ -13294,9 +13298,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J206" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J206" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K206" s="13" t="inlineStr"/>
@@ -13314,11 +13318,7 @@
     </row>
     <row r="207" ht="16" customHeight="1">
       <c r="A207" s="15" t="n"/>
-      <c r="B207" s="36" t="inlineStr">
-        <is>
-          <t>光纤光缆</t>
-        </is>
-      </c>
+      <c r="B207" s="15" t="n"/>
       <c r="C207" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13326,27 +13326,27 @@
       </c>
       <c r="D207" s="38" t="inlineStr">
         <is>
-          <t>AI数据中心高速互连光纤</t>
+          <t>GPU架构芯片，2024年登陆科创板</t>
         </is>
       </c>
       <c r="E207" s="39" t="inlineStr">
         <is>
-          <t>长飞光纤</t>
+          <t>沐曦股份</t>
         </is>
       </c>
       <c r="F207" s="40" t="inlineStr">
         <is>
-          <t>601869.SH</t>
+          <t>688802.SH</t>
         </is>
       </c>
       <c r="G207" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H207" s="41" t="inlineStr">
         <is>
-          <t>光纤预制棒/光缆</t>
+          <t>GPU架构芯片</t>
         </is>
       </c>
       <c r="I207" s="42" t="inlineStr">
@@ -13354,9 +13354,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J207" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J207" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K207" s="13" t="inlineStr"/>
@@ -13374,7 +13374,7 @@
     </row>
     <row r="208" ht="16" customHeight="1">
       <c r="A208" s="15" t="n"/>
-      <c r="B208" s="15" t="n"/>
+      <c r="B208" s="16" t="n"/>
       <c r="C208" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13382,27 +13382,27 @@
       </c>
       <c r="D208" s="38" t="inlineStr">
         <is>
-          <t>光纤光缆/海缆</t>
+          <t>GPU芯片，2024年登陆科创板</t>
         </is>
       </c>
       <c r="E208" s="39" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>摩尔线程</t>
         </is>
       </c>
       <c r="F208" s="40" t="inlineStr">
         <is>
-          <t>600487.SH</t>
+          <t>688795.SH</t>
         </is>
       </c>
       <c r="G208" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H208" s="41" t="inlineStr">
         <is>
-          <t>光纤光缆/海缆</t>
+          <t>GPU芯片</t>
         </is>
       </c>
       <c r="I208" s="42" t="inlineStr">
@@ -13410,9 +13410,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J208" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J208" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K208" s="13" t="inlineStr"/>
@@ -13430,7 +13430,11 @@
     </row>
     <row r="209" ht="16" customHeight="1">
       <c r="A209" s="15" t="n"/>
-      <c r="B209" s="15" t="n"/>
+      <c r="B209" s="36" t="inlineStr">
+        <is>
+          <t>光纤光缆</t>
+        </is>
+      </c>
       <c r="C209" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13438,17 +13442,17 @@
       </c>
       <c r="D209" s="38" t="inlineStr">
         <is>
-          <t>光纤光缆/海缆</t>
+          <t>AI数据中心高速互连光纤</t>
         </is>
       </c>
       <c r="E209" s="39" t="inlineStr">
         <is>
-          <t>中天科技</t>
+          <t>长飞光纤</t>
         </is>
       </c>
       <c r="F209" s="40" t="inlineStr">
         <is>
-          <t>600522.SH</t>
+          <t>601869.SH</t>
         </is>
       </c>
       <c r="G209" s="41" t="inlineStr">
@@ -13458,7 +13462,7 @@
       </c>
       <c r="H209" s="41" t="inlineStr">
         <is>
-          <t>光纤光缆/海缆</t>
+          <t>光纤预制棒/光缆</t>
         </is>
       </c>
       <c r="I209" s="42" t="inlineStr">
@@ -13466,9 +13470,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J209" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J209" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K209" s="13" t="inlineStr"/>
@@ -13486,7 +13490,7 @@
     </row>
     <row r="210" ht="16" customHeight="1">
       <c r="A210" s="15" t="n"/>
-      <c r="B210" s="16" t="n"/>
+      <c r="B210" s="15" t="n"/>
       <c r="C210" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13494,17 +13498,17 @@
       </c>
       <c r="D210" s="38" t="inlineStr">
         <is>
-          <t>光纤光缆/通信设备</t>
+          <t>光纤光缆/海缆</t>
         </is>
       </c>
       <c r="E210" s="39" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="F210" s="40" t="inlineStr">
         <is>
-          <t>600498.SH</t>
+          <t>600487.SH</t>
         </is>
       </c>
       <c r="G210" s="41" t="inlineStr">
@@ -13514,7 +13518,7 @@
       </c>
       <c r="H210" s="41" t="inlineStr">
         <is>
-          <t>光纤光缆/通信设备</t>
+          <t>光纤光缆/海缆</t>
         </is>
       </c>
       <c r="I210" s="42" t="inlineStr">
@@ -13522,9 +13526,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J210" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J210" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K210" s="13" t="inlineStr"/>
@@ -13542,11 +13546,7 @@
     </row>
     <row r="211" ht="16" customHeight="1">
       <c r="A211" s="15" t="n"/>
-      <c r="B211" s="36" t="inlineStr">
-        <is>
-          <t>存储芯片</t>
-        </is>
-      </c>
+      <c r="B211" s="15" t="n"/>
       <c r="C211" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13554,27 +13554,27 @@
       </c>
       <c r="D211" s="38" t="inlineStr">
         <is>
-          <t>AI训练推理大规模存储，NAND存储模组</t>
+          <t>光纤光缆/海缆</t>
         </is>
       </c>
       <c r="E211" s="39" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>中天科技</t>
         </is>
       </c>
       <c r="F211" s="40" t="inlineStr">
         <is>
-          <t>001323.SZ</t>
+          <t>600522.SH</t>
         </is>
       </c>
       <c r="G211" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H211" s="41" t="inlineStr">
         <is>
-          <t>NAND Flash存储模组</t>
+          <t>光纤光缆/海缆</t>
         </is>
       </c>
       <c r="I211" s="42" t="inlineStr">
@@ -13582,9 +13582,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J211" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J211" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K211" s="13" t="inlineStr"/>
@@ -13602,7 +13602,7 @@
     </row>
     <row r="212" ht="16" customHeight="1">
       <c r="A212" s="15" t="n"/>
-      <c r="B212" s="15" t="n"/>
+      <c r="B212" s="16" t="n"/>
       <c r="C212" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13610,17 +13610,17 @@
       </c>
       <c r="D212" s="38" t="inlineStr">
         <is>
-          <t>NOR Flash/MCU</t>
+          <t>光纤光缆/通信设备</t>
         </is>
       </c>
       <c r="E212" s="39" t="inlineStr">
         <is>
-          <t>兆易创新</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="F212" s="40" t="inlineStr">
         <is>
-          <t>603986.SH</t>
+          <t>600498.SH</t>
         </is>
       </c>
       <c r="G212" s="41" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="H212" s="41" t="inlineStr">
         <is>
-          <t>NOR Flash/MCU</t>
+          <t>光纤光缆/通信设备</t>
         </is>
       </c>
       <c r="I212" s="42" t="inlineStr">
@@ -13638,9 +13638,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J212" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J212" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K212" s="13" t="inlineStr"/>
@@ -13658,7 +13658,11 @@
     </row>
     <row r="213" ht="16" customHeight="1">
       <c r="A213" s="15" t="n"/>
-      <c r="B213" s="15" t="n"/>
+      <c r="B213" s="36" t="inlineStr">
+        <is>
+          <t>存储芯片</t>
+        </is>
+      </c>
       <c r="C213" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13666,27 +13670,27 @@
       </c>
       <c r="D213" s="38" t="inlineStr">
         <is>
-          <t>NAND存储模组</t>
+          <t>AI训练推理大规模存储，NAND存储模组</t>
         </is>
       </c>
       <c r="E213" s="39" t="inlineStr">
         <is>
-          <t>佰维存储</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="F213" s="40" t="inlineStr">
         <is>
-          <t>688525.SH</t>
+          <t>001323.SZ</t>
         </is>
       </c>
       <c r="G213" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H213" s="41" t="inlineStr">
         <is>
-          <t>NAND存储模组</t>
+          <t>NAND Flash存储模组</t>
         </is>
       </c>
       <c r="I213" s="42" t="inlineStr">
@@ -13694,9 +13698,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J213" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J213" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K213" s="13" t="inlineStr"/>
@@ -13722,27 +13726,27 @@
       </c>
       <c r="D214" s="38" t="inlineStr">
         <is>
-          <t>NAND/eMMC存储</t>
+          <t>NOR Flash/MCU</t>
         </is>
       </c>
       <c r="E214" s="39" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>兆易创新</t>
         </is>
       </c>
       <c r="F214" s="40" t="inlineStr">
         <is>
-          <t>301308.SZ</t>
+          <t>603986.SH</t>
         </is>
       </c>
       <c r="G214" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H214" s="41" t="inlineStr">
         <is>
-          <t>NAND/eMMC存储</t>
+          <t>NOR Flash/MCU</t>
         </is>
       </c>
       <c r="I214" s="42" t="inlineStr">
@@ -13750,9 +13754,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J214" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J214" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K214" s="13" t="inlineStr"/>
@@ -13778,37 +13782,37 @@
       </c>
       <c r="D215" s="38" t="inlineStr">
         <is>
-          <t>全球DRAM/NAND/HBM龙头，AI训练核心</t>
+          <t>NAND存储模组</t>
         </is>
       </c>
       <c r="E215" s="39" t="inlineStr">
         <is>
-          <t>三星电子 Samsung</t>
+          <t>佰维存储</t>
         </is>
       </c>
       <c r="F215" s="40" t="inlineStr">
         <is>
-          <t>005930.KS</t>
+          <t>688525.SH</t>
         </is>
       </c>
       <c r="G215" s="41" t="inlineStr">
         <is>
-          <t>韩国证交所</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H215" s="41" t="inlineStr">
         <is>
-          <t>DRAM/NAND/HBM</t>
+          <t>NAND存储模组</t>
         </is>
       </c>
       <c r="I215" s="42" t="inlineStr">
         <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="J215" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J215" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K215" s="13" t="inlineStr"/>
@@ -13817,32 +13821,12 @@
       <c r="N215" s="13" t="inlineStr"/>
       <c r="O215" s="13" t="inlineStr"/>
       <c r="P215" s="13" t="inlineStr"/>
-      <c r="Q215" s="14" t="inlineStr">
-        <is>
-          <t>买入,362000</t>
-        </is>
-      </c>
-      <c r="R215" s="14" t="inlineStr">
-        <is>
-          <t>买入,260000</t>
-        </is>
-      </c>
-      <c r="S215" s="14" t="inlineStr">
-        <is>
-          <t>买入,350000</t>
-        </is>
-      </c>
-      <c r="T215" s="14" t="inlineStr">
-        <is>
-          <t>买入,266000</t>
-        </is>
-      </c>
+      <c r="Q215" s="13" t="inlineStr"/>
+      <c r="R215" s="13" t="inlineStr"/>
+      <c r="S215" s="13" t="inlineStr"/>
+      <c r="T215" s="13" t="inlineStr"/>
       <c r="U215" s="13" t="inlineStr"/>
-      <c r="V215" s="14" t="inlineStr">
-        <is>
-          <t>买入,362006</t>
-        </is>
-      </c>
+      <c r="V215" s="13" t="inlineStr"/>
     </row>
     <row r="216" ht="16" customHeight="1">
       <c r="A216" s="15" t="n"/>
@@ -13854,37 +13838,37 @@
       </c>
       <c r="D216" s="38" t="inlineStr">
         <is>
-          <t>HBM3/DRAM全球第二，AI算力关键</t>
+          <t>NAND/eMMC存储</t>
         </is>
       </c>
       <c r="E216" s="39" t="inlineStr">
         <is>
-          <t>SK海力士 SK Hynix</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="F216" s="40" t="inlineStr">
         <is>
-          <t>000660.KS</t>
+          <t>301308.SZ</t>
         </is>
       </c>
       <c r="G216" s="41" t="inlineStr">
         <is>
-          <t>韩国证交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H216" s="41" t="inlineStr">
         <is>
-          <t>HBM/DRAM/NAND</t>
+          <t>NAND/eMMC存储</t>
         </is>
       </c>
       <c r="I216" s="42" t="inlineStr">
         <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="J216" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J216" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K216" s="13" t="inlineStr"/>
@@ -13893,26 +13877,10 @@
       <c r="N216" s="13" t="inlineStr"/>
       <c r="O216" s="13" t="inlineStr"/>
       <c r="P216" s="13" t="inlineStr"/>
-      <c r="Q216" s="14" t="inlineStr">
-        <is>
-          <t>增持,2900000</t>
-        </is>
-      </c>
-      <c r="R216" s="14" t="inlineStr">
-        <is>
-          <t>强力买入,1350000</t>
-        </is>
-      </c>
-      <c r="S216" s="14" t="inlineStr">
-        <is>
-          <t>买入,1450000</t>
-        </is>
-      </c>
-      <c r="T216" s="14" t="inlineStr">
-        <is>
-          <t>买入,1500000</t>
-        </is>
-      </c>
+      <c r="Q216" s="13" t="inlineStr"/>
+      <c r="R216" s="13" t="inlineStr"/>
+      <c r="S216" s="13" t="inlineStr"/>
+      <c r="T216" s="13" t="inlineStr"/>
       <c r="U216" s="13" t="inlineStr"/>
       <c r="V216" s="13" t="inlineStr"/>
     </row>
@@ -13926,22 +13894,22 @@
       </c>
       <c r="D217" s="38" t="inlineStr">
         <is>
-          <t>DRAM/NAND存储，HBM3E量产</t>
+          <t>全球DRAM/NAND/HBM龙头，AI训练核心</t>
         </is>
       </c>
       <c r="E217" s="39" t="inlineStr">
         <is>
-          <t>美光科技 Micron</t>
+          <t>三星电子 Samsung</t>
         </is>
       </c>
       <c r="F217" s="40" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>005930.KS</t>
         </is>
       </c>
       <c r="G217" s="41" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>韩国证交所</t>
         </is>
       </c>
       <c r="H217" s="41" t="inlineStr">
@@ -13951,7 +13919,7 @@
       </c>
       <c r="I217" s="42" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="J217" s="23" t="inlineStr">
@@ -13967,30 +13935,34 @@
       <c r="P217" s="13" t="inlineStr"/>
       <c r="Q217" s="14" t="inlineStr">
         <is>
-          <t>买入首选,450</t>
+          <t>买入,362000</t>
         </is>
       </c>
       <c r="R217" s="14" t="inlineStr">
         <is>
-          <t>中性,360</t>
-        </is>
-      </c>
-      <c r="S217" s="13" t="inlineStr"/>
+          <t>买入,260000</t>
+        </is>
+      </c>
+      <c r="S217" s="14" t="inlineStr">
+        <is>
+          <t>买入,350000</t>
+        </is>
+      </c>
       <c r="T217" s="14" t="inlineStr">
         <is>
-          <t>买入,535</t>
-        </is>
-      </c>
-      <c r="U217" s="14" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="V217" s="13" t="inlineStr"/>
+          <t>买入,266000</t>
+        </is>
+      </c>
+      <c r="U217" s="13" t="inlineStr"/>
+      <c r="V217" s="14" t="inlineStr">
+        <is>
+          <t>买入,362006</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="16" customHeight="1">
       <c r="A218" s="15" t="n"/>
-      <c r="B218" s="16" t="n"/>
+      <c r="B218" s="15" t="n"/>
       <c r="C218" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13998,32 +13970,32 @@
       </c>
       <c r="D218" s="38" t="inlineStr">
         <is>
-          <t>AI存储接口/网络芯片，Marvell ASIC</t>
+          <t>HBM3/DRAM全球第二，AI算力关键</t>
         </is>
       </c>
       <c r="E218" s="39" t="inlineStr">
         <is>
-          <t>美满电子 Marvell</t>
+          <t>SK海力士 SK Hynix</t>
         </is>
       </c>
       <c r="F218" s="40" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>000660.KS</t>
         </is>
       </c>
       <c r="G218" s="41" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>韩国证交所</t>
         </is>
       </c>
       <c r="H218" s="41" t="inlineStr">
         <is>
-          <t>AI网络/存储接口芯片</t>
+          <t>HBM/DRAM/NAND</t>
         </is>
       </c>
       <c r="I218" s="42" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="J218" s="23" t="inlineStr">
@@ -14039,22 +14011,30 @@
       <c r="P218" s="13" t="inlineStr"/>
       <c r="Q218" s="14" t="inlineStr">
         <is>
-          <t>增持</t>
-        </is>
-      </c>
-      <c r="R218" s="13" t="inlineStr"/>
-      <c r="S218" s="13" t="inlineStr"/>
-      <c r="T218" s="13" t="inlineStr"/>
+          <t>增持,2900000</t>
+        </is>
+      </c>
+      <c r="R218" s="14" t="inlineStr">
+        <is>
+          <t>强力买入,1350000</t>
+        </is>
+      </c>
+      <c r="S218" s="14" t="inlineStr">
+        <is>
+          <t>买入,1450000</t>
+        </is>
+      </c>
+      <c r="T218" s="14" t="inlineStr">
+        <is>
+          <t>买入,1500000</t>
+        </is>
+      </c>
       <c r="U218" s="13" t="inlineStr"/>
       <c r="V218" s="13" t="inlineStr"/>
     </row>
     <row r="219" ht="16" customHeight="1">
       <c r="A219" s="15" t="n"/>
-      <c r="B219" s="36" t="inlineStr">
-        <is>
-          <t>高速链接 Interconnect</t>
-        </is>
-      </c>
+      <c r="B219" s="15" t="n"/>
       <c r="C219" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14062,37 +14042,37 @@
       </c>
       <c r="D219" s="38" t="inlineStr">
         <is>
-          <t>AI服务器高速铜缆/连接器</t>
+          <t>DRAM/NAND存储，HBM3E量产</t>
         </is>
       </c>
       <c r="E219" s="39" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>美光科技 Micron</t>
         </is>
       </c>
       <c r="F219" s="40" t="inlineStr">
         <is>
-          <t>002475.SZ</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="G219" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="H219" s="41" t="inlineStr">
         <is>
-          <t>高速连接器/线缆</t>
+          <t>DRAM/NAND/HBM</t>
         </is>
       </c>
       <c r="I219" s="42" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="J219" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J219" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K219" s="13" t="inlineStr"/>
@@ -14103,22 +14083,30 @@
       <c r="P219" s="13" t="inlineStr"/>
       <c r="Q219" s="14" t="inlineStr">
         <is>
-          <t>增持</t>
+          <t>买入首选,450</t>
         </is>
       </c>
       <c r="R219" s="14" t="inlineStr">
         <is>
-          <t>买入</t>
+          <t>中性,360</t>
         </is>
       </c>
       <c r="S219" s="13" t="inlineStr"/>
-      <c r="T219" s="13" t="inlineStr"/>
-      <c r="U219" s="13" t="inlineStr"/>
+      <c r="T219" s="14" t="inlineStr">
+        <is>
+          <t>买入,535</t>
+        </is>
+      </c>
+      <c r="U219" s="14" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
       <c r="V219" s="13" t="inlineStr"/>
     </row>
     <row r="220" ht="16" customHeight="1">
       <c r="A220" s="15" t="n"/>
-      <c r="B220" s="15" t="n"/>
+      <c r="B220" s="16" t="n"/>
       <c r="C220" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14126,37 +14114,37 @@
       </c>
       <c r="D220" s="38" t="inlineStr">
         <is>
-          <t>高速铜缆/连接器</t>
+          <t>AI存储接口/网络芯片，Marvell ASIC</t>
         </is>
       </c>
       <c r="E220" s="39" t="inlineStr">
         <is>
-          <t>兆龙互连</t>
+          <t>美满电子 Marvell</t>
         </is>
       </c>
       <c r="F220" s="40" t="inlineStr">
         <is>
-          <t>603557.SH</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="G220" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="H220" s="41" t="inlineStr">
         <is>
-          <t>高速铜缆/连接器</t>
+          <t>AI网络/存储接口芯片</t>
         </is>
       </c>
       <c r="I220" s="42" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="J220" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J220" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K220" s="13" t="inlineStr"/>
@@ -14165,7 +14153,11 @@
       <c r="N220" s="13" t="inlineStr"/>
       <c r="O220" s="13" t="inlineStr"/>
       <c r="P220" s="13" t="inlineStr"/>
-      <c r="Q220" s="13" t="inlineStr"/>
+      <c r="Q220" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="R220" s="13" t="inlineStr"/>
       <c r="S220" s="13" t="inlineStr"/>
       <c r="T220" s="13" t="inlineStr"/>
@@ -14174,7 +14166,11 @@
     </row>
     <row r="221" ht="16" customHeight="1">
       <c r="A221" s="15" t="n"/>
-      <c r="B221" s="15" t="n"/>
+      <c r="B221" s="36" t="inlineStr">
+        <is>
+          <t>高速链接 Interconnect</t>
+        </is>
+      </c>
       <c r="C221" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14182,17 +14178,17 @@
       </c>
       <c r="D221" s="38" t="inlineStr">
         <is>
-          <t>高速线缆/热缩材料</t>
+          <t>AI服务器高速铜缆/连接器</t>
         </is>
       </c>
       <c r="E221" s="39" t="inlineStr">
         <is>
-          <t>沃尔核材</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="F221" s="40" t="inlineStr">
         <is>
-          <t>002130.SZ</t>
+          <t>002475.SZ</t>
         </is>
       </c>
       <c r="G221" s="41" t="inlineStr">
@@ -14202,7 +14198,7 @@
       </c>
       <c r="H221" s="41" t="inlineStr">
         <is>
-          <t>高速线缆/热缩材料</t>
+          <t>高速连接器/线缆</t>
         </is>
       </c>
       <c r="I221" s="42" t="inlineStr">
@@ -14210,9 +14206,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J221" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J221" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K221" s="13" t="inlineStr"/>
@@ -14221,8 +14217,16 @@
       <c r="N221" s="13" t="inlineStr"/>
       <c r="O221" s="13" t="inlineStr"/>
       <c r="P221" s="13" t="inlineStr"/>
-      <c r="Q221" s="13" t="inlineStr"/>
-      <c r="R221" s="13" t="inlineStr"/>
+      <c r="Q221" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="R221" s="14" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
       <c r="S221" s="13" t="inlineStr"/>
       <c r="T221" s="13" t="inlineStr"/>
       <c r="U221" s="13" t="inlineStr"/>
@@ -14230,7 +14234,7 @@
     </row>
     <row r="222" ht="16" customHeight="1">
       <c r="A222" s="15" t="n"/>
-      <c r="B222" s="16" t="n"/>
+      <c r="B222" s="15" t="n"/>
       <c r="C222" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14238,27 +14242,27 @@
       </c>
       <c r="D222" s="38" t="inlineStr">
         <is>
-          <t>高速连接器</t>
+          <t>高速铜缆/连接器</t>
         </is>
       </c>
       <c r="E222" s="39" t="inlineStr">
         <is>
-          <t>鼎通科技</t>
+          <t>兆龙互连</t>
         </is>
       </c>
       <c r="F222" s="40" t="inlineStr">
         <is>
-          <t>301291.SZ</t>
+          <t>603557.SH</t>
         </is>
       </c>
       <c r="G222" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H222" s="41" t="inlineStr">
         <is>
-          <t>高速连接器</t>
+          <t>高速铜缆/连接器</t>
         </is>
       </c>
       <c r="I222" s="42" t="inlineStr">
@@ -14266,9 +14270,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J222" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J222" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K222" s="13" t="inlineStr"/>
@@ -14286,11 +14290,7 @@
     </row>
     <row r="223" ht="16" customHeight="1">
       <c r="A223" s="15" t="n"/>
-      <c r="B223" s="36" t="inlineStr">
-        <is>
-          <t>液冷 Liquid Cooling</t>
-        </is>
-      </c>
+      <c r="B223" s="15" t="n"/>
       <c r="C223" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14298,17 +14298,17 @@
       </c>
       <c r="D223" s="38" t="inlineStr">
         <is>
-          <t>AI数据中心液冷散热，H100/H200热耗密度极高</t>
+          <t>高速线缆/热缩材料</t>
         </is>
       </c>
       <c r="E223" s="39" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>沃尔核材</t>
         </is>
       </c>
       <c r="F223" s="40" t="inlineStr">
         <is>
-          <t>002837.SZ</t>
+          <t>002130.SZ</t>
         </is>
       </c>
       <c r="G223" s="41" t="inlineStr">
@@ -14318,7 +14318,7 @@
       </c>
       <c r="H223" s="41" t="inlineStr">
         <is>
-          <t>液冷/机房热管理</t>
+          <t>高速线缆/热缩材料</t>
         </is>
       </c>
       <c r="I223" s="42" t="inlineStr">
@@ -14326,9 +14326,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J223" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J223" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K223" s="13" t="inlineStr"/>
@@ -14346,7 +14346,7 @@
     </row>
     <row r="224" ht="16" customHeight="1">
       <c r="A224" s="15" t="n"/>
-      <c r="B224" s="15" t="n"/>
+      <c r="B224" s="16" t="n"/>
       <c r="C224" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14354,27 +14354,27 @@
       </c>
       <c r="D224" s="38" t="inlineStr">
         <is>
-          <t>液冷系统</t>
+          <t>高速连接器</t>
         </is>
       </c>
       <c r="E224" s="39" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>鼎通科技</t>
         </is>
       </c>
       <c r="F224" s="40" t="inlineStr">
         <is>
-          <t>300499.SZ</t>
+          <t>301291.SZ</t>
         </is>
       </c>
       <c r="G224" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H224" s="41" t="inlineStr">
         <is>
-          <t>液冷系统</t>
+          <t>高速连接器</t>
         </is>
       </c>
       <c r="I224" s="42" t="inlineStr">
@@ -14382,9 +14382,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J224" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J224" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K224" s="13" t="inlineStr"/>
@@ -14402,7 +14402,11 @@
     </row>
     <row r="225" ht="16" customHeight="1">
       <c r="A225" s="15" t="n"/>
-      <c r="B225" s="16" t="n"/>
+      <c r="B225" s="36" t="inlineStr">
+        <is>
+          <t>液冷 Liquid Cooling</t>
+        </is>
+      </c>
       <c r="C225" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14410,27 +14414,27 @@
       </c>
       <c r="D225" s="38" t="inlineStr">
         <is>
-          <t>液冷AI服务器/超算</t>
+          <t>AI数据中心液冷散热，H100/H200热耗密度极高</t>
         </is>
       </c>
       <c r="E225" s="39" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="F225" s="40" t="inlineStr">
         <is>
-          <t>603019.SH</t>
+          <t>002837.SZ</t>
         </is>
       </c>
       <c r="G225" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H225" s="41" t="inlineStr">
         <is>
-          <t>液冷AI服务器/超算</t>
+          <t>液冷/机房热管理</t>
         </is>
       </c>
       <c r="I225" s="42" t="inlineStr">
@@ -14438,9 +14442,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J225" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J225" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K225" s="13" t="inlineStr"/>
@@ -14458,11 +14462,7 @@
     </row>
     <row r="226" ht="16" customHeight="1">
       <c r="A226" s="15" t="n"/>
-      <c r="B226" s="36" t="inlineStr">
-        <is>
-          <t>电源 Power Supply</t>
-        </is>
-      </c>
+      <c r="B226" s="15" t="n"/>
       <c r="C226" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14470,27 +14470,27 @@
       </c>
       <c r="D226" s="38" t="inlineStr">
         <is>
-          <t>数据中心电源/UPS</t>
+          <t>液冷系统</t>
         </is>
       </c>
       <c r="E226" s="39" t="inlineStr">
         <is>
-          <t>中恒电气</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="F226" s="40" t="inlineStr">
         <is>
-          <t>002364.SZ</t>
+          <t>300499.SZ</t>
         </is>
       </c>
       <c r="G226" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H226" s="41" t="inlineStr">
         <is>
-          <t>数据中心电源</t>
+          <t>液冷系统</t>
         </is>
       </c>
       <c r="I226" s="42" t="inlineStr">
@@ -14498,9 +14498,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J226" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J226" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K226" s="13" t="inlineStr"/>
@@ -14518,7 +14518,7 @@
     </row>
     <row r="227" ht="16" customHeight="1">
       <c r="A227" s="15" t="n"/>
-      <c r="B227" s="15" t="n"/>
+      <c r="B227" s="16" t="n"/>
       <c r="C227" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14526,27 +14526,27 @@
       </c>
       <c r="D227" s="38" t="inlineStr">
         <is>
-          <t>UPS/储能电源</t>
+          <t>液冷AI服务器/超算</t>
         </is>
       </c>
       <c r="E227" s="39" t="inlineStr">
         <is>
-          <t>圣阳股份</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="F227" s="40" t="inlineStr">
         <is>
-          <t>002580.SZ</t>
+          <t>603019.SH</t>
         </is>
       </c>
       <c r="G227" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H227" s="41" t="inlineStr">
         <is>
-          <t>UPS/储能电源</t>
+          <t>液冷AI服务器/超算</t>
         </is>
       </c>
       <c r="I227" s="42" t="inlineStr">
@@ -14554,9 +14554,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J227" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J227" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K227" s="13" t="inlineStr"/>
@@ -14574,7 +14574,11 @@
     </row>
     <row r="228" ht="16" customHeight="1">
       <c r="A228" s="15" t="n"/>
-      <c r="B228" s="15" t="n"/>
+      <c r="B228" s="36" t="inlineStr">
+        <is>
+          <t>电源 Power Supply</t>
+        </is>
+      </c>
       <c r="C228" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14582,27 +14586,27 @@
       </c>
       <c r="D228" s="38" t="inlineStr">
         <is>
-          <t>服务器电源</t>
+          <t>数据中心电源/UPS</t>
         </is>
       </c>
       <c r="E228" s="39" t="inlineStr">
         <is>
-          <t>欧陆通</t>
+          <t>中恒电气</t>
         </is>
       </c>
       <c r="F228" s="40" t="inlineStr">
         <is>
-          <t>300870.SZ</t>
+          <t>002364.SZ</t>
         </is>
       </c>
       <c r="G228" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H228" s="41" t="inlineStr">
         <is>
-          <t>服务器电源</t>
+          <t>数据中心电源</t>
         </is>
       </c>
       <c r="I228" s="42" t="inlineStr">
@@ -14610,9 +14614,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J228" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J228" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K228" s="13" t="inlineStr"/>
@@ -14621,24 +14625,16 @@
       <c r="N228" s="13" t="inlineStr"/>
       <c r="O228" s="13" t="inlineStr"/>
       <c r="P228" s="13" t="inlineStr"/>
-      <c r="Q228" s="14" t="inlineStr">
-        <is>
-          <t>增持</t>
-        </is>
-      </c>
+      <c r="Q228" s="13" t="inlineStr"/>
       <c r="R228" s="13" t="inlineStr"/>
-      <c r="S228" s="14" t="inlineStr">
-        <is>
-          <t>增持</t>
-        </is>
-      </c>
+      <c r="S228" s="13" t="inlineStr"/>
       <c r="T228" s="13" t="inlineStr"/>
       <c r="U228" s="13" t="inlineStr"/>
       <c r="V228" s="13" t="inlineStr"/>
     </row>
     <row r="229" ht="16" customHeight="1">
       <c r="A229" s="15" t="n"/>
-      <c r="B229" s="16" t="n"/>
+      <c r="B229" s="15" t="n"/>
       <c r="C229" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14646,17 +14642,17 @@
       </c>
       <c r="D229" s="38" t="inlineStr">
         <is>
-          <t>工业电源/服务器电源</t>
+          <t>UPS/储能电源</t>
         </is>
       </c>
       <c r="E229" s="39" t="inlineStr">
         <is>
-          <t>麦格米特</t>
+          <t>圣阳股份</t>
         </is>
       </c>
       <c r="F229" s="40" t="inlineStr">
         <is>
-          <t>002851.SZ</t>
+          <t>002580.SZ</t>
         </is>
       </c>
       <c r="G229" s="41" t="inlineStr">
@@ -14666,7 +14662,7 @@
       </c>
       <c r="H229" s="41" t="inlineStr">
         <is>
-          <t>工业电源/服务器电源</t>
+          <t>UPS/储能电源</t>
         </is>
       </c>
       <c r="I229" s="42" t="inlineStr">
@@ -14674,9 +14670,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J229" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J229" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K229" s="13" t="inlineStr"/>
@@ -14694,11 +14690,7 @@
     </row>
     <row r="230" ht="16" customHeight="1">
       <c r="A230" s="15" t="n"/>
-      <c r="B230" s="36" t="inlineStr">
-        <is>
-          <t>AIDC 数据中心</t>
-        </is>
-      </c>
+      <c r="B230" s="15" t="n"/>
       <c r="C230" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14706,27 +14698,27 @@
       </c>
       <c r="D230" s="38" t="inlineStr">
         <is>
-          <t>AI数据中心建设运营</t>
+          <t>服务器电源</t>
         </is>
       </c>
       <c r="E230" s="39" t="inlineStr">
         <is>
-          <t>润泽科技</t>
+          <t>欧陆通</t>
         </is>
       </c>
       <c r="F230" s="40" t="inlineStr">
         <is>
-          <t>300442.SZ</t>
+          <t>300870.SZ</t>
         </is>
       </c>
       <c r="G230" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H230" s="41" t="inlineStr">
         <is>
-          <t>AIDC建设运营</t>
+          <t>服务器电源</t>
         </is>
       </c>
       <c r="I230" s="42" t="inlineStr">
@@ -14734,9 +14726,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J230" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J230" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K230" s="13" t="inlineStr"/>
@@ -14745,16 +14737,24 @@
       <c r="N230" s="13" t="inlineStr"/>
       <c r="O230" s="13" t="inlineStr"/>
       <c r="P230" s="13" t="inlineStr"/>
-      <c r="Q230" s="13" t="inlineStr"/>
+      <c r="Q230" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="R230" s="13" t="inlineStr"/>
-      <c r="S230" s="13" t="inlineStr"/>
+      <c r="S230" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="T230" s="13" t="inlineStr"/>
       <c r="U230" s="13" t="inlineStr"/>
       <c r="V230" s="13" t="inlineStr"/>
     </row>
     <row r="231" ht="16" customHeight="1">
       <c r="A231" s="15" t="n"/>
-      <c r="B231" s="15" t="n"/>
+      <c r="B231" s="16" t="n"/>
       <c r="C231" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14762,27 +14762,27 @@
       </c>
       <c r="D231" s="38" t="inlineStr">
         <is>
-          <t>CDN/AIDC</t>
+          <t>工业电源/服务器电源</t>
         </is>
       </c>
       <c r="E231" s="39" t="inlineStr">
         <is>
-          <t>网宿科技</t>
+          <t>麦格米特</t>
         </is>
       </c>
       <c r="F231" s="40" t="inlineStr">
         <is>
-          <t>300017.SZ</t>
+          <t>002851.SZ</t>
         </is>
       </c>
       <c r="G231" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H231" s="41" t="inlineStr">
         <is>
-          <t>CDN/AIDC</t>
+          <t>工业电源/服务器电源</t>
         </is>
       </c>
       <c r="I231" s="42" t="inlineStr">
@@ -14790,9 +14790,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J231" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J231" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K231" s="13" t="inlineStr"/>
@@ -14810,7 +14810,11 @@
     </row>
     <row r="232" ht="16" customHeight="1">
       <c r="A232" s="15" t="n"/>
-      <c r="B232" s="15" t="n"/>
+      <c r="B232" s="36" t="inlineStr">
+        <is>
+          <t>AIDC 数据中心</t>
+        </is>
+      </c>
       <c r="C232" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14818,27 +14822,27 @@
       </c>
       <c r="D232" s="38" t="inlineStr">
         <is>
-          <t>IDC/AIDC</t>
+          <t>AI数据中心建设运营</t>
         </is>
       </c>
       <c r="E232" s="39" t="inlineStr">
         <is>
-          <t>光环新网</t>
+          <t>润泽科技</t>
         </is>
       </c>
       <c r="F232" s="40" t="inlineStr">
         <is>
-          <t>300383.SZ</t>
+          <t>300442.SZ</t>
         </is>
       </c>
       <c r="G232" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H232" s="41" t="inlineStr">
         <is>
-          <t>IDC/AIDC</t>
+          <t>AIDC建设运营</t>
         </is>
       </c>
       <c r="I232" s="42" t="inlineStr">
@@ -14846,9 +14850,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J232" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J232" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K232" s="13" t="inlineStr"/>
@@ -14866,7 +14870,7 @@
     </row>
     <row r="233" ht="16" customHeight="1">
       <c r="A233" s="15" t="n"/>
-      <c r="B233" s="16" t="n"/>
+      <c r="B233" s="15" t="n"/>
       <c r="C233" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14874,27 +14878,27 @@
       </c>
       <c r="D233" s="38" t="inlineStr">
         <is>
-          <t>IDC/AIDC建设运营</t>
+          <t>CDN/AIDC</t>
         </is>
       </c>
       <c r="E233" s="39" t="inlineStr">
         <is>
-          <t>数据港</t>
+          <t>网宿科技</t>
         </is>
       </c>
       <c r="F233" s="40" t="inlineStr">
         <is>
-          <t>603881.SH</t>
+          <t>300017.SZ</t>
         </is>
       </c>
       <c r="G233" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H233" s="41" t="inlineStr">
         <is>
-          <t>IDC/AIDC建设运营</t>
+          <t>CDN/AIDC</t>
         </is>
       </c>
       <c r="I233" s="42" t="inlineStr">
@@ -14902,9 +14906,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J233" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J233" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K233" s="13" t="inlineStr"/>
@@ -14922,11 +14926,7 @@
     </row>
     <row r="234" ht="16" customHeight="1">
       <c r="A234" s="15" t="n"/>
-      <c r="B234" s="36" t="inlineStr">
-        <is>
-          <t>算电协同</t>
-        </is>
-      </c>
+      <c r="B234" s="15" t="n"/>
       <c r="C234" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14934,27 +14934,27 @@
       </c>
       <c r="D234" s="38" t="inlineStr">
         <is>
-          <t>算力+电力协同，绿电支撑AI数据中心</t>
+          <t>IDC/AIDC</t>
         </is>
       </c>
       <c r="E234" s="39" t="inlineStr">
         <is>
-          <t>豫能控股</t>
+          <t>光环新网</t>
         </is>
       </c>
       <c r="F234" s="40" t="inlineStr">
         <is>
-          <t>001896.SZ</t>
+          <t>300383.SZ</t>
         </is>
       </c>
       <c r="G234" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H234" s="41" t="inlineStr">
         <is>
-          <t>电力/算力协同</t>
+          <t>IDC/AIDC</t>
         </is>
       </c>
       <c r="I234" s="42" t="inlineStr">
@@ -14962,9 +14962,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J234" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J234" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K234" s="13" t="inlineStr"/>
@@ -14982,7 +14982,7 @@
     </row>
     <row r="235" ht="16" customHeight="1">
       <c r="A235" s="15" t="n"/>
-      <c r="B235" s="15" t="n"/>
+      <c r="B235" s="16" t="n"/>
       <c r="C235" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14990,27 +14990,27 @@
       </c>
       <c r="D235" s="38" t="inlineStr">
         <is>
-          <t>绿电/算力协同</t>
+          <t>IDC/AIDC建设运营</t>
         </is>
       </c>
       <c r="E235" s="39" t="inlineStr">
         <is>
-          <t>协鑫能科</t>
+          <t>数据港</t>
         </is>
       </c>
       <c r="F235" s="40" t="inlineStr">
         <is>
-          <t>002015.SZ</t>
+          <t>603881.SH</t>
         </is>
       </c>
       <c r="G235" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H235" s="41" t="inlineStr">
         <is>
-          <t>绿电/算力协同</t>
+          <t>IDC/AIDC建设运营</t>
         </is>
       </c>
       <c r="I235" s="42" t="inlineStr">
@@ -15018,9 +15018,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J235" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J235" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K235" s="13" t="inlineStr"/>
@@ -15038,7 +15038,12 @@
     </row>
     <row r="236" ht="16" customHeight="1">
       <c r="A236" s="15" t="n"/>
-      <c r="B236" s="16" t="n"/>
+      <c r="B236" s="36" t="inlineStr">
+        <is>
+          <t>数据中心配电
+固态变压器</t>
+        </is>
+      </c>
       <c r="C236" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -15046,27 +15051,27 @@
       </c>
       <c r="D236" s="38" t="inlineStr">
         <is>
-          <t>绿电/数字能源</t>
+          <t>数字化固态变压器，SiC功率器件核心应用，AIDC配电关键</t>
         </is>
       </c>
       <c r="E236" s="39" t="inlineStr">
         <is>
-          <t>韶能股份</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="F236" s="40" t="inlineStr">
         <is>
-          <t>000601.SZ</t>
+          <t>601126.SH</t>
         </is>
       </c>
       <c r="G236" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H236" s="41" t="inlineStr">
         <is>
-          <t>绿电/数字能源</t>
+          <t>固态变压器/继电保护</t>
         </is>
       </c>
       <c r="I236" s="42" t="inlineStr">
@@ -15074,9 +15079,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J236" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J236" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K236" s="13" t="inlineStr"/>
@@ -15094,11 +15099,7 @@
     </row>
     <row r="237" ht="16" customHeight="1">
       <c r="A237" s="15" t="n"/>
-      <c r="B237" s="36" t="inlineStr">
-        <is>
-          <t>算力租赁</t>
-        </is>
-      </c>
+      <c r="B237" s="15" t="n"/>
       <c r="C237" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -15106,17 +15107,17 @@
       </c>
       <c r="D237" s="38" t="inlineStr">
         <is>
-          <t>GPU云算力租赁</t>
+          <t>高压开关设备/固态变压器</t>
         </is>
       </c>
       <c r="E237" s="39" t="inlineStr">
         <is>
-          <t>利通电子</t>
+          <t>中国西电</t>
         </is>
       </c>
       <c r="F237" s="40" t="inlineStr">
         <is>
-          <t>603629.SH</t>
+          <t>601179.SH</t>
         </is>
       </c>
       <c r="G237" s="41" t="inlineStr">
@@ -15126,7 +15127,7 @@
       </c>
       <c r="H237" s="41" t="inlineStr">
         <is>
-          <t>算力租赁/GPU云</t>
+          <t>高压开关/固态变压器</t>
         </is>
       </c>
       <c r="I237" s="42" t="inlineStr">
@@ -15134,9 +15135,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J237" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J237" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K237" s="13" t="inlineStr"/>
@@ -15162,27 +15163,27 @@
       </c>
       <c r="D238" s="38" t="inlineStr">
         <is>
-          <t>算力/数据中心租赁</t>
+          <t>电源变压器/固态变压器/磁性元件</t>
         </is>
       </c>
       <c r="E238" s="39" t="inlineStr">
         <is>
-          <t>协创数据</t>
+          <t>伊戈尔</t>
         </is>
       </c>
       <c r="F238" s="40" t="inlineStr">
         <is>
-          <t>300857.SZ</t>
+          <t>002922.SZ</t>
         </is>
       </c>
       <c r="G238" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H238" s="41" t="inlineStr">
         <is>
-          <t>算力/数据中心租赁</t>
+          <t>变压器/电源模块</t>
         </is>
       </c>
       <c r="I238" s="42" t="inlineStr">
@@ -15190,9 +15191,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J238" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J238" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K238" s="13" t="inlineStr"/>
@@ -15210,7 +15211,7 @@
     </row>
     <row r="239" ht="16" customHeight="1">
       <c r="A239" s="15" t="n"/>
-      <c r="B239" s="15" t="n"/>
+      <c r="B239" s="16" t="n"/>
       <c r="C239" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -15218,17 +15219,17 @@
       </c>
       <c r="D239" s="38" t="inlineStr">
         <is>
-          <t>算力云/GPU租赁</t>
+          <t>干式变压器/固态变压器，AIDC配电</t>
         </is>
       </c>
       <c r="E239" s="39" t="inlineStr">
         <is>
-          <t>优刻得</t>
+          <t>金盘科技</t>
         </is>
       </c>
       <c r="F239" s="40" t="inlineStr">
         <is>
-          <t>688158.SH</t>
+          <t>688676.SH</t>
         </is>
       </c>
       <c r="G239" s="41" t="inlineStr">
@@ -15238,7 +15239,7 @@
       </c>
       <c r="H239" s="41" t="inlineStr">
         <is>
-          <t>算力云/GPU租赁</t>
+          <t>干式/固态变压器</t>
         </is>
       </c>
       <c r="I239" s="42" t="inlineStr">
@@ -15246,9 +15247,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J239" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J239" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K239" s="13" t="inlineStr"/>
@@ -15265,8 +15266,12 @@
       <c r="V239" s="13" t="inlineStr"/>
     </row>
     <row r="240" ht="16" customHeight="1">
-      <c r="A240" s="16" t="n"/>
-      <c r="B240" s="16" t="n"/>
+      <c r="A240" s="15" t="n"/>
+      <c r="B240" s="36" t="inlineStr">
+        <is>
+          <t>算电协同</t>
+        </is>
+      </c>
       <c r="C240" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -15274,27 +15279,27 @@
       </c>
       <c r="D240" s="38" t="inlineStr">
         <is>
-          <t>算力租赁/AI云服务</t>
+          <t>算力+电力协同，绿电支撑AI数据中心</t>
         </is>
       </c>
       <c r="E240" s="39" t="inlineStr">
         <is>
-          <t>宏景科技</t>
+          <t>豫能控股</t>
         </is>
       </c>
       <c r="F240" s="40" t="inlineStr">
         <is>
-          <t>301396.SZ</t>
+          <t>001896.SZ</t>
         </is>
       </c>
       <c r="G240" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H240" s="41" t="inlineStr">
         <is>
-          <t>算力租赁/AI云服务</t>
+          <t>电力/算力协同</t>
         </is>
       </c>
       <c r="I240" s="42" t="inlineStr">
@@ -15302,9 +15307,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J240" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J240" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K240" s="13" t="inlineStr"/>
@@ -15320,35 +15325,374 @@
       <c r="U240" s="13" t="inlineStr"/>
       <c r="V240" s="13" t="inlineStr"/>
     </row>
+    <row r="241" ht="16" customHeight="1">
+      <c r="A241" s="15" t="n"/>
+      <c r="B241" s="15" t="n"/>
+      <c r="C241" s="37" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="D241" s="38" t="inlineStr">
+        <is>
+          <t>绿电/算力协同</t>
+        </is>
+      </c>
+      <c r="E241" s="39" t="inlineStr">
+        <is>
+          <t>协鑫能科</t>
+        </is>
+      </c>
+      <c r="F241" s="40" t="inlineStr">
+        <is>
+          <t>002015.SZ</t>
+        </is>
+      </c>
+      <c r="G241" s="41" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="H241" s="41" t="inlineStr">
+        <is>
+          <t>绿电/算力协同</t>
+        </is>
+      </c>
+      <c r="I241" s="42" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J241" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
+        </is>
+      </c>
+      <c r="K241" s="13" t="inlineStr"/>
+      <c r="L241" s="13" t="inlineStr"/>
+      <c r="M241" s="13" t="inlineStr"/>
+      <c r="N241" s="13" t="inlineStr"/>
+      <c r="O241" s="13" t="inlineStr"/>
+      <c r="P241" s="13" t="inlineStr"/>
+      <c r="Q241" s="13" t="inlineStr"/>
+      <c r="R241" s="13" t="inlineStr"/>
+      <c r="S241" s="13" t="inlineStr"/>
+      <c r="T241" s="13" t="inlineStr"/>
+      <c r="U241" s="13" t="inlineStr"/>
+      <c r="V241" s="13" t="inlineStr"/>
+    </row>
+    <row r="242" ht="16" customHeight="1">
+      <c r="A242" s="15" t="n"/>
+      <c r="B242" s="16" t="n"/>
+      <c r="C242" s="37" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="D242" s="38" t="inlineStr">
+        <is>
+          <t>绿电/数字能源</t>
+        </is>
+      </c>
+      <c r="E242" s="39" t="inlineStr">
+        <is>
+          <t>韶能股份</t>
+        </is>
+      </c>
+      <c r="F242" s="40" t="inlineStr">
+        <is>
+          <t>000601.SZ</t>
+        </is>
+      </c>
+      <c r="G242" s="41" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="H242" s="41" t="inlineStr">
+        <is>
+          <t>绿电/数字能源</t>
+        </is>
+      </c>
+      <c r="I242" s="42" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J242" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
+        </is>
+      </c>
+      <c r="K242" s="13" t="inlineStr"/>
+      <c r="L242" s="13" t="inlineStr"/>
+      <c r="M242" s="13" t="inlineStr"/>
+      <c r="N242" s="13" t="inlineStr"/>
+      <c r="O242" s="13" t="inlineStr"/>
+      <c r="P242" s="13" t="inlineStr"/>
+      <c r="Q242" s="13" t="inlineStr"/>
+      <c r="R242" s="13" t="inlineStr"/>
+      <c r="S242" s="13" t="inlineStr"/>
+      <c r="T242" s="13" t="inlineStr"/>
+      <c r="U242" s="13" t="inlineStr"/>
+      <c r="V242" s="13" t="inlineStr"/>
+    </row>
+    <row r="243" ht="16" customHeight="1">
+      <c r="A243" s="15" t="n"/>
+      <c r="B243" s="36" t="inlineStr">
+        <is>
+          <t>算力租赁</t>
+        </is>
+      </c>
+      <c r="C243" s="37" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="D243" s="38" t="inlineStr">
+        <is>
+          <t>GPU云算力租赁</t>
+        </is>
+      </c>
+      <c r="E243" s="39" t="inlineStr">
+        <is>
+          <t>利通电子</t>
+        </is>
+      </c>
+      <c r="F243" s="40" t="inlineStr">
+        <is>
+          <t>603629.SH</t>
+        </is>
+      </c>
+      <c r="G243" s="41" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="H243" s="41" t="inlineStr">
+        <is>
+          <t>算力租赁/GPU云</t>
+        </is>
+      </c>
+      <c r="I243" s="42" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J243" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
+        </is>
+      </c>
+      <c r="K243" s="13" t="inlineStr"/>
+      <c r="L243" s="13" t="inlineStr"/>
+      <c r="M243" s="13" t="inlineStr"/>
+      <c r="N243" s="13" t="inlineStr"/>
+      <c r="O243" s="13" t="inlineStr"/>
+      <c r="P243" s="13" t="inlineStr"/>
+      <c r="Q243" s="13" t="inlineStr"/>
+      <c r="R243" s="13" t="inlineStr"/>
+      <c r="S243" s="13" t="inlineStr"/>
+      <c r="T243" s="13" t="inlineStr"/>
+      <c r="U243" s="13" t="inlineStr"/>
+      <c r="V243" s="13" t="inlineStr"/>
+    </row>
+    <row r="244" ht="16" customHeight="1">
+      <c r="A244" s="15" t="n"/>
+      <c r="B244" s="15" t="n"/>
+      <c r="C244" s="37" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="D244" s="38" t="inlineStr">
+        <is>
+          <t>算力/数据中心租赁</t>
+        </is>
+      </c>
+      <c r="E244" s="39" t="inlineStr">
+        <is>
+          <t>协创数据</t>
+        </is>
+      </c>
+      <c r="F244" s="40" t="inlineStr">
+        <is>
+          <t>300857.SZ</t>
+        </is>
+      </c>
+      <c r="G244" s="41" t="inlineStr">
+        <is>
+          <t>深交所创业板</t>
+        </is>
+      </c>
+      <c r="H244" s="41" t="inlineStr">
+        <is>
+          <t>算力/数据中心租赁</t>
+        </is>
+      </c>
+      <c r="I244" s="42" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J244" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
+        </is>
+      </c>
+      <c r="K244" s="13" t="inlineStr"/>
+      <c r="L244" s="13" t="inlineStr"/>
+      <c r="M244" s="13" t="inlineStr"/>
+      <c r="N244" s="13" t="inlineStr"/>
+      <c r="O244" s="13" t="inlineStr"/>
+      <c r="P244" s="13" t="inlineStr"/>
+      <c r="Q244" s="13" t="inlineStr"/>
+      <c r="R244" s="13" t="inlineStr"/>
+      <c r="S244" s="13" t="inlineStr"/>
+      <c r="T244" s="13" t="inlineStr"/>
+      <c r="U244" s="13" t="inlineStr"/>
+      <c r="V244" s="13" t="inlineStr"/>
+    </row>
+    <row r="245" ht="16" customHeight="1">
+      <c r="A245" s="15" t="n"/>
+      <c r="B245" s="15" t="n"/>
+      <c r="C245" s="37" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="D245" s="38" t="inlineStr">
+        <is>
+          <t>算力云/GPU租赁</t>
+        </is>
+      </c>
+      <c r="E245" s="39" t="inlineStr">
+        <is>
+          <t>优刻得</t>
+        </is>
+      </c>
+      <c r="F245" s="40" t="inlineStr">
+        <is>
+          <t>688158.SH</t>
+        </is>
+      </c>
+      <c r="G245" s="41" t="inlineStr">
+        <is>
+          <t>上交所科创板</t>
+        </is>
+      </c>
+      <c r="H245" s="41" t="inlineStr">
+        <is>
+          <t>算力云/GPU租赁</t>
+        </is>
+      </c>
+      <c r="I245" s="42" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J245" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
+        </is>
+      </c>
+      <c r="K245" s="13" t="inlineStr"/>
+      <c r="L245" s="13" t="inlineStr"/>
+      <c r="M245" s="13" t="inlineStr"/>
+      <c r="N245" s="13" t="inlineStr"/>
+      <c r="O245" s="13" t="inlineStr"/>
+      <c r="P245" s="13" t="inlineStr"/>
+      <c r="Q245" s="13" t="inlineStr"/>
+      <c r="R245" s="13" t="inlineStr"/>
+      <c r="S245" s="13" t="inlineStr"/>
+      <c r="T245" s="13" t="inlineStr"/>
+      <c r="U245" s="13" t="inlineStr"/>
+      <c r="V245" s="13" t="inlineStr"/>
+    </row>
+    <row r="246" ht="16" customHeight="1">
+      <c r="A246" s="16" t="n"/>
+      <c r="B246" s="16" t="n"/>
+      <c r="C246" s="37" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="D246" s="38" t="inlineStr">
+        <is>
+          <t>算力租赁/AI云服务</t>
+        </is>
+      </c>
+      <c r="E246" s="39" t="inlineStr">
+        <is>
+          <t>宏景科技</t>
+        </is>
+      </c>
+      <c r="F246" s="40" t="inlineStr">
+        <is>
+          <t>301396.SZ</t>
+        </is>
+      </c>
+      <c r="G246" s="41" t="inlineStr">
+        <is>
+          <t>深交所创业板</t>
+        </is>
+      </c>
+      <c r="H246" s="41" t="inlineStr">
+        <is>
+          <t>算力租赁/AI云服务</t>
+        </is>
+      </c>
+      <c r="I246" s="42" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J246" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
+        </is>
+      </c>
+      <c r="K246" s="13" t="inlineStr"/>
+      <c r="L246" s="13" t="inlineStr"/>
+      <c r="M246" s="13" t="inlineStr"/>
+      <c r="N246" s="13" t="inlineStr"/>
+      <c r="O246" s="13" t="inlineStr"/>
+      <c r="P246" s="13" t="inlineStr"/>
+      <c r="Q246" s="13" t="inlineStr"/>
+      <c r="R246" s="13" t="inlineStr"/>
+      <c r="S246" s="13" t="inlineStr"/>
+      <c r="T246" s="13" t="inlineStr"/>
+      <c r="U246" s="13" t="inlineStr"/>
+      <c r="V246" s="13" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A3:V3"/>
-  <mergeCells count="70">
+  <mergeCells count="71">
     <mergeCell ref="A2:V2"/>
-    <mergeCell ref="B188:B193"/>
     <mergeCell ref="B78:B82"/>
-    <mergeCell ref="B184:B187"/>
+    <mergeCell ref="B236:B239"/>
     <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B213:B220"/>
     <mergeCell ref="B170:B171"/>
     <mergeCell ref="B59:B62"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="B108:B110"/>
     <mergeCell ref="B142:B144"/>
-    <mergeCell ref="A116:A175"/>
+    <mergeCell ref="B190:B195"/>
     <mergeCell ref="A27:A68"/>
     <mergeCell ref="B89:B91"/>
     <mergeCell ref="B129:B131"/>
     <mergeCell ref="B36:B38"/>
+    <mergeCell ref="A116:A177"/>
     <mergeCell ref="B157:B165"/>
-    <mergeCell ref="B180:B183"/>
-    <mergeCell ref="B234:B236"/>
+    <mergeCell ref="B232:B235"/>
     <mergeCell ref="B132:B133"/>
     <mergeCell ref="B139:B141"/>
-    <mergeCell ref="B219:B222"/>
-    <mergeCell ref="A176:A240"/>
-    <mergeCell ref="B198:B202"/>
+    <mergeCell ref="B228:B231"/>
+    <mergeCell ref="B182:B185"/>
     <mergeCell ref="B151:B156"/>
-    <mergeCell ref="B176:B179"/>
-    <mergeCell ref="B172:B175"/>
+    <mergeCell ref="B243:B246"/>
+    <mergeCell ref="B200:B204"/>
     <mergeCell ref="B119:B122"/>
     <mergeCell ref="B75:B77"/>
     <mergeCell ref="B166:B169"/>
@@ -15361,13 +15705,15 @@
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="B96:B98"/>
     <mergeCell ref="B69:B74"/>
-    <mergeCell ref="B194:B197"/>
-    <mergeCell ref="B223:B225"/>
+    <mergeCell ref="B178:B181"/>
+    <mergeCell ref="B196:B199"/>
+    <mergeCell ref="B205:B208"/>
     <mergeCell ref="B99:B100"/>
     <mergeCell ref="B134:B138"/>
     <mergeCell ref="B45:B53"/>
-    <mergeCell ref="B230:B233"/>
-    <mergeCell ref="B226:B229"/>
+    <mergeCell ref="A178:A246"/>
+    <mergeCell ref="B172:B177"/>
+    <mergeCell ref="B186:B189"/>
     <mergeCell ref="B15:B20"/>
     <mergeCell ref="B123:B124"/>
     <mergeCell ref="B92:B93"/>
@@ -15376,23 +15722,23 @@
     <mergeCell ref="B101:B103"/>
     <mergeCell ref="B111:B115"/>
     <mergeCell ref="B116:B118"/>
-    <mergeCell ref="B207:B210"/>
-    <mergeCell ref="B211:B218"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="A4:A20"/>
     <mergeCell ref="B148:B150"/>
     <mergeCell ref="A69:A95"/>
     <mergeCell ref="B55:B58"/>
-    <mergeCell ref="B237:B240"/>
+    <mergeCell ref="B240:B242"/>
     <mergeCell ref="B94:B95"/>
     <mergeCell ref="B104:B107"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="B9:B11"/>
+    <mergeCell ref="B225:B227"/>
+    <mergeCell ref="B209:B212"/>
     <mergeCell ref="B125:B126"/>
-    <mergeCell ref="B203:B206"/>
     <mergeCell ref="B85:B88"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="B63:B68"/>
+    <mergeCell ref="B221:B224"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15404,7 +15750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15629,169 +15975,2151 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="34" t="inlineStr">
-        <is>
-          <t>固态变压器</t>
-        </is>
-      </c>
-      <c r="B8" s="45" t="inlineStr">
-        <is>
-          <t>数字化固态变压器，AIDC配电核心</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>四方股份</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>601126.SH</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>固态变压器/继电保护</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="H8" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="15" t="n"/>
-      <c r="B9" s="45" t="inlineStr">
-        <is>
-          <t>高压开关设备/固态变压器</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>中国西电</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>601179.SH</t>
-        </is>
-      </c>
-      <c r="E9" s="10" t="inlineStr">
-        <is>
-          <t>上交所</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>高压开关/固态变压器</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="H9" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="15" t="n"/>
-      <c r="B10" s="45" t="inlineStr">
-        <is>
-          <t>电源变压器/固态变压器</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>伊戈尔</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>002922.SZ</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>变压器/电源模块</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="H10" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="16" t="n"/>
-      <c r="B11" s="45" t="inlineStr">
-        <is>
-          <t>干式变压器/固态变压器</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>金盘科技</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>688676.SH</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>上交所科创板</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>干式变压器/固态变压器</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="H11" s="46" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A8:A11"/>
+  <mergeCells count="3">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="48" t="inlineStr">
+        <is>
+          <t>其他科技标的  —  人形机器人 / 无人机 / 台湾半导体 / 全球AI平台 / 分销 / 面板等</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>此表标的与半导体工序无直接关联，涵盖机器人/自动化/台湾IC设计/全球半导体平台/元器件分销/面板显示等科技赛道</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>子类</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>公司名称</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>标的代码</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>市场</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>细分行业</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>币种</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>MS目标价</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>高盛目标价</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>摩根大通</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>UBS</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>美银/美林</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>巴克莱</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>人形机器人
+工业自动化</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>谐波减速器，人形机器人关节核心，国内垄断</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>绿的谐波</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>688017.SH</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>上交所科创板</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>谐波减速器</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr"/>
+      <c r="I4" s="13" t="inlineStr"/>
+      <c r="J4" s="13" t="inlineStr"/>
+      <c r="K4" s="13" t="inlineStr"/>
+      <c r="L4" s="13" t="inlineStr"/>
+      <c r="M4" s="13" t="inlineStr"/>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="15" t="n"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>微型传动/精密齿轮箱</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>兆威机电</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>003021.SZ</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>微型传动/精密齿轮</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H5" s="13" t="inlineStr"/>
+      <c r="I5" s="13" t="inlineStr"/>
+      <c r="J5" s="13" t="inlineStr"/>
+      <c r="K5" s="13" t="inlineStr"/>
+      <c r="L5" s="13" t="inlineStr"/>
+      <c r="M5" s="13" t="inlineStr"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="15" t="n"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>步进电机/伺服驱动系统</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>鸣志电器</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>603728.SH</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>步进/伺服电机</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr"/>
+      <c r="I6" s="13" t="inlineStr"/>
+      <c r="J6" s="13" t="inlineStr"/>
+      <c r="K6" s="13" t="inlineStr"/>
+      <c r="L6" s="13" t="inlineStr"/>
+      <c r="M6" s="13" t="inlineStr"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>3D视觉传感器/ToF，机器人感知</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>奥比中光</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>688322.SH</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>上交所科创板</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>3D视觉/ToF传感器</t>
+        </is>
+      </c>
+      <c r="G7" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H7" s="13" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr"/>
+      <c r="J7" s="13" t="inlineStr"/>
+      <c r="K7" s="13" t="inlineStr"/>
+      <c r="L7" s="13" t="inlineStr"/>
+      <c r="M7" s="13" t="inlineStr"/>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>谐波减速器全球龙头</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Harmonic Drive Systems</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>6324.T</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>东京证交所</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>谐波减速器</t>
+        </is>
+      </c>
+      <c r="G8" s="11" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr"/>
+      <c r="J8" s="13" t="inlineStr"/>
+      <c r="K8" s="13" t="inlineStr"/>
+      <c r="L8" s="13" t="inlineStr"/>
+      <c r="M8" s="13" t="inlineStr"/>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>热管理/流体控制，机器人/新能源车</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>三花智控</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>002050.SZ</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>热管理/流体控制</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr"/>
+      <c r="J9" s="13" t="inlineStr"/>
+      <c r="K9" s="13" t="inlineStr"/>
+      <c r="L9" s="13" t="inlineStr"/>
+      <c r="M9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>汽车/机器人结构件，特斯拉供应链</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>拓普集团</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>601689.SH</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>汽车/机器人部件</t>
+        </is>
+      </c>
+      <c r="G10" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr"/>
+      <c r="J10" s="13" t="inlineStr"/>
+      <c r="K10" s="13" t="inlineStr"/>
+      <c r="L10" s="13" t="inlineStr"/>
+      <c r="M10" s="13" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>工业机器人本体，国内龙头</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>埃斯顿</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>002747.SZ</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>工业机器人</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H11" s="13" t="inlineStr"/>
+      <c r="I11" s="13" t="inlineStr"/>
+      <c r="J11" s="13" t="inlineStr"/>
+      <c r="K11" s="13" t="inlineStr"/>
+      <c r="L11" s="13" t="inlineStr"/>
+      <c r="M11" s="13" t="inlineStr"/>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>工业自动化/PLC，全球前三</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Rockwell Automation</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>ROK</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>工业自动化/PLC</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr"/>
+      <c r="J12" s="13" t="inlineStr"/>
+      <c r="K12" s="13" t="inlineStr"/>
+      <c r="L12" s="13" t="inlineStr"/>
+      <c r="M12" s="13" t="inlineStr"/>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>工业机器人/电力/自动化，全球龙头</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>ABBNY</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>工业自动化/机器人</t>
+        </is>
+      </c>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H13" s="13" t="inlineStr"/>
+      <c r="I13" s="13" t="inlineStr"/>
+      <c r="J13" s="13" t="inlineStr"/>
+      <c r="K13" s="13" t="inlineStr"/>
+      <c r="L13" s="13" t="inlineStr"/>
+      <c r="M13" s="13" t="inlineStr"/>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>无人机
+自动驾驶感知</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>军/民用无人机整机，国产龙头</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>中无人机</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>688297.SH</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>上交所科创板</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>军/民用无人机</t>
+        </is>
+      </c>
+      <c r="G14" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr"/>
+      <c r="I14" s="13" t="inlineStr"/>
+      <c r="J14" s="13" t="inlineStr"/>
+      <c r="K14" s="13" t="inlineStr"/>
+      <c r="L14" s="13" t="inlineStr"/>
+      <c r="M14" s="13" t="inlineStr"/>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>工业/军用无人机</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>纵横股份</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>688070.SH</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>上交所科创板</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>工业/军用无人机</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H15" s="13" t="inlineStr"/>
+      <c r="I15" s="13" t="inlineStr"/>
+      <c r="J15" s="13" t="inlineStr"/>
+      <c r="K15" s="13" t="inlineStr"/>
+      <c r="L15" s="13" t="inlineStr"/>
+      <c r="M15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>飞控/惯导系统</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>星网宇达</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>002829.SZ</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>飞控/惯导系统</t>
+        </is>
+      </c>
+      <c r="G16" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr"/>
+      <c r="J16" s="13" t="inlineStr"/>
+      <c r="K16" s="13" t="inlineStr"/>
+      <c r="L16" s="13" t="inlineStr"/>
+      <c r="M16" s="13" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>军用无人机，美国防部供应商</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>AeroVironment</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>AVAV</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>军用无人机</t>
+        </is>
+      </c>
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H17" s="13" t="inlineStr"/>
+      <c r="I17" s="13" t="inlineStr"/>
+      <c r="J17" s="13" t="inlineStr"/>
+      <c r="K17" s="13" t="inlineStr"/>
+      <c r="L17" s="13" t="inlineStr"/>
+      <c r="M17" s="13" t="inlineStr"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>高精度GNSS/RTK定位，测绘无人机</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>华测导航</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>300627.SZ</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>深交所创业板</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>高精度GNSS/RTK</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr"/>
+      <c r="I18" s="13" t="inlineStr"/>
+      <c r="J18" s="13" t="inlineStr"/>
+      <c r="K18" s="13" t="inlineStr"/>
+      <c r="L18" s="13" t="inlineStr"/>
+      <c r="M18" s="13" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>高精地图/车联网</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>四维图新</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>002405.SZ</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>高精地图/车联网</t>
+        </is>
+      </c>
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr"/>
+      <c r="I19" s="13" t="inlineStr"/>
+      <c r="J19" s="13" t="inlineStr"/>
+      <c r="K19" s="13" t="inlineStr"/>
+      <c r="L19" s="13" t="inlineStr"/>
+      <c r="M19" s="13" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>固态激光雷达，自动驾驶感知</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Ouster</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>OUST</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>固态激光雷达</t>
+        </is>
+      </c>
+      <c r="G20" s="11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H20" s="13" t="inlineStr"/>
+      <c r="I20" s="13" t="inlineStr"/>
+      <c r="J20" s="13" t="inlineStr"/>
+      <c r="K20" s="13" t="inlineStr"/>
+      <c r="L20" s="13" t="inlineStr"/>
+      <c r="M20" s="13" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>自动驾驶视觉芯片/感知系统，Intel子公司</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Mobileye</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>MBLY</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>自动驾驶感知芯片</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>下调至中性,10</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr"/>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>中性,9</t>
+        </is>
+      </c>
+      <c r="K21" s="14" t="inlineStr">
+        <is>
+          <t>中性,10</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr"/>
+      <c r="M21" s="14" t="inlineStr">
+        <is>
+          <t>增持,14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>工控/自动化</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>变频器/伺服驱动/新能源，国内龙头</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>深圳汇川</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>300124.SZ</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>深交所创业板</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>变频器/伺服驱动</t>
+        </is>
+      </c>
+      <c r="G22" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr"/>
+      <c r="J22" s="13" t="inlineStr"/>
+      <c r="K22" s="13" t="inlineStr"/>
+      <c r="L22" s="13" t="inlineStr"/>
+      <c r="M22" s="13" t="inlineStr"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>DCS/工业控制系统，石化/化工核心</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>中控技术</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>688777.SH</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>上交所科创板</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>DCS/工业控制</t>
+        </is>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr"/>
+      <c r="J23" s="13" t="inlineStr"/>
+      <c r="K23" s="13" t="inlineStr"/>
+      <c r="L23" s="13" t="inlineStr"/>
+      <c r="M23" s="13" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>台湾
+半导体</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>无晶圆IC设计，手机SoC全球龙头，AI PC加速</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>联发科 MediaTek</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>2454.TW</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>台湾证交所</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>IC设计/移动SoC</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>增持首选</t>
+        </is>
+      </c>
+      <c r="I24" s="13" t="inlineStr"/>
+      <c r="J24" s="13" t="inlineStr"/>
+      <c r="K24" s="13" t="inlineStr"/>
+      <c r="L24" s="13" t="inlineStr"/>
+      <c r="M24" s="13" t="inlineStr"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>ASIC设计/CoWoS算力芯片，AI算力受益</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>世芯电子 Alchip</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>3661.TW</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>台湾证交所</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>ASIC设计/先进封装</t>
+        </is>
+      </c>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="13" t="inlineStr"/>
+      <c r="K25" s="13" t="inlineStr"/>
+      <c r="L25" s="13" t="inlineStr"/>
+      <c r="M25" s="13" t="inlineStr"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>RISC-V IP核授权，嵌入式处理器</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>晶心科技 Andes</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>6533.TW</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>台湾证交所</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>RISC-V IP核</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I26" s="13" t="inlineStr"/>
+      <c r="J26" s="13" t="inlineStr"/>
+      <c r="K26" s="13" t="inlineStr"/>
+      <c r="L26" s="13" t="inlineStr"/>
+      <c r="M26" s="13" t="inlineStr"/>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="15" t="n"/>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>12英寸硅片，全球前三大硅片厂</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>环球晶圆 GlobalWafers</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>3443.TW</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>台湾证交所</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>大硅片/外延片</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I27" s="13" t="inlineStr"/>
+      <c r="J27" s="13" t="inlineStr"/>
+      <c r="K27" s="13" t="inlineStr"/>
+      <c r="L27" s="13" t="inlineStr"/>
+      <c r="M27" s="13" t="inlineStr"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>NAND控制器IC，群联全球份额第一</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>群联电子 Phison</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>8299.TW</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>台湾证交所</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>NAND控制器IC</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I28" s="13" t="inlineStr"/>
+      <c r="J28" s="13" t="inlineStr"/>
+      <c r="K28" s="13" t="inlineStr"/>
+      <c r="L28" s="13" t="inlineStr"/>
+      <c r="M28" s="13" t="inlineStr"/>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="15" t="n"/>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>显示驱动IC，联咏全球前三</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>联咏科技 Novatek</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>3034.TW</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>台湾证交所</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>显示驱动IC</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I29" s="13" t="inlineStr"/>
+      <c r="J29" s="13" t="inlineStr"/>
+      <c r="K29" s="13" t="inlineStr"/>
+      <c r="L29" s="13" t="inlineStr"/>
+      <c r="M29" s="13" t="inlineStr"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>触控/指纹IC设计</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>义隆电子 Elan</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>2458.TW</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>台湾证交所</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>触控/指纹IC设计</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I30" s="13" t="inlineStr"/>
+      <c r="J30" s="13" t="inlineStr"/>
+      <c r="K30" s="13" t="inlineStr"/>
+      <c r="L30" s="13" t="inlineStr"/>
+      <c r="M30" s="13" t="inlineStr"/>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="15" t="n"/>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>以太网/光通信连接IC，AI数据中心互连</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>亚信科技 Asmedia</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>5269.TW</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>台湾证交所</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>IC设计/连接芯片</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I31" s="13" t="inlineStr"/>
+      <c r="J31" s="13" t="inlineStr"/>
+      <c r="K31" s="13" t="inlineStr"/>
+      <c r="L31" s="13" t="inlineStr"/>
+      <c r="M31" s="13" t="inlineStr"/>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="16" t="n"/>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>MCU/嵌入式控制器IC</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>新唐科技 Nuvoton</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>4919.TW</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>台湾证交所</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>MCU/嵌入式IC</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I32" s="13" t="inlineStr"/>
+      <c r="J32" s="13" t="inlineStr"/>
+      <c r="K32" s="13" t="inlineStr"/>
+      <c r="L32" s="13" t="inlineStr"/>
+      <c r="M32" s="13" t="inlineStr"/>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>全球半导体
+AI平台</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>GPU/AI加速器全球绝对垄断，H100/H200/B200</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>英伟达 NVIDIA</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>GPU/AI加速器</t>
+        </is>
+      </c>
+      <c r="G33" s="11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H33" s="13" t="inlineStr"/>
+      <c r="I33" s="13" t="inlineStr"/>
+      <c r="J33" s="13" t="inlineStr"/>
+      <c r="K33" s="13" t="inlineStr"/>
+      <c r="L33" s="13" t="inlineStr"/>
+      <c r="M33" s="13" t="inlineStr"/>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="15" t="n"/>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>AI芯片/视觉SoC，ADAS/边缘AI，Ambarella</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Ambarella</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>AMBA</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>AI视觉SoC/ADAS</t>
+        </is>
+      </c>
+      <c r="G34" s="11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I34" s="13" t="inlineStr"/>
+      <c r="J34" s="13" t="inlineStr"/>
+      <c r="K34" s="13" t="inlineStr"/>
+      <c r="L34" s="13" t="inlineStr"/>
+      <c r="M34" s="13" t="inlineStr"/>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="15" t="n"/>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>模拟/混合信号芯片，工业/汽车/通信</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>亚德诺 ADI</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>模拟/混合信号芯片</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I35" s="13" t="inlineStr"/>
+      <c r="J35" s="13" t="inlineStr"/>
+      <c r="K35" s="13" t="inlineStr"/>
+      <c r="L35" s="13" t="inlineStr"/>
+      <c r="M35" s="13" t="inlineStr"/>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="15" t="n"/>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>汽车/物联网芯片，NXP</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>恩智浦 NXP</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>NXPI</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>汽车/物联网芯片</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I36" s="13" t="inlineStr"/>
+      <c r="J36" s="13" t="inlineStr"/>
+      <c r="K36" s="13" t="inlineStr"/>
+      <c r="L36" s="13" t="inlineStr"/>
+      <c r="M36" s="13" t="inlineStr"/>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="15" t="n"/>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>射频/滤波器芯片，5G手机核心</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>科沃 Qorvo</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>QRVO</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>射频/滤波器芯片</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I37" s="13" t="inlineStr"/>
+      <c r="J37" s="13" t="inlineStr"/>
+      <c r="K37" s="13" t="inlineStr"/>
+      <c r="L37" s="13" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="M37" s="14" t="inlineStr">
+        <is>
+          <t>增持,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="15" t="n"/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>物联网/WiFi/BT芯片，乐鑫</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>乐鑫科技</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>688018.SH</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>上交所科创板</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>物联网/WiFi芯片</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I38" s="13" t="inlineStr"/>
+      <c r="J38" s="13" t="inlineStr"/>
+      <c r="K38" s="13" t="inlineStr"/>
+      <c r="L38" s="13" t="inlineStr"/>
+      <c r="M38" s="13" t="inlineStr"/>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="16" t="n"/>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>电动汽车/机器人/AI全栈，特斯拉</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>特斯拉 Tesla</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>EV/AI/机器人</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H39" s="13" t="inlineStr"/>
+      <c r="I39" s="13" t="inlineStr"/>
+      <c r="J39" s="13" t="inlineStr"/>
+      <c r="K39" s="13" t="inlineStr"/>
+      <c r="L39" s="13" t="inlineStr"/>
+      <c r="M39" s="13" t="inlineStr"/>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="34" t="inlineStr">
+        <is>
+          <t>半导体
+分销/封测</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>半导体元器件分销，国内龙头</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>中电港</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>001287.SZ</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>半导体元器件分销</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H40" s="13" t="inlineStr"/>
+      <c r="I40" s="13" t="inlineStr"/>
+      <c r="J40" s="13" t="inlineStr"/>
+      <c r="K40" s="13" t="inlineStr"/>
+      <c r="L40" s="13" t="inlineStr"/>
+      <c r="M40" s="13" t="inlineStr"/>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="15" t="n"/>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>半导体/电子元器件分销</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>力源信息</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>300184.SZ</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>深交所创业板</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>半导体元器件分销</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H41" s="13" t="inlineStr"/>
+      <c r="I41" s="13" t="inlineStr"/>
+      <c r="J41" s="13" t="inlineStr"/>
+      <c r="K41" s="13" t="inlineStr"/>
+      <c r="L41" s="13" t="inlineStr"/>
+      <c r="M41" s="13" t="inlineStr"/>
+    </row>
+    <row r="42" ht="16" customHeight="1">
+      <c r="A42" s="15" t="n"/>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>半导体元器件分销/智能硬件</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>商络电子</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>300975.SZ</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>深交所创业板</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>半导体元器件分销</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H42" s="13" t="inlineStr"/>
+      <c r="I42" s="13" t="inlineStr"/>
+      <c r="J42" s="13" t="inlineStr"/>
+      <c r="K42" s="13" t="inlineStr"/>
+      <c r="L42" s="13" t="inlineStr"/>
+      <c r="M42" s="13" t="inlineStr"/>
+    </row>
+    <row r="43" ht="16" customHeight="1">
+      <c r="A43" s="16" t="n"/>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>闪存/存储产品，U盘/SSD品牌</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>朗科科技</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>300042.SZ</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>深交所创业板</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>存储产品/闪存</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H43" s="13" t="inlineStr"/>
+      <c r="I43" s="13" t="inlineStr"/>
+      <c r="J43" s="13" t="inlineStr"/>
+      <c r="K43" s="13" t="inlineStr"/>
+      <c r="L43" s="13" t="inlineStr"/>
+      <c r="M43" s="13" t="inlineStr"/>
+    </row>
+    <row r="44" ht="16" customHeight="1">
+      <c r="A44" s="30" t="inlineStr">
+        <is>
+          <t>面板/显示
+其他科技</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>全球最大面板厂，京东方</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>京东方A</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>000725.SZ</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>面板/显示器件</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H44" s="13" t="inlineStr"/>
+      <c r="I44" s="13" t="inlineStr"/>
+      <c r="J44" s="13" t="inlineStr"/>
+      <c r="K44" s="13" t="inlineStr"/>
+      <c r="L44" s="13" t="inlineStr"/>
+      <c r="M44" s="13" t="inlineStr"/>
+    </row>
+    <row r="45" ht="16" customHeight="1">
+      <c r="A45" s="15" t="n"/>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>中小尺寸显示屏，深天马</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>深天马A</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>000050.SZ</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>中小尺寸显示屏</t>
+        </is>
+      </c>
+      <c r="G45" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H45" s="13" t="inlineStr"/>
+      <c r="I45" s="13" t="inlineStr"/>
+      <c r="J45" s="13" t="inlineStr"/>
+      <c r="K45" s="13" t="inlineStr"/>
+      <c r="L45" s="13" t="inlineStr"/>
+      <c r="M45" s="13" t="inlineStr"/>
+    </row>
+    <row r="46" ht="16" customHeight="1">
+      <c r="A46" s="15" t="n"/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>超薄玻璃/光学薄膜，AMOLED基板</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>沃格光电</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>603773.SH</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>超薄玻璃/光学薄膜</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H46" s="13" t="inlineStr"/>
+      <c r="I46" s="13" t="inlineStr"/>
+      <c r="J46" s="13" t="inlineStr"/>
+      <c r="K46" s="13" t="inlineStr"/>
+      <c r="L46" s="13" t="inlineStr"/>
+      <c r="M46" s="13" t="inlineStr"/>
+    </row>
+    <row r="47" ht="16" customHeight="1">
+      <c r="A47" s="15" t="n"/>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>玻纤/电子布，日本龙头</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>日东纺织 Nitto Boseki</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>3110.T</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>东京证交所</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>玻纤/电子布</t>
+        </is>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I47" s="13" t="inlineStr"/>
+      <c r="J47" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr"/>
+      <c r="L47" s="13" t="inlineStr"/>
+      <c r="M47" s="13" t="inlineStr"/>
+    </row>
+    <row r="48" ht="16" customHeight="1">
+      <c r="A48" s="15" t="n"/>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>特种玻璃/光纤/显示器基板，全球龙头</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>康宁 Corning</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>GLW</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>NYSE</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>特种玻璃/光纤</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I48" s="13" t="inlineStr"/>
+      <c r="J48" s="13" t="inlineStr"/>
+      <c r="K48" s="13" t="inlineStr"/>
+      <c r="L48" s="13" t="inlineStr"/>
+      <c r="M48" s="13" t="inlineStr"/>
+    </row>
+    <row r="49" ht="16" customHeight="1">
+      <c r="A49" s="15" t="n"/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>碳纤维/高性能复合材料，航空航天</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>光威复材</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>300699.SZ</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>深交所创业板</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>碳纤维/复合材料</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H49" s="13" t="inlineStr"/>
+      <c r="I49" s="13" t="inlineStr"/>
+      <c r="J49" s="13" t="inlineStr"/>
+      <c r="K49" s="13" t="inlineStr"/>
+      <c r="L49" s="13" t="inlineStr"/>
+      <c r="M49" s="13" t="inlineStr"/>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="15" t="n"/>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>台达电子，电源/散热/自动化，AI服务器配套</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Delta Electronics 台达</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>2308.TW</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>台湾证交所</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>电源/散热/自动化</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="I50" s="13" t="inlineStr"/>
+      <c r="J50" s="13" t="inlineStr"/>
+      <c r="K50" s="13" t="inlineStr"/>
+      <c r="L50" s="13" t="inlineStr"/>
+      <c r="M50" s="13" t="inlineStr"/>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="16" t="n"/>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>汽车结构件/电池托盘，震裕</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>震裕科技</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>300953.SZ</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>深交所创业板</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>汽车结构件/电池托盘</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H51" s="13" t="inlineStr"/>
+      <c r="I51" s="13" t="inlineStr"/>
+      <c r="J51" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="K51" s="13" t="inlineStr"/>
+      <c r="L51" s="13" t="inlineStr"/>
+      <c r="M51" s="13" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A44:A51"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A32"/>
+    <mergeCell ref="A33:A39"/>
+    <mergeCell ref="A4:A13"/>
+    <mergeCell ref="A14:A21"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A40:A43"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/半导体全产业链标的.xlsx
+++ b/半导体全产业链标的.xlsx
@@ -830,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V246"/>
+  <dimension ref="A1:V247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -15610,8 +15610,8 @@
       <c r="V245" s="13" t="inlineStr"/>
     </row>
     <row r="246" ht="16" customHeight="1">
-      <c r="A246" s="16" t="n"/>
-      <c r="B246" s="16" t="n"/>
+      <c r="A246" s="15" t="n"/>
+      <c r="B246" s="15" t="n"/>
       <c r="C246" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -15664,6 +15664,62 @@
       <c r="T246" s="13" t="inlineStr"/>
       <c r="U246" s="13" t="inlineStr"/>
       <c r="V246" s="13" t="inlineStr"/>
+    </row>
+    <row r="247" ht="16" customHeight="1">
+      <c r="A247" s="16" t="n"/>
+      <c r="B247" s="16" t="n"/>
+      <c r="C247" s="37" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="D247" s="38" t="inlineStr">
+        <is>
+          <t>GPU云算力租赁，欧洲最大AI基础设施云平台，从Yandex拆分上市</t>
+        </is>
+      </c>
+      <c r="E247" s="39" t="inlineStr">
+        <is>
+          <t>Nebius Group</t>
+        </is>
+      </c>
+      <c r="F247" s="40" t="inlineStr">
+        <is>
+          <t>NBIS</t>
+        </is>
+      </c>
+      <c r="G247" s="41" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="H247" s="41" t="inlineStr">
+        <is>
+          <t>GPU云/AI基础设施租赁</t>
+        </is>
+      </c>
+      <c r="I247" s="42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J247" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K247" s="13" t="inlineStr"/>
+      <c r="L247" s="13" t="inlineStr"/>
+      <c r="M247" s="13" t="inlineStr"/>
+      <c r="N247" s="13" t="inlineStr"/>
+      <c r="O247" s="13" t="inlineStr"/>
+      <c r="P247" s="13" t="inlineStr"/>
+      <c r="Q247" s="13" t="inlineStr"/>
+      <c r="R247" s="13" t="inlineStr"/>
+      <c r="S247" s="13" t="inlineStr"/>
+      <c r="T247" s="13" t="inlineStr"/>
+      <c r="U247" s="13" t="inlineStr"/>
+      <c r="V247" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:V3"/>
@@ -15689,9 +15745,9 @@
     <mergeCell ref="B132:B133"/>
     <mergeCell ref="B139:B141"/>
     <mergeCell ref="B228:B231"/>
+    <mergeCell ref="A178:A247"/>
     <mergeCell ref="B182:B185"/>
     <mergeCell ref="B151:B156"/>
-    <mergeCell ref="B243:B246"/>
     <mergeCell ref="B200:B204"/>
     <mergeCell ref="B119:B122"/>
     <mergeCell ref="B75:B77"/>
@@ -15711,7 +15767,6 @@
     <mergeCell ref="B99:B100"/>
     <mergeCell ref="B134:B138"/>
     <mergeCell ref="B45:B53"/>
-    <mergeCell ref="A178:A246"/>
     <mergeCell ref="B172:B177"/>
     <mergeCell ref="B186:B189"/>
     <mergeCell ref="B15:B20"/>
@@ -15736,6 +15791,7 @@
     <mergeCell ref="B209:B212"/>
     <mergeCell ref="B125:B126"/>
     <mergeCell ref="B85:B88"/>
+    <mergeCell ref="B243:B247"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="B63:B68"/>
     <mergeCell ref="B221:B224"/>

--- a/半导体全产业链标的.xlsx
+++ b/半导体全产业链标的.xlsx
@@ -830,7 +830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V247"/>
+  <dimension ref="A1:V253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10075,7 +10075,7 @@
       <c r="A151" s="15" t="n"/>
       <c r="B151" s="17" t="inlineStr">
         <is>
-          <t>MLCC电容</t>
+          <t>铝电解电容</t>
         </is>
       </c>
       <c r="C151" s="17" t="inlineStr">
@@ -10085,27 +10085,27 @@
       </c>
       <c r="D151" s="18" t="inlineStr">
         <is>
-          <t>电子工业大米，今年涨幅&gt;50%，全球供应缺口明显</t>
+          <t>铝电解电容用化成箔/腐蚀箔龙头，AI服务器电源/UPS核心材料</t>
         </is>
       </c>
       <c r="E151" s="19" t="inlineStr">
         <is>
-          <t>风华高科</t>
+          <t>东阳光</t>
         </is>
       </c>
       <c r="F151" s="20" t="inlineStr">
         <is>
-          <t>000636.SZ</t>
+          <t>600673.SH</t>
         </is>
       </c>
       <c r="G151" s="21" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H151" s="21" t="inlineStr">
         <is>
-          <t>MLCC/片式电容</t>
+          <t>铝箔/化成箔/腐蚀箔</t>
         </is>
       </c>
       <c r="I151" s="22" t="inlineStr">
@@ -10133,7 +10133,7 @@
     </row>
     <row r="152" ht="16" customHeight="1">
       <c r="A152" s="15" t="n"/>
-      <c r="B152" s="15" t="n"/>
+      <c r="B152" s="16" t="n"/>
       <c r="C152" s="17" t="inlineStr">
         <is>
           <t>材料</t>
@@ -10141,27 +10141,27 @@
       </c>
       <c r="D152" s="18" t="inlineStr">
         <is>
-          <t>MLCC/电子陶瓷</t>
+          <t>铝电解电容龙头，AI服务器电源/UPS大容量储能刚需</t>
         </is>
       </c>
       <c r="E152" s="19" t="inlineStr">
         <is>
-          <t>三环集团</t>
+          <t>江海股份</t>
         </is>
       </c>
       <c r="F152" s="20" t="inlineStr">
         <is>
-          <t>300408.SZ</t>
+          <t>002484.SZ</t>
         </is>
       </c>
       <c r="G152" s="21" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H152" s="21" t="inlineStr">
         <is>
-          <t>MLCC/电子陶瓷</t>
+          <t>铝电解电容</t>
         </is>
       </c>
       <c r="I152" s="22" t="inlineStr">
@@ -10189,7 +10189,11 @@
     </row>
     <row r="153" ht="16" customHeight="1">
       <c r="A153" s="15" t="n"/>
-      <c r="B153" s="15" t="n"/>
+      <c r="B153" s="17" t="inlineStr">
+        <is>
+          <t>超级电容器</t>
+        </is>
+      </c>
       <c r="C153" s="17" t="inlineStr">
         <is>
           <t>材料</t>
@@ -10197,27 +10201,27 @@
       </c>
       <c r="D153" s="18" t="inlineStr">
         <is>
-          <t>MLCC载带/隔离纸</t>
+          <t>超级电容器电极用活性炭/电容炭，EDLC核心材料，AI服务器瞬态功率缓冲与数据中心UPS替代铅酸电池</t>
         </is>
       </c>
       <c r="E153" s="19" t="inlineStr">
         <is>
-          <t>洁美科技</t>
+          <t>元力股份</t>
         </is>
       </c>
       <c r="F153" s="20" t="inlineStr">
         <is>
-          <t>002859.SZ</t>
+          <t>300164.SZ</t>
         </is>
       </c>
       <c r="G153" s="21" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H153" s="21" t="inlineStr">
         <is>
-          <t>MLCC载带/隔离纸</t>
+          <t>电容炭/活性炭</t>
         </is>
       </c>
       <c r="I153" s="22" t="inlineStr">
@@ -10245,7 +10249,11 @@
     </row>
     <row r="154" ht="16" customHeight="1">
       <c r="A154" s="15" t="n"/>
-      <c r="B154" s="15" t="n"/>
+      <c r="B154" s="17" t="inlineStr">
+        <is>
+          <t>MLCC电容</t>
+        </is>
+      </c>
       <c r="C154" s="17" t="inlineStr">
         <is>
           <t>材料</t>
@@ -10253,27 +10261,27 @@
       </c>
       <c r="D154" s="18" t="inlineStr">
         <is>
-          <t>军工/高可靠MLCC</t>
+          <t>电子工业大米，今年涨幅&gt;50%，全球供应缺口明显</t>
         </is>
       </c>
       <c r="E154" s="19" t="inlineStr">
         <is>
-          <t>鸿远电子</t>
+          <t>风华高科</t>
         </is>
       </c>
       <c r="F154" s="20" t="inlineStr">
         <is>
-          <t>603267.SH</t>
+          <t>000636.SZ</t>
         </is>
       </c>
       <c r="G154" s="21" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H154" s="21" t="inlineStr">
         <is>
-          <t>军工/高可靠MLCC</t>
+          <t>MLCC/片式电容</t>
         </is>
       </c>
       <c r="I154" s="22" t="inlineStr">
@@ -10309,17 +10317,17 @@
       </c>
       <c r="D155" s="18" t="inlineStr">
         <is>
-          <t>MLCC陶瓷粉/介质材料</t>
+          <t>MLCC/电子陶瓷</t>
         </is>
       </c>
       <c r="E155" s="19" t="inlineStr">
         <is>
-          <t>国瓷材料</t>
+          <t>三环集团</t>
         </is>
       </c>
       <c r="F155" s="20" t="inlineStr">
         <is>
-          <t>300285.SZ</t>
+          <t>300408.SZ</t>
         </is>
       </c>
       <c r="G155" s="21" t="inlineStr">
@@ -10329,7 +10337,7 @@
       </c>
       <c r="H155" s="21" t="inlineStr">
         <is>
-          <t>MLCC陶瓷粉/介质</t>
+          <t>MLCC/电子陶瓷</t>
         </is>
       </c>
       <c r="I155" s="22" t="inlineStr">
@@ -10357,7 +10365,7 @@
     </row>
     <row r="156" ht="16" customHeight="1">
       <c r="A156" s="15" t="n"/>
-      <c r="B156" s="16" t="n"/>
+      <c r="B156" s="15" t="n"/>
       <c r="C156" s="17" t="inlineStr">
         <is>
           <t>材料</t>
@@ -10365,37 +10373,37 @@
       </c>
       <c r="D156" s="18" t="inlineStr">
         <is>
-          <t>全球MLCC龙头，被动元件</t>
+          <t>MLCC载带/隔离纸</t>
         </is>
       </c>
       <c r="E156" s="19" t="inlineStr">
         <is>
-          <t>村田制作所 Murata</t>
+          <t>洁美科技</t>
         </is>
       </c>
       <c r="F156" s="20" t="inlineStr">
         <is>
-          <t>6981.T</t>
+          <t>002859.SZ</t>
         </is>
       </c>
       <c r="G156" s="21" t="inlineStr">
         <is>
-          <t>东京证交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H156" s="21" t="inlineStr">
         <is>
-          <t>MLCC/被动元件</t>
+          <t>MLCC载带/隔离纸</t>
         </is>
       </c>
       <c r="I156" s="22" t="inlineStr">
         <is>
-          <t>JPY</t>
-        </is>
-      </c>
-      <c r="J156" s="12" t="inlineStr">
-        <is>
-          <t>★</t>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J156" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K156" s="13" t="inlineStr"/>
@@ -10413,11 +10421,7 @@
     </row>
     <row r="157" ht="16" customHeight="1">
       <c r="A157" s="15" t="n"/>
-      <c r="B157" s="17" t="inlineStr">
-        <is>
-          <t>铜箔/电子布</t>
-        </is>
-      </c>
+      <c r="B157" s="15" t="n"/>
       <c r="C157" s="17" t="inlineStr">
         <is>
           <t>材料</t>
@@ -10425,27 +10429,27 @@
       </c>
       <c r="D157" s="18" t="inlineStr">
         <is>
-          <t>锂电负极/PCB覆铜板材料，今年价格翻倍</t>
+          <t>军工/高可靠MLCC</t>
         </is>
       </c>
       <c r="E157" s="19" t="inlineStr">
         <is>
-          <t>铜冠铜箔</t>
+          <t>鸿远电子</t>
         </is>
       </c>
       <c r="F157" s="20" t="inlineStr">
         <is>
-          <t>301217.SZ</t>
+          <t>603267.SH</t>
         </is>
       </c>
       <c r="G157" s="21" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H157" s="21" t="inlineStr">
         <is>
-          <t>电解铜箔</t>
+          <t>军工/高可靠MLCC</t>
         </is>
       </c>
       <c r="I157" s="22" t="inlineStr">
@@ -10481,27 +10485,27 @@
       </c>
       <c r="D158" s="18" t="inlineStr">
         <is>
-          <t>高端电解铜箔</t>
+          <t>MLCC陶瓷粉/介质材料</t>
         </is>
       </c>
       <c r="E158" s="19" t="inlineStr">
         <is>
-          <t>嘉元科技</t>
+          <t>国瓷材料</t>
         </is>
       </c>
       <c r="F158" s="20" t="inlineStr">
         <is>
-          <t>688388.SH</t>
+          <t>300285.SZ</t>
         </is>
       </c>
       <c r="G158" s="21" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H158" s="21" t="inlineStr">
         <is>
-          <t>高端电解铜箔</t>
+          <t>MLCC陶瓷粉/介质</t>
         </is>
       </c>
       <c r="I158" s="22" t="inlineStr">
@@ -10537,37 +10541,37 @@
       </c>
       <c r="D159" s="18" t="inlineStr">
         <is>
-          <t>电解铜箔/锂电铜箔</t>
+          <t>全球MLCC龙头，被动元件</t>
         </is>
       </c>
       <c r="E159" s="19" t="inlineStr">
         <is>
-          <t>诺德股份</t>
+          <t>村田制作所 Murata</t>
         </is>
       </c>
       <c r="F159" s="20" t="inlineStr">
         <is>
-          <t>600110.SH</t>
+          <t>6981.T</t>
         </is>
       </c>
       <c r="G159" s="21" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>东京证交所</t>
         </is>
       </c>
       <c r="H159" s="21" t="inlineStr">
         <is>
-          <t>电解铜箔</t>
+          <t>MLCC/被动元件</t>
         </is>
       </c>
       <c r="I159" s="22" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="J159" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>JPY</t>
+        </is>
+      </c>
+      <c r="J159" s="12" t="inlineStr">
+        <is>
+          <t>★</t>
         </is>
       </c>
       <c r="K159" s="13" t="inlineStr"/>
@@ -10585,7 +10589,7 @@
     </row>
     <row r="160" ht="16" customHeight="1">
       <c r="A160" s="15" t="n"/>
-      <c r="B160" s="15" t="n"/>
+      <c r="B160" s="16" t="n"/>
       <c r="C160" s="17" t="inlineStr">
         <is>
           <t>材料</t>
@@ -10593,27 +10597,27 @@
       </c>
       <c r="D160" s="18" t="inlineStr">
         <is>
-          <t>高端超薄铜箔，AI服务器PCB用</t>
+          <t>MLCC内电极超细镍粉龙头，国产替代MLCC上游核心材料</t>
         </is>
       </c>
       <c r="E160" s="19" t="inlineStr">
         <is>
-          <t>中一科技</t>
+          <t>博迁新材</t>
         </is>
       </c>
       <c r="F160" s="20" t="inlineStr">
         <is>
-          <t>003031.SZ</t>
+          <t>605376.SH</t>
         </is>
       </c>
       <c r="G160" s="21" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H160" s="21" t="inlineStr">
         <is>
-          <t>高端超薄铜箔</t>
+          <t>MLCC内电极镍粉</t>
         </is>
       </c>
       <c r="I160" s="22" t="inlineStr">
@@ -10641,7 +10645,11 @@
     </row>
     <row r="161" ht="16" customHeight="1">
       <c r="A161" s="15" t="n"/>
-      <c r="B161" s="15" t="n"/>
+      <c r="B161" s="17" t="inlineStr">
+        <is>
+          <t>软磁材料/电感</t>
+        </is>
+      </c>
       <c r="C161" s="17" t="inlineStr">
         <is>
           <t>材料</t>
@@ -10649,17 +10657,17 @@
       </c>
       <c r="D161" s="18" t="inlineStr">
         <is>
-          <t>高精铜箔/压延铜箔</t>
+          <t>金属软磁粉芯国内龙头，AI服务器功率电感核心上游材料</t>
         </is>
       </c>
       <c r="E161" s="19" t="inlineStr">
         <is>
-          <t>德福科技</t>
+          <t>铂科新材</t>
         </is>
       </c>
       <c r="F161" s="20" t="inlineStr">
         <is>
-          <t>301511.SZ</t>
+          <t>300811.SZ</t>
         </is>
       </c>
       <c r="G161" s="21" t="inlineStr">
@@ -10669,7 +10677,7 @@
       </c>
       <c r="H161" s="21" t="inlineStr">
         <is>
-          <t>高精铜箔</t>
+          <t>金属软磁粉芯</t>
         </is>
       </c>
       <c r="I161" s="22" t="inlineStr">
@@ -10697,7 +10705,7 @@
     </row>
     <row r="162" ht="16" customHeight="1">
       <c r="A162" s="15" t="n"/>
-      <c r="B162" s="15" t="n"/>
+      <c r="B162" s="16" t="n"/>
       <c r="C162" s="17" t="inlineStr">
         <is>
           <t>材料</t>
@@ -10705,27 +10713,27 @@
       </c>
       <c r="D162" s="18" t="inlineStr">
         <is>
-          <t>覆铜板关键增强材料，高端电子布价格翻倍，缺货至2028</t>
+          <t>片式叠层电感/磁珠国内龙头，5G/AI服务器被动元件核心</t>
         </is>
       </c>
       <c r="E162" s="19" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>顺络电子</t>
         </is>
       </c>
       <c r="F162" s="20" t="inlineStr">
         <is>
-          <t>600176.SH</t>
+          <t>002138.SZ</t>
         </is>
       </c>
       <c r="G162" s="21" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H162" s="21" t="inlineStr">
         <is>
-          <t>玻纤/电子布</t>
+          <t>片式电感/磁珠</t>
         </is>
       </c>
       <c r="I162" s="22" t="inlineStr">
@@ -10753,7 +10761,11 @@
     </row>
     <row r="163" ht="16" customHeight="1">
       <c r="A163" s="15" t="n"/>
-      <c r="B163" s="15" t="n"/>
+      <c r="B163" s="17" t="inlineStr">
+        <is>
+          <t>铜箔/电子布</t>
+        </is>
+      </c>
       <c r="C163" s="17" t="inlineStr">
         <is>
           <t>材料</t>
@@ -10761,27 +10773,27 @@
       </c>
       <c r="D163" s="18" t="inlineStr">
         <is>
-          <t>高端电子布</t>
+          <t>锂电负极/PCB覆铜板材料，今年价格翻倍</t>
         </is>
       </c>
       <c r="E163" s="19" t="inlineStr">
         <is>
-          <t>宏和科技</t>
+          <t>铜冠铜箔</t>
         </is>
       </c>
       <c r="F163" s="20" t="inlineStr">
         <is>
-          <t>603256.SH</t>
+          <t>301217.SZ</t>
         </is>
       </c>
       <c r="G163" s="21" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H163" s="21" t="inlineStr">
         <is>
-          <t>高端电子布</t>
+          <t>电解铜箔</t>
         </is>
       </c>
       <c r="I163" s="22" t="inlineStr">
@@ -10817,27 +10829,27 @@
       </c>
       <c r="D164" s="18" t="inlineStr">
         <is>
-          <t>玻纤/复合材料</t>
+          <t>高端电解铜箔</t>
         </is>
       </c>
       <c r="E164" s="19" t="inlineStr">
         <is>
-          <t>中材科技</t>
+          <t>嘉元科技</t>
         </is>
       </c>
       <c r="F164" s="20" t="inlineStr">
         <is>
-          <t>002080.SZ</t>
+          <t>688388.SH</t>
         </is>
       </c>
       <c r="G164" s="21" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H164" s="21" t="inlineStr">
         <is>
-          <t>玻纤/复合材料</t>
+          <t>高端电解铜箔</t>
         </is>
       </c>
       <c r="I164" s="22" t="inlineStr">
@@ -10856,24 +10868,16 @@
       <c r="N164" s="13" t="inlineStr"/>
       <c r="O164" s="13" t="inlineStr"/>
       <c r="P164" s="13" t="inlineStr"/>
-      <c r="Q164" s="14" t="inlineStr">
-        <is>
-          <t>增持</t>
-        </is>
-      </c>
+      <c r="Q164" s="13" t="inlineStr"/>
       <c r="R164" s="13" t="inlineStr"/>
-      <c r="S164" s="14" t="inlineStr">
-        <is>
-          <t>增持</t>
-        </is>
-      </c>
+      <c r="S164" s="13" t="inlineStr"/>
       <c r="T164" s="13" t="inlineStr"/>
       <c r="U164" s="13" t="inlineStr"/>
       <c r="V164" s="13" t="inlineStr"/>
     </row>
     <row r="165" ht="16" customHeight="1">
       <c r="A165" s="15" t="n"/>
-      <c r="B165" s="16" t="n"/>
+      <c r="B165" s="15" t="n"/>
       <c r="C165" s="17" t="inlineStr">
         <is>
           <t>材料</t>
@@ -10881,27 +10885,27 @@
       </c>
       <c r="D165" s="18" t="inlineStr">
         <is>
-          <t>玻纤/电子布，日本龙头</t>
+          <t>电解铜箔/锂电铜箔</t>
         </is>
       </c>
       <c r="E165" s="19" t="inlineStr">
         <is>
-          <t>国际复材</t>
+          <t>诺德股份</t>
         </is>
       </c>
       <c r="F165" s="20" t="inlineStr">
         <is>
-          <t>301526.SZ</t>
+          <t>600110.SH</t>
         </is>
       </c>
       <c r="G165" s="21" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H165" s="21" t="inlineStr">
         <is>
-          <t>玻纤/电子布</t>
+          <t>电解铜箔</t>
         </is>
       </c>
       <c r="I165" s="22" t="inlineStr">
@@ -10929,11 +10933,7 @@
     </row>
     <row r="166" ht="16" customHeight="1">
       <c r="A166" s="15" t="n"/>
-      <c r="B166" s="17" t="inlineStr">
-        <is>
-          <t>树脂/PCB基材</t>
-        </is>
-      </c>
+      <c r="B166" s="15" t="n"/>
       <c r="C166" s="17" t="inlineStr">
         <is>
           <t>材料</t>
@@ -10941,27 +10941,27 @@
       </c>
       <c r="D166" s="18" t="inlineStr">
         <is>
-          <t>覆铜板用环氧树脂/改性材料，PCB基材关键</t>
+          <t>高端超薄铜箔，AI服务器PCB用</t>
         </is>
       </c>
       <c r="E166" s="19" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>中一科技</t>
         </is>
       </c>
       <c r="F166" s="20" t="inlineStr">
         <is>
-          <t>601208.SH</t>
+          <t>003031.SZ</t>
         </is>
       </c>
       <c r="G166" s="21" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H166" s="21" t="inlineStr">
         <is>
-          <t>树脂/PCB基材</t>
+          <t>高端超薄铜箔</t>
         </is>
       </c>
       <c r="I166" s="22" t="inlineStr">
@@ -10997,27 +10997,27 @@
       </c>
       <c r="D167" s="18" t="inlineStr">
         <is>
-          <t>酚醛树脂/环氧树脂，PCB基材</t>
+          <t>高精铜箔/压延铜箔</t>
         </is>
       </c>
       <c r="E167" s="19" t="inlineStr">
         <is>
-          <t>圣泉集团</t>
+          <t>德福科技</t>
         </is>
       </c>
       <c r="F167" s="20" t="inlineStr">
         <is>
-          <t>605589.SH</t>
+          <t>301511.SZ</t>
         </is>
       </c>
       <c r="G167" s="21" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H167" s="21" t="inlineStr">
         <is>
-          <t>酚醛/环氧树脂</t>
+          <t>高精铜箔</t>
         </is>
       </c>
       <c r="I167" s="22" t="inlineStr">
@@ -11053,27 +11053,27 @@
       </c>
       <c r="D168" s="18" t="inlineStr">
         <is>
-          <t>覆铜板专用树脂/功能材料</t>
+          <t>覆铜板关键增强材料，高端电子布价格翻倍，缺货至2028</t>
         </is>
       </c>
       <c r="E168" s="19" t="inlineStr">
         <is>
-          <t>美联新材</t>
+          <t>中国巨石</t>
         </is>
       </c>
       <c r="F168" s="20" t="inlineStr">
         <is>
-          <t>300586.SZ</t>
+          <t>600176.SH</t>
         </is>
       </c>
       <c r="G168" s="21" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H168" s="21" t="inlineStr">
         <is>
-          <t>覆铜板树脂材料</t>
+          <t>玻纤/电子布</t>
         </is>
       </c>
       <c r="I168" s="22" t="inlineStr">
@@ -11101,7 +11101,7 @@
     </row>
     <row r="169" ht="16" customHeight="1">
       <c r="A169" s="15" t="n"/>
-      <c r="B169" s="16" t="n"/>
+      <c r="B169" s="15" t="n"/>
       <c r="C169" s="17" t="inlineStr">
         <is>
           <t>材料</t>
@@ -11109,17 +11109,17 @@
       </c>
       <c r="D169" s="18" t="inlineStr">
         <is>
-          <t>电子级环氧树脂/PCB基材</t>
+          <t>高端电子布</t>
         </is>
       </c>
       <c r="E169" s="19" t="inlineStr">
         <is>
-          <t>宏昌电子</t>
+          <t>宏和科技</t>
         </is>
       </c>
       <c r="F169" s="20" t="inlineStr">
         <is>
-          <t>603002.SH</t>
+          <t>603256.SH</t>
         </is>
       </c>
       <c r="G169" s="21" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="H169" s="21" t="inlineStr">
         <is>
-          <t>环氧树脂/PCB基材</t>
+          <t>高端电子布</t>
         </is>
       </c>
       <c r="I169" s="22" t="inlineStr">
@@ -11157,11 +11157,7 @@
     </row>
     <row r="170" ht="16" customHeight="1">
       <c r="A170" s="15" t="n"/>
-      <c r="B170" s="17" t="inlineStr">
-        <is>
-          <t>石英/特种材料</t>
-        </is>
-      </c>
+      <c r="B170" s="15" t="n"/>
       <c r="C170" s="17" t="inlineStr">
         <is>
           <t>材料</t>
@@ -11169,27 +11165,27 @@
       </c>
       <c r="D170" s="18" t="inlineStr">
         <is>
-          <t>高纯石英纤维/石英玻璃，半导体炉管材料</t>
+          <t>玻纤/复合材料</t>
         </is>
       </c>
       <c r="E170" s="19" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>中材科技</t>
         </is>
       </c>
       <c r="F170" s="20" t="inlineStr">
         <is>
-          <t>300395.SZ</t>
+          <t>002080.SZ</t>
         </is>
       </c>
       <c r="G170" s="21" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H170" s="21" t="inlineStr">
         <is>
-          <t>石英纤维/石英玻璃</t>
+          <t>玻纤/复合材料</t>
         </is>
       </c>
       <c r="I170" s="22" t="inlineStr">
@@ -11208,9 +11204,17 @@
       <c r="N170" s="13" t="inlineStr"/>
       <c r="O170" s="13" t="inlineStr"/>
       <c r="P170" s="13" t="inlineStr"/>
-      <c r="Q170" s="13" t="inlineStr"/>
+      <c r="Q170" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="R170" s="13" t="inlineStr"/>
-      <c r="S170" s="13" t="inlineStr"/>
+      <c r="S170" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="T170" s="13" t="inlineStr"/>
       <c r="U170" s="13" t="inlineStr"/>
       <c r="V170" s="13" t="inlineStr"/>
@@ -11225,27 +11229,27 @@
       </c>
       <c r="D171" s="18" t="inlineStr">
         <is>
-          <t>无机非金属粉体，半导体封装填料</t>
+          <t>玻纤/电子布，日本龙头</t>
         </is>
       </c>
       <c r="E171" s="19" t="inlineStr">
         <is>
-          <t>联瑞新材</t>
+          <t>国际复材</t>
         </is>
       </c>
       <c r="F171" s="20" t="inlineStr">
         <is>
-          <t>688300.SH</t>
+          <t>301526.SZ</t>
         </is>
       </c>
       <c r="G171" s="21" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H171" s="21" t="inlineStr">
         <is>
-          <t>无机粉体/封装填料</t>
+          <t>玻纤/电子布</t>
         </is>
       </c>
       <c r="I171" s="22" t="inlineStr">
@@ -11275,7 +11279,7 @@
       <c r="A172" s="15" t="n"/>
       <c r="B172" s="17" t="inlineStr">
         <is>
-          <t>金刚石散热</t>
+          <t>树脂/PCB基材</t>
         </is>
       </c>
       <c r="C172" s="17" t="inlineStr">
@@ -11285,17 +11289,17 @@
       </c>
       <c r="D172" s="18" t="inlineStr">
         <is>
-          <t>人工金刚石/热管理材料，AI芯片散热关键</t>
+          <t>覆铜板用环氧树脂/改性材料，PCB基材关键</t>
         </is>
       </c>
       <c r="E172" s="19" t="inlineStr">
         <is>
-          <t>黄河旋风</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="F172" s="20" t="inlineStr">
         <is>
-          <t>600172.SH</t>
+          <t>601208.SH</t>
         </is>
       </c>
       <c r="G172" s="21" t="inlineStr">
@@ -11305,7 +11309,7 @@
       </c>
       <c r="H172" s="21" t="inlineStr">
         <is>
-          <t>人工金刚石/热管理</t>
+          <t>树脂/PCB基材</t>
         </is>
       </c>
       <c r="I172" s="22" t="inlineStr">
@@ -11341,27 +11345,27 @@
       </c>
       <c r="D173" s="18" t="inlineStr">
         <is>
-          <t>超硬材料/金刚石工具</t>
+          <t>酚醛树脂/环氧树脂，PCB基材</t>
         </is>
       </c>
       <c r="E173" s="19" t="inlineStr">
         <is>
-          <t>四方达</t>
+          <t>圣泉集团</t>
         </is>
       </c>
       <c r="F173" s="20" t="inlineStr">
         <is>
-          <t>300179.SZ</t>
+          <t>605589.SH</t>
         </is>
       </c>
       <c r="G173" s="21" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H173" s="21" t="inlineStr">
         <is>
-          <t>超硬材料/金刚石</t>
+          <t>酚醛/环氧树脂</t>
         </is>
       </c>
       <c r="I173" s="22" t="inlineStr">
@@ -11397,17 +11401,17 @@
       </c>
       <c r="D174" s="18" t="inlineStr">
         <is>
-          <t>人工金刚石/超硬材料</t>
+          <t>覆铜板专用树脂/功能材料</t>
         </is>
       </c>
       <c r="E174" s="19" t="inlineStr">
         <is>
-          <t>力量钻石</t>
+          <t>美联新材</t>
         </is>
       </c>
       <c r="F174" s="20" t="inlineStr">
         <is>
-          <t>301071.SZ</t>
+          <t>300586.SZ</t>
         </is>
       </c>
       <c r="G174" s="21" t="inlineStr">
@@ -11417,7 +11421,7 @@
       </c>
       <c r="H174" s="21" t="inlineStr">
         <is>
-          <t>人工金刚石</t>
+          <t>覆铜板树脂材料</t>
         </is>
       </c>
       <c r="I174" s="22" t="inlineStr">
@@ -11445,7 +11449,7 @@
     </row>
     <row r="175" ht="16" customHeight="1">
       <c r="A175" s="15" t="n"/>
-      <c r="B175" s="15" t="n"/>
+      <c r="B175" s="16" t="n"/>
       <c r="C175" s="17" t="inlineStr">
         <is>
           <t>材料</t>
@@ -11453,27 +11457,27 @@
       </c>
       <c r="D175" s="18" t="inlineStr">
         <is>
-          <t>CVD金刚石/超硬涂层，芯片散热基板</t>
+          <t>电子级环氧树脂/PCB基材</t>
         </is>
       </c>
       <c r="E175" s="19" t="inlineStr">
         <is>
-          <t>沃尔德</t>
+          <t>宏昌电子</t>
         </is>
       </c>
       <c r="F175" s="20" t="inlineStr">
         <is>
-          <t>688028.SH</t>
+          <t>603002.SH</t>
         </is>
       </c>
       <c r="G175" s="21" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H175" s="21" t="inlineStr">
         <is>
-          <t>CVD金刚石/超硬涂层</t>
+          <t>环氧树脂/PCB基材</t>
         </is>
       </c>
       <c r="I175" s="22" t="inlineStr">
@@ -11501,7 +11505,11 @@
     </row>
     <row r="176" ht="16" customHeight="1">
       <c r="A176" s="15" t="n"/>
-      <c r="B176" s="15" t="n"/>
+      <c r="B176" s="17" t="inlineStr">
+        <is>
+          <t>石英/特种材料</t>
+        </is>
+      </c>
       <c r="C176" s="17" t="inlineStr">
         <is>
           <t>材料</t>
@@ -11509,27 +11517,27 @@
       </c>
       <c r="D176" s="18" t="inlineStr">
         <is>
-          <t>人工金刚石/军工超硬材料</t>
+          <t>高纯石英纤维/石英玻璃，半导体炉管材料</t>
         </is>
       </c>
       <c r="E176" s="19" t="inlineStr">
         <is>
-          <t>中兵红箭</t>
+          <t>菲利华</t>
         </is>
       </c>
       <c r="F176" s="20" t="inlineStr">
         <is>
-          <t>000519.SZ</t>
+          <t>300395.SZ</t>
         </is>
       </c>
       <c r="G176" s="21" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H176" s="21" t="inlineStr">
         <is>
-          <t>人工金刚石/军工超硬</t>
+          <t>石英纤维/石英玻璃</t>
         </is>
       </c>
       <c r="I176" s="22" t="inlineStr">
@@ -11556,7 +11564,7 @@
       <c r="V176" s="13" t="inlineStr"/>
     </row>
     <row r="177" ht="16" customHeight="1">
-      <c r="A177" s="16" t="n"/>
+      <c r="A177" s="15" t="n"/>
       <c r="B177" s="16" t="n"/>
       <c r="C177" s="17" t="inlineStr">
         <is>
@@ -11565,27 +11573,27 @@
       </c>
       <c r="D177" s="18" t="inlineStr">
         <is>
-          <t>精密轴承/金刚石工具</t>
+          <t>无机非金属粉体，半导体封装填料</t>
         </is>
       </c>
       <c r="E177" s="19" t="inlineStr">
         <is>
-          <t>国机精工</t>
+          <t>联瑞新材</t>
         </is>
       </c>
       <c r="F177" s="20" t="inlineStr">
         <is>
-          <t>002046.SZ</t>
+          <t>688300.SH</t>
         </is>
       </c>
       <c r="G177" s="21" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H177" s="21" t="inlineStr">
         <is>
-          <t>精密轴承/超硬材料</t>
+          <t>无机粉体/封装填料</t>
         </is>
       </c>
       <c r="I177" s="22" t="inlineStr">
@@ -11612,55 +11620,50 @@
       <c r="V177" s="13" t="inlineStr"/>
     </row>
     <row r="178" ht="16" customHeight="1">
-      <c r="A178" s="3" t="inlineStr">
-        <is>
-          <t>5. AI算力
-应用层</t>
-        </is>
-      </c>
-      <c r="B178" s="36" t="inlineStr">
-        <is>
-          <t>光模块设备</t>
-        </is>
-      </c>
-      <c r="C178" s="37" t="inlineStr">
-        <is>
-          <t>AI算力</t>
-        </is>
-      </c>
-      <c r="D178" s="38" t="inlineStr">
-        <is>
-          <t>光模块/光芯片封装测试设备，AI数据中心必需</t>
-        </is>
-      </c>
-      <c r="E178" s="39" t="inlineStr">
-        <is>
-          <t>罗博特科</t>
-        </is>
-      </c>
-      <c r="F178" s="40" t="inlineStr">
-        <is>
-          <t>688062.SH</t>
-        </is>
-      </c>
-      <c r="G178" s="41" t="inlineStr">
-        <is>
-          <t>上交所科创板</t>
-        </is>
-      </c>
-      <c r="H178" s="41" t="inlineStr">
-        <is>
-          <t>光模块封装测试设备</t>
-        </is>
-      </c>
-      <c r="I178" s="42" t="inlineStr">
+      <c r="A178" s="15" t="n"/>
+      <c r="B178" s="17" t="inlineStr">
+        <is>
+          <t>金刚石散热</t>
+        </is>
+      </c>
+      <c r="C178" s="17" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="D178" s="18" t="inlineStr">
+        <is>
+          <t>人工金刚石/热管理材料，AI芯片散热关键</t>
+        </is>
+      </c>
+      <c r="E178" s="19" t="inlineStr">
+        <is>
+          <t>黄河旋风</t>
+        </is>
+      </c>
+      <c r="F178" s="20" t="inlineStr">
+        <is>
+          <t>600172.SH</t>
+        </is>
+      </c>
+      <c r="G178" s="21" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="H178" s="21" t="inlineStr">
+        <is>
+          <t>人工金刚石/热管理</t>
+        </is>
+      </c>
+      <c r="I178" s="22" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="J178" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J178" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K178" s="13" t="inlineStr"/>
@@ -11679,44 +11682,44 @@
     <row r="179" ht="16" customHeight="1">
       <c r="A179" s="15" t="n"/>
       <c r="B179" s="15" t="n"/>
-      <c r="C179" s="37" t="inlineStr">
-        <is>
-          <t>AI算力</t>
-        </is>
-      </c>
-      <c r="D179" s="38" t="inlineStr">
-        <is>
-          <t>光模块自动化生产设备</t>
-        </is>
-      </c>
-      <c r="E179" s="39" t="inlineStr">
-        <is>
-          <t>科瑞技术</t>
-        </is>
-      </c>
-      <c r="F179" s="40" t="inlineStr">
-        <is>
-          <t>002957.SZ</t>
-        </is>
-      </c>
-      <c r="G179" s="41" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="H179" s="41" t="inlineStr">
-        <is>
-          <t>光模块生产设备</t>
-        </is>
-      </c>
-      <c r="I179" s="42" t="inlineStr">
+      <c r="C179" s="17" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="D179" s="18" t="inlineStr">
+        <is>
+          <t>超硬材料/金刚石工具</t>
+        </is>
+      </c>
+      <c r="E179" s="19" t="inlineStr">
+        <is>
+          <t>四方达</t>
+        </is>
+      </c>
+      <c r="F179" s="20" t="inlineStr">
+        <is>
+          <t>300179.SZ</t>
+        </is>
+      </c>
+      <c r="G179" s="21" t="inlineStr">
+        <is>
+          <t>深交所创业板</t>
+        </is>
+      </c>
+      <c r="H179" s="21" t="inlineStr">
+        <is>
+          <t>超硬材料/金刚石</t>
+        </is>
+      </c>
+      <c r="I179" s="22" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="J179" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J179" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K179" s="13" t="inlineStr"/>
@@ -11735,44 +11738,44 @@
     <row r="180" ht="16" customHeight="1">
       <c r="A180" s="15" t="n"/>
       <c r="B180" s="15" t="n"/>
-      <c r="C180" s="37" t="inlineStr">
-        <is>
-          <t>AI算力</t>
-        </is>
-      </c>
-      <c r="D180" s="38" t="inlineStr">
-        <is>
-          <t>光模块组装/测试设备</t>
-        </is>
-      </c>
-      <c r="E180" s="39" t="inlineStr">
-        <is>
-          <t>博杰股份</t>
-        </is>
-      </c>
-      <c r="F180" s="40" t="inlineStr">
-        <is>
-          <t>300784.SZ</t>
-        </is>
-      </c>
-      <c r="G180" s="41" t="inlineStr">
+      <c r="C180" s="17" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="D180" s="18" t="inlineStr">
+        <is>
+          <t>人工金刚石/超硬材料</t>
+        </is>
+      </c>
+      <c r="E180" s="19" t="inlineStr">
+        <is>
+          <t>力量钻石</t>
+        </is>
+      </c>
+      <c r="F180" s="20" t="inlineStr">
+        <is>
+          <t>301071.SZ</t>
+        </is>
+      </c>
+      <c r="G180" s="21" t="inlineStr">
         <is>
           <t>深交所创业板</t>
         </is>
       </c>
-      <c r="H180" s="41" t="inlineStr">
-        <is>
-          <t>光模块组装设备</t>
-        </is>
-      </c>
-      <c r="I180" s="42" t="inlineStr">
+      <c r="H180" s="21" t="inlineStr">
+        <is>
+          <t>人工金刚石</t>
+        </is>
+      </c>
+      <c r="I180" s="22" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="J180" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J180" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K180" s="13" t="inlineStr"/>
@@ -11790,45 +11793,45 @@
     </row>
     <row r="181" ht="16" customHeight="1">
       <c r="A181" s="15" t="n"/>
-      <c r="B181" s="16" t="n"/>
-      <c r="C181" s="37" t="inlineStr">
-        <is>
-          <t>AI算力</t>
-        </is>
-      </c>
-      <c r="D181" s="38" t="inlineStr">
-        <is>
-          <t>激光/光模块加工设备</t>
-        </is>
-      </c>
-      <c r="E181" s="39" t="inlineStr">
-        <is>
-          <t>德龙激光</t>
-        </is>
-      </c>
-      <c r="F181" s="40" t="inlineStr">
-        <is>
-          <t>688170.SH</t>
-        </is>
-      </c>
-      <c r="G181" s="41" t="inlineStr">
+      <c r="B181" s="15" t="n"/>
+      <c r="C181" s="17" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="D181" s="18" t="inlineStr">
+        <is>
+          <t>CVD金刚石/超硬涂层，芯片散热基板</t>
+        </is>
+      </c>
+      <c r="E181" s="19" t="inlineStr">
+        <is>
+          <t>沃尔德</t>
+        </is>
+      </c>
+      <c r="F181" s="20" t="inlineStr">
+        <is>
+          <t>688028.SH</t>
+        </is>
+      </c>
+      <c r="G181" s="21" t="inlineStr">
         <is>
           <t>上交所科创板</t>
         </is>
       </c>
-      <c r="H181" s="41" t="inlineStr">
-        <is>
-          <t>激光加工/光模块设备</t>
-        </is>
-      </c>
-      <c r="I181" s="42" t="inlineStr">
+      <c r="H181" s="21" t="inlineStr">
+        <is>
+          <t>CVD金刚石/超硬涂层</t>
+        </is>
+      </c>
+      <c r="I181" s="22" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="J181" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J181" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K181" s="13" t="inlineStr"/>
@@ -11846,49 +11849,45 @@
     </row>
     <row r="182" ht="16" customHeight="1">
       <c r="A182" s="15" t="n"/>
-      <c r="B182" s="36" t="inlineStr">
-        <is>
-          <t>CPO 共封装光学</t>
-        </is>
-      </c>
-      <c r="C182" s="37" t="inlineStr">
-        <is>
-          <t>AI算力</t>
-        </is>
-      </c>
-      <c r="D182" s="38" t="inlineStr">
-        <is>
-          <t>数据中心光电共封装，AI算力核心互连技术</t>
-        </is>
-      </c>
-      <c r="E182" s="39" t="inlineStr">
-        <is>
-          <t>中际旭创</t>
-        </is>
-      </c>
-      <c r="F182" s="40" t="inlineStr">
-        <is>
-          <t>300308.SZ</t>
-        </is>
-      </c>
-      <c r="G182" s="41" t="inlineStr">
+      <c r="B182" s="15" t="n"/>
+      <c r="C182" s="17" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="D182" s="18" t="inlineStr">
+        <is>
+          <t>人工金刚石/军工超硬材料</t>
+        </is>
+      </c>
+      <c r="E182" s="19" t="inlineStr">
+        <is>
+          <t>中兵红箭</t>
+        </is>
+      </c>
+      <c r="F182" s="20" t="inlineStr">
+        <is>
+          <t>000519.SZ</t>
+        </is>
+      </c>
+      <c r="G182" s="21" t="inlineStr">
         <is>
           <t>深交所</t>
         </is>
       </c>
-      <c r="H182" s="41" t="inlineStr">
-        <is>
-          <t>CPO/光模块</t>
-        </is>
-      </c>
-      <c r="I182" s="42" t="inlineStr">
+      <c r="H182" s="21" t="inlineStr">
+        <is>
+          <t>人工金刚石/军工超硬</t>
+        </is>
+      </c>
+      <c r="I182" s="22" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="J182" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J182" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K182" s="13" t="inlineStr"/>
@@ -11905,46 +11904,46 @@
       <c r="V182" s="13" t="inlineStr"/>
     </row>
     <row r="183" ht="16" customHeight="1">
-      <c r="A183" s="15" t="n"/>
-      <c r="B183" s="15" t="n"/>
-      <c r="C183" s="37" t="inlineStr">
-        <is>
-          <t>AI算力</t>
-        </is>
-      </c>
-      <c r="D183" s="38" t="inlineStr">
-        <is>
-          <t>数据中心光电共封装</t>
-        </is>
-      </c>
-      <c r="E183" s="39" t="inlineStr">
-        <is>
-          <t>新易盛</t>
-        </is>
-      </c>
-      <c r="F183" s="40" t="inlineStr">
-        <is>
-          <t>300502.SZ</t>
-        </is>
-      </c>
-      <c r="G183" s="41" t="inlineStr">
-        <is>
-          <t>深交所创业板</t>
-        </is>
-      </c>
-      <c r="H183" s="41" t="inlineStr">
-        <is>
-          <t>CPO/光模块</t>
-        </is>
-      </c>
-      <c r="I183" s="42" t="inlineStr">
+      <c r="A183" s="16" t="n"/>
+      <c r="B183" s="16" t="n"/>
+      <c r="C183" s="17" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="D183" s="18" t="inlineStr">
+        <is>
+          <t>精密轴承/金刚石工具</t>
+        </is>
+      </c>
+      <c r="E183" s="19" t="inlineStr">
+        <is>
+          <t>国机精工</t>
+        </is>
+      </c>
+      <c r="F183" s="20" t="inlineStr">
+        <is>
+          <t>002046.SZ</t>
+        </is>
+      </c>
+      <c r="G183" s="21" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="H183" s="21" t="inlineStr">
+        <is>
+          <t>精密轴承/超硬材料</t>
+        </is>
+      </c>
+      <c r="I183" s="22" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="J183" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J183" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K183" s="13" t="inlineStr"/>
@@ -11961,8 +11960,17 @@
       <c r="V183" s="13" t="inlineStr"/>
     </row>
     <row r="184" ht="16" customHeight="1">
-      <c r="A184" s="15" t="n"/>
-      <c r="B184" s="15" t="n"/>
+      <c r="A184" s="3" t="inlineStr">
+        <is>
+          <t>5. AI算力
+应用层</t>
+        </is>
+      </c>
+      <c r="B184" s="36" t="inlineStr">
+        <is>
+          <t>光模块设备</t>
+        </is>
+      </c>
       <c r="C184" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -11970,27 +11978,27 @@
       </c>
       <c r="D184" s="38" t="inlineStr">
         <is>
-          <t>CPO光互连组件</t>
+          <t>光模块/光芯片封装测试设备，AI数据中心必需</t>
         </is>
       </c>
       <c r="E184" s="39" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>罗博特科</t>
         </is>
       </c>
       <c r="F184" s="40" t="inlineStr">
         <is>
-          <t>300394.SZ</t>
+          <t>688062.SH</t>
         </is>
       </c>
       <c r="G184" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H184" s="41" t="inlineStr">
         <is>
-          <t>CPO光互连组件</t>
+          <t>光模块封装测试设备</t>
         </is>
       </c>
       <c r="I184" s="42" t="inlineStr">
@@ -11998,9 +12006,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J184" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J184" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K184" s="13" t="inlineStr"/>
@@ -12018,7 +12026,7 @@
     </row>
     <row r="185" ht="16" customHeight="1">
       <c r="A185" s="15" t="n"/>
-      <c r="B185" s="16" t="n"/>
+      <c r="B185" s="15" t="n"/>
       <c r="C185" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12026,17 +12034,17 @@
       </c>
       <c r="D185" s="38" t="inlineStr">
         <is>
-          <t>激光/光通信器件</t>
+          <t>光模块自动化生产设备</t>
         </is>
       </c>
       <c r="E185" s="39" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>科瑞技术</t>
         </is>
       </c>
       <c r="F185" s="40" t="inlineStr">
         <is>
-          <t>000988.SZ</t>
+          <t>002957.SZ</t>
         </is>
       </c>
       <c r="G185" s="41" t="inlineStr">
@@ -12046,7 +12054,7 @@
       </c>
       <c r="H185" s="41" t="inlineStr">
         <is>
-          <t>激光/光通信器件</t>
+          <t>光模块生产设备</t>
         </is>
       </c>
       <c r="I185" s="42" t="inlineStr">
@@ -12054,9 +12062,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J185" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J185" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K185" s="13" t="inlineStr"/>
@@ -12074,11 +12082,7 @@
     </row>
     <row r="186" ht="16" customHeight="1">
       <c r="A186" s="15" t="n"/>
-      <c r="B186" s="36" t="inlineStr">
-        <is>
-          <t>OCS 光交换</t>
-        </is>
-      </c>
+      <c r="B186" s="15" t="n"/>
       <c r="C186" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12086,27 +12090,27 @@
       </c>
       <c r="D186" s="38" t="inlineStr">
         <is>
-          <t>光学交换技术，替代电交换降低数据中心能耗</t>
+          <t>光模块组装/测试设备</t>
         </is>
       </c>
       <c r="E186" s="39" t="inlineStr">
         <is>
-          <t>腾景科技</t>
+          <t>博杰股份</t>
         </is>
       </c>
       <c r="F186" s="40" t="inlineStr">
         <is>
-          <t>688195.SH</t>
+          <t>300784.SZ</t>
         </is>
       </c>
       <c r="G186" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H186" s="41" t="inlineStr">
         <is>
-          <t>光开关/OCS器件</t>
+          <t>光模块组装设备</t>
         </is>
       </c>
       <c r="I186" s="42" t="inlineStr">
@@ -12114,9 +12118,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J186" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J186" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K186" s="13" t="inlineStr"/>
@@ -12134,7 +12138,7 @@
     </row>
     <row r="187" ht="16" customHeight="1">
       <c r="A187" s="15" t="n"/>
-      <c r="B187" s="15" t="n"/>
+      <c r="B187" s="16" t="n"/>
       <c r="C187" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12142,27 +12146,27 @@
       </c>
       <c r="D187" s="38" t="inlineStr">
         <is>
-          <t>晶体光学/激光器件</t>
+          <t>激光/光模块加工设备</t>
         </is>
       </c>
       <c r="E187" s="39" t="inlineStr">
         <is>
-          <t>福晶科技</t>
+          <t>德龙激光</t>
         </is>
       </c>
       <c r="F187" s="40" t="inlineStr">
         <is>
-          <t>002222.SZ</t>
+          <t>688170.SH</t>
         </is>
       </c>
       <c r="G187" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H187" s="41" t="inlineStr">
         <is>
-          <t>晶体光学/激光器件</t>
+          <t>激光加工/光模块设备</t>
         </is>
       </c>
       <c r="I187" s="42" t="inlineStr">
@@ -12170,9 +12174,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J187" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J187" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K187" s="13" t="inlineStr"/>
@@ -12190,7 +12194,11 @@
     </row>
     <row r="188" ht="16" customHeight="1">
       <c r="A188" s="15" t="n"/>
-      <c r="B188" s="15" t="n"/>
+      <c r="B188" s="36" t="inlineStr">
+        <is>
+          <t>CPO 共封装光学</t>
+        </is>
+      </c>
       <c r="C188" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12198,27 +12206,27 @@
       </c>
       <c r="D188" s="38" t="inlineStr">
         <is>
-          <t>OCS光学组件</t>
+          <t>数据中心光电共封装，AI算力核心互连技术</t>
         </is>
       </c>
       <c r="E188" s="39" t="inlineStr">
         <is>
-          <t>光库科技</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="F188" s="40" t="inlineStr">
         <is>
-          <t>300620.SZ</t>
+          <t>300308.SZ</t>
         </is>
       </c>
       <c r="G188" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H188" s="41" t="inlineStr">
         <is>
-          <t>OCS光学组件</t>
+          <t>CPO/光模块</t>
         </is>
       </c>
       <c r="I188" s="42" t="inlineStr">
@@ -12226,9 +12234,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J188" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J188" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K188" s="13" t="inlineStr"/>
@@ -12246,7 +12254,7 @@
     </row>
     <row r="189" ht="16" customHeight="1">
       <c r="A189" s="15" t="n"/>
-      <c r="B189" s="16" t="n"/>
+      <c r="B189" s="15" t="n"/>
       <c r="C189" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12254,27 +12262,27 @@
       </c>
       <c r="D189" s="38" t="inlineStr">
         <is>
-          <t>光模块/相干光器件</t>
+          <t>数据中心光电共封装</t>
         </is>
       </c>
       <c r="E189" s="39" t="inlineStr">
         <is>
-          <t>德科立</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="F189" s="40" t="inlineStr">
         <is>
-          <t>688205.SH</t>
+          <t>300502.SZ</t>
         </is>
       </c>
       <c r="G189" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H189" s="41" t="inlineStr">
         <is>
-          <t>光模块/相干光器件</t>
+          <t>CPO/光模块</t>
         </is>
       </c>
       <c r="I189" s="42" t="inlineStr">
@@ -12282,9 +12290,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J189" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J189" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K189" s="13" t="inlineStr"/>
@@ -12302,11 +12310,7 @@
     </row>
     <row r="190" ht="16" customHeight="1">
       <c r="A190" s="15" t="n"/>
-      <c r="B190" s="36" t="inlineStr">
-        <is>
-          <t>光芯片 Photonic Chip</t>
-        </is>
-      </c>
+      <c r="B190" s="15" t="n"/>
       <c r="C190" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12314,27 +12318,27 @@
       </c>
       <c r="D190" s="38" t="inlineStr">
         <is>
-          <t>AI算力光互连核心芯片</t>
+          <t>CPO光互连组件</t>
         </is>
       </c>
       <c r="E190" s="39" t="inlineStr">
         <is>
-          <t>源杰科技</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="F190" s="40" t="inlineStr">
         <is>
-          <t>688498.SH</t>
+          <t>300394.SZ</t>
         </is>
       </c>
       <c r="G190" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H190" s="41" t="inlineStr">
         <is>
-          <t>激光/光芯片</t>
+          <t>CPO光互连组件</t>
         </is>
       </c>
       <c r="I190" s="42" t="inlineStr">
@@ -12342,9 +12346,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J190" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J190" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K190" s="13" t="inlineStr"/>
@@ -12353,24 +12357,16 @@
       <c r="N190" s="13" t="inlineStr"/>
       <c r="O190" s="13" t="inlineStr"/>
       <c r="P190" s="13" t="inlineStr"/>
-      <c r="Q190" s="14" t="inlineStr">
-        <is>
-          <t>增持</t>
-        </is>
-      </c>
+      <c r="Q190" s="13" t="inlineStr"/>
       <c r="R190" s="13" t="inlineStr"/>
-      <c r="S190" s="14" t="inlineStr">
-        <is>
-          <t>增持</t>
-        </is>
-      </c>
+      <c r="S190" s="13" t="inlineStr"/>
       <c r="T190" s="13" t="inlineStr"/>
       <c r="U190" s="13" t="inlineStr"/>
       <c r="V190" s="13" t="inlineStr"/>
     </row>
     <row r="191" ht="16" customHeight="1">
       <c r="A191" s="15" t="n"/>
-      <c r="B191" s="15" t="n"/>
+      <c r="B191" s="16" t="n"/>
       <c r="C191" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12378,27 +12374,27 @@
       </c>
       <c r="D191" s="38" t="inlineStr">
         <is>
-          <t>光芯片/PLC分路器</t>
+          <t>激光/光通信器件</t>
         </is>
       </c>
       <c r="E191" s="39" t="inlineStr">
         <is>
-          <t>仕佳光子</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="F191" s="40" t="inlineStr">
         <is>
-          <t>688313.SH</t>
+          <t>000988.SZ</t>
         </is>
       </c>
       <c r="G191" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H191" s="41" t="inlineStr">
         <is>
-          <t>光芯片/PLC</t>
+          <t>激光/光通信器件</t>
         </is>
       </c>
       <c r="I191" s="42" t="inlineStr">
@@ -12406,9 +12402,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J191" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J191" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K191" s="13" t="inlineStr"/>
@@ -12426,7 +12422,11 @@
     </row>
     <row r="192" ht="16" customHeight="1">
       <c r="A192" s="15" t="n"/>
-      <c r="B192" s="15" t="n"/>
+      <c r="B192" s="36" t="inlineStr">
+        <is>
+          <t>OCS 光交换</t>
+        </is>
+      </c>
       <c r="C192" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12434,27 +12434,27 @@
       </c>
       <c r="D192" s="38" t="inlineStr">
         <is>
-          <t>光芯片/光模块</t>
+          <t>光学交换技术，替代电交换降低数据中心能耗</t>
         </is>
       </c>
       <c r="E192" s="39" t="inlineStr">
         <is>
-          <t>光迅科技</t>
+          <t>腾景科技</t>
         </is>
       </c>
       <c r="F192" s="40" t="inlineStr">
         <is>
-          <t>002281.SZ</t>
+          <t>688195.SH</t>
         </is>
       </c>
       <c r="G192" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H192" s="41" t="inlineStr">
         <is>
-          <t>光芯片/光模块</t>
+          <t>光开关/OCS器件</t>
         </is>
       </c>
       <c r="I192" s="42" t="inlineStr">
@@ -12462,9 +12462,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J192" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J192" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K192" s="13" t="inlineStr"/>
@@ -12490,27 +12490,27 @@
       </c>
       <c r="D193" s="38" t="inlineStr">
         <is>
-          <t>高功率激光芯片</t>
+          <t>晶体光学/激光器件</t>
         </is>
       </c>
       <c r="E193" s="39" t="inlineStr">
         <is>
-          <t>长光华芯</t>
+          <t>福晶科技</t>
         </is>
       </c>
       <c r="F193" s="40" t="inlineStr">
         <is>
-          <t>688048.SH</t>
+          <t>002222.SZ</t>
         </is>
       </c>
       <c r="G193" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H193" s="41" t="inlineStr">
         <is>
-          <t>高功率激光芯片</t>
+          <t>晶体光学/激光器件</t>
         </is>
       </c>
       <c r="I193" s="42" t="inlineStr">
@@ -12518,9 +12518,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J193" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J193" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K193" s="13" t="inlineStr"/>
@@ -12546,37 +12546,37 @@
       </c>
       <c r="D194" s="38" t="inlineStr">
         <is>
-          <t>硅光/相干光芯片，全球领先</t>
+          <t>OCS光学组件</t>
         </is>
       </c>
       <c r="E194" s="39" t="inlineStr">
         <is>
-          <t>相干公司 Coherent</t>
+          <t>光库科技</t>
         </is>
       </c>
       <c r="F194" s="40" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>300620.SZ</t>
         </is>
       </c>
       <c r="G194" s="41" t="inlineStr">
         <is>
-          <t>NYSE</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H194" s="41" t="inlineStr">
         <is>
-          <t>硅光/相干光芯片</t>
+          <t>OCS光学组件</t>
         </is>
       </c>
       <c r="I194" s="42" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J194" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J194" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K194" s="13" t="inlineStr"/>
@@ -12585,23 +12585,11 @@
       <c r="N194" s="13" t="inlineStr"/>
       <c r="O194" s="13" t="inlineStr"/>
       <c r="P194" s="13" t="inlineStr"/>
-      <c r="Q194" s="14" t="inlineStr">
-        <is>
-          <t>持有,330</t>
-        </is>
-      </c>
+      <c r="Q194" s="13" t="inlineStr"/>
       <c r="R194" s="13" t="inlineStr"/>
-      <c r="S194" s="14" t="inlineStr">
-        <is>
-          <t>增持,300</t>
-        </is>
-      </c>
+      <c r="S194" s="13" t="inlineStr"/>
       <c r="T194" s="13" t="inlineStr"/>
-      <c r="U194" s="14" t="inlineStr">
-        <is>
-          <t>买入,400</t>
-        </is>
-      </c>
+      <c r="U194" s="13" t="inlineStr"/>
       <c r="V194" s="13" t="inlineStr"/>
     </row>
     <row r="195" ht="16" customHeight="1">
@@ -12614,37 +12602,37 @@
       </c>
       <c r="D195" s="38" t="inlineStr">
         <is>
-          <t>光通信芯片/VCSEL/硅光，数据中心高速互连</t>
+          <t>光模块/相干光器件</t>
         </is>
       </c>
       <c r="E195" s="39" t="inlineStr">
         <is>
-          <t>鲁门特姆 Lumentum</t>
+          <t>德科立</t>
         </is>
       </c>
       <c r="F195" s="40" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>688205.SH</t>
         </is>
       </c>
       <c r="G195" s="41" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H195" s="41" t="inlineStr">
         <is>
-          <t>光通信芯片/VCSEL</t>
+          <t>光模块/相干光器件</t>
         </is>
       </c>
       <c r="I195" s="42" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J195" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J195" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K195" s="13" t="inlineStr"/>
@@ -12653,34 +12641,18 @@
       <c r="N195" s="13" t="inlineStr"/>
       <c r="O195" s="13" t="inlineStr"/>
       <c r="P195" s="13" t="inlineStr"/>
-      <c r="Q195" s="14" t="inlineStr">
-        <is>
-          <t>持有,上调900</t>
-        </is>
-      </c>
+      <c r="Q195" s="13" t="inlineStr"/>
       <c r="R195" s="13" t="inlineStr"/>
-      <c r="S195" s="14" t="inlineStr">
-        <is>
-          <t>增持,1130</t>
-        </is>
-      </c>
-      <c r="T195" s="14" t="inlineStr">
-        <is>
-          <t>买入,960</t>
-        </is>
-      </c>
+      <c r="S195" s="13" t="inlineStr"/>
+      <c r="T195" s="13" t="inlineStr"/>
       <c r="U195" s="13" t="inlineStr"/>
-      <c r="V195" s="14" t="inlineStr">
-        <is>
-          <t>持有,1000</t>
-        </is>
-      </c>
+      <c r="V195" s="13" t="inlineStr"/>
     </row>
     <row r="196" ht="16" customHeight="1">
       <c r="A196" s="15" t="n"/>
       <c r="B196" s="36" t="inlineStr">
         <is>
-          <t>AI服务器 PCB</t>
+          <t>光芯片 Photonic Chip</t>
         </is>
       </c>
       <c r="C196" s="37" t="inlineStr">
@@ -12690,27 +12662,27 @@
       </c>
       <c r="D196" s="38" t="inlineStr">
         <is>
-          <t>AI服务器PCB，算力硬件关键基材，今年大涨60%</t>
+          <t>AI算力光互连核心芯片</t>
         </is>
       </c>
       <c r="E196" s="39" t="inlineStr">
         <is>
-          <t>胜宏科技</t>
+          <t>源杰科技</t>
         </is>
       </c>
       <c r="F196" s="40" t="inlineStr">
         <is>
-          <t>300476.SZ</t>
+          <t>688498.SH</t>
         </is>
       </c>
       <c r="G196" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H196" s="41" t="inlineStr">
         <is>
-          <t>AI服务器PCB</t>
+          <t>激光/光芯片</t>
         </is>
       </c>
       <c r="I196" s="42" t="inlineStr">
@@ -12729,9 +12701,17 @@
       <c r="N196" s="13" t="inlineStr"/>
       <c r="O196" s="13" t="inlineStr"/>
       <c r="P196" s="13" t="inlineStr"/>
-      <c r="Q196" s="13" t="inlineStr"/>
+      <c r="Q196" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="R196" s="13" t="inlineStr"/>
-      <c r="S196" s="13" t="inlineStr"/>
+      <c r="S196" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="T196" s="13" t="inlineStr"/>
       <c r="U196" s="13" t="inlineStr"/>
       <c r="V196" s="13" t="inlineStr"/>
@@ -12746,27 +12726,27 @@
       </c>
       <c r="D197" s="38" t="inlineStr">
         <is>
-          <t>高端PCB/FPC</t>
+          <t>光芯片/PLC分路器</t>
         </is>
       </c>
       <c r="E197" s="39" t="inlineStr">
         <is>
-          <t>东山精密</t>
+          <t>仕佳光子</t>
         </is>
       </c>
       <c r="F197" s="40" t="inlineStr">
         <is>
-          <t>002384.SZ</t>
+          <t>688313.SH</t>
         </is>
       </c>
       <c r="G197" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H197" s="41" t="inlineStr">
         <is>
-          <t>高端PCB/FPC</t>
+          <t>光芯片/PLC</t>
         </is>
       </c>
       <c r="I197" s="42" t="inlineStr">
@@ -12785,17 +12765,9 @@
       <c r="N197" s="13" t="inlineStr"/>
       <c r="O197" s="13" t="inlineStr"/>
       <c r="P197" s="13" t="inlineStr"/>
-      <c r="Q197" s="14" t="inlineStr">
-        <is>
-          <t>增持</t>
-        </is>
-      </c>
+      <c r="Q197" s="13" t="inlineStr"/>
       <c r="R197" s="13" t="inlineStr"/>
-      <c r="S197" s="14" t="inlineStr">
-        <is>
-          <t>增持</t>
-        </is>
-      </c>
+      <c r="S197" s="13" t="inlineStr"/>
       <c r="T197" s="13" t="inlineStr"/>
       <c r="U197" s="13" t="inlineStr"/>
       <c r="V197" s="13" t="inlineStr"/>
@@ -12810,17 +12782,17 @@
       </c>
       <c r="D198" s="38" t="inlineStr">
         <is>
-          <t>AI服务器/封装基板</t>
+          <t>光芯片/光模块</t>
         </is>
       </c>
       <c r="E198" s="39" t="inlineStr">
         <is>
-          <t>深南电路</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="F198" s="40" t="inlineStr">
         <is>
-          <t>002916.SZ</t>
+          <t>002281.SZ</t>
         </is>
       </c>
       <c r="G198" s="41" t="inlineStr">
@@ -12830,7 +12802,7 @@
       </c>
       <c r="H198" s="41" t="inlineStr">
         <is>
-          <t>AI服务器/封装基板</t>
+          <t>光芯片/光模块</t>
         </is>
       </c>
       <c r="I198" s="42" t="inlineStr">
@@ -12858,7 +12830,7 @@
     </row>
     <row r="199" ht="16" customHeight="1">
       <c r="A199" s="15" t="n"/>
-      <c r="B199" s="16" t="n"/>
+      <c r="B199" s="15" t="n"/>
       <c r="C199" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12866,27 +12838,27 @@
       </c>
       <c r="D199" s="38" t="inlineStr">
         <is>
-          <t>高速高频PCB</t>
+          <t>高功率激光芯片</t>
         </is>
       </c>
       <c r="E199" s="39" t="inlineStr">
         <is>
-          <t>沪电股份</t>
+          <t>长光华芯</t>
         </is>
       </c>
       <c r="F199" s="40" t="inlineStr">
         <is>
-          <t>002463.SZ</t>
+          <t>688048.SH</t>
         </is>
       </c>
       <c r="G199" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H199" s="41" t="inlineStr">
         <is>
-          <t>高速高频PCB</t>
+          <t>高功率激光芯片</t>
         </is>
       </c>
       <c r="I199" s="42" t="inlineStr">
@@ -12914,11 +12886,7 @@
     </row>
     <row r="200" ht="16" customHeight="1">
       <c r="A200" s="15" t="n"/>
-      <c r="B200" s="36" t="inlineStr">
-        <is>
-          <t>AI服务器整机</t>
-        </is>
-      </c>
+      <c r="B200" s="15" t="n"/>
       <c r="C200" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12926,37 +12894,37 @@
       </c>
       <c r="D200" s="38" t="inlineStr">
         <is>
-          <t>AI服务器代工/组装</t>
+          <t>硅光/相干光芯片，全球领先</t>
         </is>
       </c>
       <c r="E200" s="39" t="inlineStr">
         <is>
-          <t>工业富联</t>
+          <t>相干公司 Coherent</t>
         </is>
       </c>
       <c r="F200" s="40" t="inlineStr">
         <is>
-          <t>601138.SH</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="G200" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>NYSE</t>
         </is>
       </c>
       <c r="H200" s="41" t="inlineStr">
         <is>
-          <t>AI服务器代工/组装</t>
+          <t>硅光/相干光芯片</t>
         </is>
       </c>
       <c r="I200" s="42" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="J200" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J200" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K200" s="13" t="inlineStr"/>
@@ -12967,18 +12935,26 @@
       <c r="P200" s="13" t="inlineStr"/>
       <c r="Q200" s="14" t="inlineStr">
         <is>
-          <t>增持</t>
+          <t>持有,330</t>
         </is>
       </c>
       <c r="R200" s="13" t="inlineStr"/>
-      <c r="S200" s="13" t="inlineStr"/>
+      <c r="S200" s="14" t="inlineStr">
+        <is>
+          <t>增持,300</t>
+        </is>
+      </c>
       <c r="T200" s="13" t="inlineStr"/>
-      <c r="U200" s="13" t="inlineStr"/>
+      <c r="U200" s="14" t="inlineStr">
+        <is>
+          <t>买入,400</t>
+        </is>
+      </c>
       <c r="V200" s="13" t="inlineStr"/>
     </row>
     <row r="201" ht="16" customHeight="1">
       <c r="A201" s="15" t="n"/>
-      <c r="B201" s="15" t="n"/>
+      <c r="B201" s="16" t="n"/>
       <c r="C201" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -12986,37 +12962,37 @@
       </c>
       <c r="D201" s="38" t="inlineStr">
         <is>
-          <t>AI服务器整机</t>
+          <t>光通信芯片/VCSEL/硅光，数据中心高速互连</t>
         </is>
       </c>
       <c r="E201" s="39" t="inlineStr">
         <is>
-          <t>浪潮信息</t>
+          <t>鲁门特姆 Lumentum</t>
         </is>
       </c>
       <c r="F201" s="40" t="inlineStr">
         <is>
-          <t>000977.SZ</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="G201" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="H201" s="41" t="inlineStr">
         <is>
-          <t>AI服务器整机</t>
+          <t>光通信芯片/VCSEL</t>
         </is>
       </c>
       <c r="I201" s="42" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="J201" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J201" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K201" s="13" t="inlineStr"/>
@@ -13025,16 +13001,36 @@
       <c r="N201" s="13" t="inlineStr"/>
       <c r="O201" s="13" t="inlineStr"/>
       <c r="P201" s="13" t="inlineStr"/>
-      <c r="Q201" s="13" t="inlineStr"/>
+      <c r="Q201" s="14" t="inlineStr">
+        <is>
+          <t>持有,上调900</t>
+        </is>
+      </c>
       <c r="R201" s="13" t="inlineStr"/>
-      <c r="S201" s="13" t="inlineStr"/>
-      <c r="T201" s="13" t="inlineStr"/>
+      <c r="S201" s="14" t="inlineStr">
+        <is>
+          <t>增持,1130</t>
+        </is>
+      </c>
+      <c r="T201" s="14" t="inlineStr">
+        <is>
+          <t>买入,960</t>
+        </is>
+      </c>
       <c r="U201" s="13" t="inlineStr"/>
-      <c r="V201" s="13" t="inlineStr"/>
+      <c r="V201" s="14" t="inlineStr">
+        <is>
+          <t>持有,1000</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="16" customHeight="1">
       <c r="A202" s="15" t="n"/>
-      <c r="B202" s="15" t="n"/>
+      <c r="B202" s="36" t="inlineStr">
+        <is>
+          <t>AI服务器 PCB</t>
+        </is>
+      </c>
       <c r="C202" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13042,27 +13038,27 @@
       </c>
       <c r="D202" s="38" t="inlineStr">
         <is>
-          <t>AI服务器/网络设备</t>
+          <t>AI服务器PCB，算力硬件关键基材，今年大涨60%</t>
         </is>
       </c>
       <c r="E202" s="39" t="inlineStr">
         <is>
-          <t>紫光股份</t>
+          <t>胜宏科技</t>
         </is>
       </c>
       <c r="F202" s="40" t="inlineStr">
         <is>
-          <t>000938.SZ</t>
+          <t>300476.SZ</t>
         </is>
       </c>
       <c r="G202" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H202" s="41" t="inlineStr">
         <is>
-          <t>AI服务器/网络设备</t>
+          <t>AI服务器PCB</t>
         </is>
       </c>
       <c r="I202" s="42" t="inlineStr">
@@ -13070,9 +13066,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J202" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J202" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K202" s="13" t="inlineStr"/>
@@ -13098,27 +13094,27 @@
       </c>
       <c r="D203" s="38" t="inlineStr">
         <is>
-          <t>AI服务器/超算</t>
+          <t>高端PCB/FPC</t>
         </is>
       </c>
       <c r="E203" s="39" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="F203" s="40" t="inlineStr">
         <is>
-          <t>603019.SH</t>
+          <t>002384.SZ</t>
         </is>
       </c>
       <c r="G203" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H203" s="41" t="inlineStr">
         <is>
-          <t>AI服务器/超算</t>
+          <t>高端PCB/FPC</t>
         </is>
       </c>
       <c r="I203" s="42" t="inlineStr">
@@ -13126,9 +13122,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J203" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J203" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K203" s="13" t="inlineStr"/>
@@ -13137,16 +13133,24 @@
       <c r="N203" s="13" t="inlineStr"/>
       <c r="O203" s="13" t="inlineStr"/>
       <c r="P203" s="13" t="inlineStr"/>
-      <c r="Q203" s="13" t="inlineStr"/>
+      <c r="Q203" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="R203" s="13" t="inlineStr"/>
-      <c r="S203" s="13" t="inlineStr"/>
+      <c r="S203" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="T203" s="13" t="inlineStr"/>
       <c r="U203" s="13" t="inlineStr"/>
       <c r="V203" s="13" t="inlineStr"/>
     </row>
     <row r="204" ht="16" customHeight="1">
       <c r="A204" s="15" t="n"/>
-      <c r="B204" s="16" t="n"/>
+      <c r="B204" s="15" t="n"/>
       <c r="C204" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13154,37 +13158,37 @@
       </c>
       <c r="D204" s="38" t="inlineStr">
         <is>
-          <t>AI服务器/机柜，台湾云端服务器龙头</t>
+          <t>AI服务器/封装基板</t>
         </is>
       </c>
       <c r="E204" s="39" t="inlineStr">
         <is>
-          <t>纬颖科技 Wiwynn</t>
+          <t>深南电路</t>
         </is>
       </c>
       <c r="F204" s="40" t="inlineStr">
         <is>
-          <t>6669.TW</t>
+          <t>002916.SZ</t>
         </is>
       </c>
       <c r="G204" s="41" t="inlineStr">
         <is>
-          <t>台湾证交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H204" s="41" t="inlineStr">
         <is>
-          <t>AI服务器/机柜</t>
+          <t>AI服务器/封装基板</t>
         </is>
       </c>
       <c r="I204" s="42" t="inlineStr">
         <is>
-          <t>TWD</t>
-        </is>
-      </c>
-      <c r="J204" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J204" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K204" s="13" t="inlineStr"/>
@@ -13202,11 +13206,7 @@
     </row>
     <row r="205" ht="16" customHeight="1">
       <c r="A205" s="15" t="n"/>
-      <c r="B205" s="36" t="inlineStr">
-        <is>
-          <t>AI芯片</t>
-        </is>
-      </c>
+      <c r="B205" s="16" t="n"/>
       <c r="C205" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13214,27 +13214,27 @@
       </c>
       <c r="D205" s="38" t="inlineStr">
         <is>
-          <t>国产GPU/DCU芯片，AI训练推理</t>
+          <t>高速高频PCB</t>
         </is>
       </c>
       <c r="E205" s="39" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>沪电股份</t>
         </is>
       </c>
       <c r="F205" s="40" t="inlineStr">
         <is>
-          <t>688041.SH</t>
+          <t>002463.SZ</t>
         </is>
       </c>
       <c r="G205" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H205" s="41" t="inlineStr">
         <is>
-          <t>GPU/DCU芯片</t>
+          <t>高速高频PCB</t>
         </is>
       </c>
       <c r="I205" s="42" t="inlineStr">
@@ -13242,9 +13242,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J205" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J205" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K205" s="13" t="inlineStr"/>
@@ -13262,7 +13262,11 @@
     </row>
     <row r="206" ht="16" customHeight="1">
       <c r="A206" s="15" t="n"/>
-      <c r="B206" s="15" t="n"/>
+      <c r="B206" s="36" t="inlineStr">
+        <is>
+          <t>AI服务器整机</t>
+        </is>
+      </c>
       <c r="C206" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13270,27 +13274,27 @@
       </c>
       <c r="D206" s="38" t="inlineStr">
         <is>
-          <t>AI推理/训练芯片</t>
+          <t>AI服务器代工/组装</t>
         </is>
       </c>
       <c r="E206" s="39" t="inlineStr">
         <is>
-          <t>寒武纪</t>
+          <t>工业富联</t>
         </is>
       </c>
       <c r="F206" s="40" t="inlineStr">
         <is>
-          <t>688256.SH</t>
+          <t>601138.SH</t>
         </is>
       </c>
       <c r="G206" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H206" s="41" t="inlineStr">
         <is>
-          <t>AI推理/训练芯片</t>
+          <t>AI服务器代工/组装</t>
         </is>
       </c>
       <c r="I206" s="42" t="inlineStr">
@@ -13298,9 +13302,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J206" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J206" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K206" s="13" t="inlineStr"/>
@@ -13309,7 +13313,11 @@
       <c r="N206" s="13" t="inlineStr"/>
       <c r="O206" s="13" t="inlineStr"/>
       <c r="P206" s="13" t="inlineStr"/>
-      <c r="Q206" s="13" t="inlineStr"/>
+      <c r="Q206" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="R206" s="13" t="inlineStr"/>
       <c r="S206" s="13" t="inlineStr"/>
       <c r="T206" s="13" t="inlineStr"/>
@@ -13326,27 +13334,27 @@
       </c>
       <c r="D207" s="38" t="inlineStr">
         <is>
-          <t>GPU架构芯片，2024年登陆科创板</t>
+          <t>AI服务器整机</t>
         </is>
       </c>
       <c r="E207" s="39" t="inlineStr">
         <is>
-          <t>沐曦股份</t>
+          <t>浪潮信息</t>
         </is>
       </c>
       <c r="F207" s="40" t="inlineStr">
         <is>
-          <t>688802.SH</t>
+          <t>000977.SZ</t>
         </is>
       </c>
       <c r="G207" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H207" s="41" t="inlineStr">
         <is>
-          <t>GPU架构芯片</t>
+          <t>AI服务器整机</t>
         </is>
       </c>
       <c r="I207" s="42" t="inlineStr">
@@ -13354,9 +13362,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J207" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J207" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K207" s="13" t="inlineStr"/>
@@ -13374,7 +13382,7 @@
     </row>
     <row r="208" ht="16" customHeight="1">
       <c r="A208" s="15" t="n"/>
-      <c r="B208" s="16" t="n"/>
+      <c r="B208" s="15" t="n"/>
       <c r="C208" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13382,27 +13390,27 @@
       </c>
       <c r="D208" s="38" t="inlineStr">
         <is>
-          <t>GPU芯片，2024年登陆科创板</t>
+          <t>AI服务器/网络设备</t>
         </is>
       </c>
       <c r="E208" s="39" t="inlineStr">
         <is>
-          <t>摩尔线程</t>
+          <t>紫光股份</t>
         </is>
       </c>
       <c r="F208" s="40" t="inlineStr">
         <is>
-          <t>688795.SH</t>
+          <t>000938.SZ</t>
         </is>
       </c>
       <c r="G208" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H208" s="41" t="inlineStr">
         <is>
-          <t>GPU芯片</t>
+          <t>AI服务器/网络设备</t>
         </is>
       </c>
       <c r="I208" s="42" t="inlineStr">
@@ -13410,9 +13418,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J208" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J208" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K208" s="13" t="inlineStr"/>
@@ -13430,11 +13438,7 @@
     </row>
     <row r="209" ht="16" customHeight="1">
       <c r="A209" s="15" t="n"/>
-      <c r="B209" s="36" t="inlineStr">
-        <is>
-          <t>光纤光缆</t>
-        </is>
-      </c>
+      <c r="B209" s="15" t="n"/>
       <c r="C209" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13442,17 +13446,17 @@
       </c>
       <c r="D209" s="38" t="inlineStr">
         <is>
-          <t>AI数据中心高速互连光纤</t>
+          <t>AI服务器/超算</t>
         </is>
       </c>
       <c r="E209" s="39" t="inlineStr">
         <is>
-          <t>长飞光纤</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="F209" s="40" t="inlineStr">
         <is>
-          <t>601869.SH</t>
+          <t>603019.SH</t>
         </is>
       </c>
       <c r="G209" s="41" t="inlineStr">
@@ -13462,7 +13466,7 @@
       </c>
       <c r="H209" s="41" t="inlineStr">
         <is>
-          <t>光纤预制棒/光缆</t>
+          <t>AI服务器/超算</t>
         </is>
       </c>
       <c r="I209" s="42" t="inlineStr">
@@ -13470,9 +13474,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J209" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J209" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K209" s="13" t="inlineStr"/>
@@ -13490,7 +13494,7 @@
     </row>
     <row r="210" ht="16" customHeight="1">
       <c r="A210" s="15" t="n"/>
-      <c r="B210" s="15" t="n"/>
+      <c r="B210" s="16" t="n"/>
       <c r="C210" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13498,37 +13502,37 @@
       </c>
       <c r="D210" s="38" t="inlineStr">
         <is>
-          <t>光纤光缆/海缆</t>
+          <t>AI服务器/机柜，台湾云端服务器龙头</t>
         </is>
       </c>
       <c r="E210" s="39" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>纬颖科技 Wiwynn</t>
         </is>
       </c>
       <c r="F210" s="40" t="inlineStr">
         <is>
-          <t>600487.SH</t>
+          <t>6669.TW</t>
         </is>
       </c>
       <c r="G210" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>台湾证交所</t>
         </is>
       </c>
       <c r="H210" s="41" t="inlineStr">
         <is>
-          <t>光纤光缆/海缆</t>
+          <t>AI服务器/机柜</t>
         </is>
       </c>
       <c r="I210" s="42" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="J210" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+          <t>TWD</t>
+        </is>
+      </c>
+      <c r="J210" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K210" s="13" t="inlineStr"/>
@@ -13546,7 +13550,11 @@
     </row>
     <row r="211" ht="16" customHeight="1">
       <c r="A211" s="15" t="n"/>
-      <c r="B211" s="15" t="n"/>
+      <c r="B211" s="36" t="inlineStr">
+        <is>
+          <t>AI芯片</t>
+        </is>
+      </c>
       <c r="C211" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13554,27 +13562,27 @@
       </c>
       <c r="D211" s="38" t="inlineStr">
         <is>
-          <t>光纤光缆/海缆</t>
+          <t>国产GPU/DCU芯片，AI训练推理</t>
         </is>
       </c>
       <c r="E211" s="39" t="inlineStr">
         <is>
-          <t>中天科技</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="F211" s="40" t="inlineStr">
         <is>
-          <t>600522.SH</t>
+          <t>688041.SH</t>
         </is>
       </c>
       <c r="G211" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H211" s="41" t="inlineStr">
         <is>
-          <t>光纤光缆/海缆</t>
+          <t>GPU/DCU芯片</t>
         </is>
       </c>
       <c r="I211" s="42" t="inlineStr">
@@ -13582,9 +13590,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J211" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J211" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K211" s="13" t="inlineStr"/>
@@ -13602,7 +13610,7 @@
     </row>
     <row r="212" ht="16" customHeight="1">
       <c r="A212" s="15" t="n"/>
-      <c r="B212" s="16" t="n"/>
+      <c r="B212" s="15" t="n"/>
       <c r="C212" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13610,27 +13618,27 @@
       </c>
       <c r="D212" s="38" t="inlineStr">
         <is>
-          <t>光纤光缆/通信设备</t>
+          <t>AI推理/训练芯片</t>
         </is>
       </c>
       <c r="E212" s="39" t="inlineStr">
         <is>
-          <t>烽火通信</t>
+          <t>寒武纪</t>
         </is>
       </c>
       <c r="F212" s="40" t="inlineStr">
         <is>
-          <t>600498.SH</t>
+          <t>688256.SH</t>
         </is>
       </c>
       <c r="G212" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H212" s="41" t="inlineStr">
         <is>
-          <t>光纤光缆/通信设备</t>
+          <t>AI推理/训练芯片</t>
         </is>
       </c>
       <c r="I212" s="42" t="inlineStr">
@@ -13638,9 +13646,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J212" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J212" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K212" s="13" t="inlineStr"/>
@@ -13658,11 +13666,7 @@
     </row>
     <row r="213" ht="16" customHeight="1">
       <c r="A213" s="15" t="n"/>
-      <c r="B213" s="36" t="inlineStr">
-        <is>
-          <t>存储芯片</t>
-        </is>
-      </c>
+      <c r="B213" s="15" t="n"/>
       <c r="C213" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13670,27 +13674,27 @@
       </c>
       <c r="D213" s="38" t="inlineStr">
         <is>
-          <t>AI训练推理大规模存储，NAND存储模组</t>
+          <t>GPU架构芯片，2024年登陆科创板</t>
         </is>
       </c>
       <c r="E213" s="39" t="inlineStr">
         <is>
-          <t>德明利</t>
+          <t>沐曦股份</t>
         </is>
       </c>
       <c r="F213" s="40" t="inlineStr">
         <is>
-          <t>001323.SZ</t>
+          <t>688802.SH</t>
         </is>
       </c>
       <c r="G213" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H213" s="41" t="inlineStr">
         <is>
-          <t>NAND Flash存储模组</t>
+          <t>GPU架构芯片</t>
         </is>
       </c>
       <c r="I213" s="42" t="inlineStr">
@@ -13698,9 +13702,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J213" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J213" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K213" s="13" t="inlineStr"/>
@@ -13718,7 +13722,7 @@
     </row>
     <row r="214" ht="16" customHeight="1">
       <c r="A214" s="15" t="n"/>
-      <c r="B214" s="15" t="n"/>
+      <c r="B214" s="16" t="n"/>
       <c r="C214" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13726,27 +13730,27 @@
       </c>
       <c r="D214" s="38" t="inlineStr">
         <is>
-          <t>NOR Flash/MCU</t>
+          <t>GPU芯片，2024年登陆科创板</t>
         </is>
       </c>
       <c r="E214" s="39" t="inlineStr">
         <is>
-          <t>兆易创新</t>
+          <t>摩尔线程</t>
         </is>
       </c>
       <c r="F214" s="40" t="inlineStr">
         <is>
-          <t>603986.SH</t>
+          <t>688795.SH</t>
         </is>
       </c>
       <c r="G214" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H214" s="41" t="inlineStr">
         <is>
-          <t>NOR Flash/MCU</t>
+          <t>GPU芯片</t>
         </is>
       </c>
       <c r="I214" s="42" t="inlineStr">
@@ -13754,9 +13758,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J214" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J214" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K214" s="13" t="inlineStr"/>
@@ -13774,7 +13778,11 @@
     </row>
     <row r="215" ht="16" customHeight="1">
       <c r="A215" s="15" t="n"/>
-      <c r="B215" s="15" t="n"/>
+      <c r="B215" s="36" t="inlineStr">
+        <is>
+          <t>光纤光缆</t>
+        </is>
+      </c>
       <c r="C215" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13782,27 +13790,27 @@
       </c>
       <c r="D215" s="38" t="inlineStr">
         <is>
-          <t>NAND存储模组</t>
+          <t>AI数据中心高速互连光纤</t>
         </is>
       </c>
       <c r="E215" s="39" t="inlineStr">
         <is>
-          <t>佰维存储</t>
+          <t>长飞光纤</t>
         </is>
       </c>
       <c r="F215" s="40" t="inlineStr">
         <is>
-          <t>688525.SH</t>
+          <t>601869.SH</t>
         </is>
       </c>
       <c r="G215" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H215" s="41" t="inlineStr">
         <is>
-          <t>NAND存储模组</t>
+          <t>光纤预制棒/光缆</t>
         </is>
       </c>
       <c r="I215" s="42" t="inlineStr">
@@ -13810,9 +13818,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J215" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J215" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K215" s="13" t="inlineStr"/>
@@ -13838,27 +13846,27 @@
       </c>
       <c r="D216" s="38" t="inlineStr">
         <is>
-          <t>NAND/eMMC存储</t>
+          <t>光纤光缆/海缆</t>
         </is>
       </c>
       <c r="E216" s="39" t="inlineStr">
         <is>
-          <t>江波龙</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="F216" s="40" t="inlineStr">
         <is>
-          <t>301308.SZ</t>
+          <t>600487.SH</t>
         </is>
       </c>
       <c r="G216" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H216" s="41" t="inlineStr">
         <is>
-          <t>NAND/eMMC存储</t>
+          <t>光纤光缆/海缆</t>
         </is>
       </c>
       <c r="I216" s="42" t="inlineStr">
@@ -13866,9 +13874,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J216" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J216" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K216" s="13" t="inlineStr"/>
@@ -13894,37 +13902,37 @@
       </c>
       <c r="D217" s="38" t="inlineStr">
         <is>
-          <t>全球DRAM/NAND/HBM龙头，AI训练核心</t>
+          <t>光纤光缆/海缆</t>
         </is>
       </c>
       <c r="E217" s="39" t="inlineStr">
         <is>
-          <t>三星电子 Samsung</t>
+          <t>中天科技</t>
         </is>
       </c>
       <c r="F217" s="40" t="inlineStr">
         <is>
-          <t>005930.KS</t>
+          <t>600522.SH</t>
         </is>
       </c>
       <c r="G217" s="41" t="inlineStr">
         <is>
-          <t>韩国证交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H217" s="41" t="inlineStr">
         <is>
-          <t>DRAM/NAND/HBM</t>
+          <t>光纤光缆/海缆</t>
         </is>
       </c>
       <c r="I217" s="42" t="inlineStr">
         <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="J217" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J217" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K217" s="13" t="inlineStr"/>
@@ -13933,36 +13941,16 @@
       <c r="N217" s="13" t="inlineStr"/>
       <c r="O217" s="13" t="inlineStr"/>
       <c r="P217" s="13" t="inlineStr"/>
-      <c r="Q217" s="14" t="inlineStr">
-        <is>
-          <t>买入,362000</t>
-        </is>
-      </c>
-      <c r="R217" s="14" t="inlineStr">
-        <is>
-          <t>买入,260000</t>
-        </is>
-      </c>
-      <c r="S217" s="14" t="inlineStr">
-        <is>
-          <t>买入,350000</t>
-        </is>
-      </c>
-      <c r="T217" s="14" t="inlineStr">
-        <is>
-          <t>买入,266000</t>
-        </is>
-      </c>
+      <c r="Q217" s="13" t="inlineStr"/>
+      <c r="R217" s="13" t="inlineStr"/>
+      <c r="S217" s="13" t="inlineStr"/>
+      <c r="T217" s="13" t="inlineStr"/>
       <c r="U217" s="13" t="inlineStr"/>
-      <c r="V217" s="14" t="inlineStr">
-        <is>
-          <t>买入,362006</t>
-        </is>
-      </c>
+      <c r="V217" s="13" t="inlineStr"/>
     </row>
     <row r="218" ht="16" customHeight="1">
       <c r="A218" s="15" t="n"/>
-      <c r="B218" s="15" t="n"/>
+      <c r="B218" s="16" t="n"/>
       <c r="C218" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -13970,37 +13958,37 @@
       </c>
       <c r="D218" s="38" t="inlineStr">
         <is>
-          <t>HBM3/DRAM全球第二，AI算力关键</t>
+          <t>光纤光缆/通信设备</t>
         </is>
       </c>
       <c r="E218" s="39" t="inlineStr">
         <is>
-          <t>SK海力士 SK Hynix</t>
+          <t>烽火通信</t>
         </is>
       </c>
       <c r="F218" s="40" t="inlineStr">
         <is>
-          <t>000660.KS</t>
+          <t>600498.SH</t>
         </is>
       </c>
       <c r="G218" s="41" t="inlineStr">
         <is>
-          <t>韩国证交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H218" s="41" t="inlineStr">
         <is>
-          <t>HBM/DRAM/NAND</t>
+          <t>光纤光缆/通信设备</t>
         </is>
       </c>
       <c r="I218" s="42" t="inlineStr">
         <is>
-          <t>KRW</t>
-        </is>
-      </c>
-      <c r="J218" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J218" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K218" s="13" t="inlineStr"/>
@@ -14009,32 +13997,20 @@
       <c r="N218" s="13" t="inlineStr"/>
       <c r="O218" s="13" t="inlineStr"/>
       <c r="P218" s="13" t="inlineStr"/>
-      <c r="Q218" s="14" t="inlineStr">
-        <is>
-          <t>增持,2900000</t>
-        </is>
-      </c>
-      <c r="R218" s="14" t="inlineStr">
-        <is>
-          <t>强力买入,1350000</t>
-        </is>
-      </c>
-      <c r="S218" s="14" t="inlineStr">
-        <is>
-          <t>买入,1450000</t>
-        </is>
-      </c>
-      <c r="T218" s="14" t="inlineStr">
-        <is>
-          <t>买入,1500000</t>
-        </is>
-      </c>
+      <c r="Q218" s="13" t="inlineStr"/>
+      <c r="R218" s="13" t="inlineStr"/>
+      <c r="S218" s="13" t="inlineStr"/>
+      <c r="T218" s="13" t="inlineStr"/>
       <c r="U218" s="13" t="inlineStr"/>
       <c r="V218" s="13" t="inlineStr"/>
     </row>
     <row r="219" ht="16" customHeight="1">
       <c r="A219" s="15" t="n"/>
-      <c r="B219" s="15" t="n"/>
+      <c r="B219" s="36" t="inlineStr">
+        <is>
+          <t>存储芯片</t>
+        </is>
+      </c>
       <c r="C219" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14042,37 +14018,37 @@
       </c>
       <c r="D219" s="38" t="inlineStr">
         <is>
-          <t>DRAM/NAND存储，HBM3E量产</t>
+          <t>AI训练推理大规模存储，NAND存储模组</t>
         </is>
       </c>
       <c r="E219" s="39" t="inlineStr">
         <is>
-          <t>美光科技 Micron</t>
+          <t>德明利</t>
         </is>
       </c>
       <c r="F219" s="40" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>001323.SZ</t>
         </is>
       </c>
       <c r="G219" s="41" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H219" s="41" t="inlineStr">
         <is>
-          <t>DRAM/NAND/HBM</t>
+          <t>NAND Flash存储模组</t>
         </is>
       </c>
       <c r="I219" s="42" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J219" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J219" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K219" s="13" t="inlineStr"/>
@@ -14081,32 +14057,16 @@
       <c r="N219" s="13" t="inlineStr"/>
       <c r="O219" s="13" t="inlineStr"/>
       <c r="P219" s="13" t="inlineStr"/>
-      <c r="Q219" s="14" t="inlineStr">
-        <is>
-          <t>买入首选,450</t>
-        </is>
-      </c>
-      <c r="R219" s="14" t="inlineStr">
-        <is>
-          <t>中性,360</t>
-        </is>
-      </c>
+      <c r="Q219" s="13" t="inlineStr"/>
+      <c r="R219" s="13" t="inlineStr"/>
       <c r="S219" s="13" t="inlineStr"/>
-      <c r="T219" s="14" t="inlineStr">
-        <is>
-          <t>买入,535</t>
-        </is>
-      </c>
-      <c r="U219" s="14" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
+      <c r="T219" s="13" t="inlineStr"/>
+      <c r="U219" s="13" t="inlineStr"/>
       <c r="V219" s="13" t="inlineStr"/>
     </row>
     <row r="220" ht="16" customHeight="1">
       <c r="A220" s="15" t="n"/>
-      <c r="B220" s="16" t="n"/>
+      <c r="B220" s="15" t="n"/>
       <c r="C220" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14114,37 +14074,37 @@
       </c>
       <c r="D220" s="38" t="inlineStr">
         <is>
-          <t>AI存储接口/网络芯片，Marvell ASIC</t>
+          <t>NOR Flash/MCU</t>
         </is>
       </c>
       <c r="E220" s="39" t="inlineStr">
         <is>
-          <t>美满电子 Marvell</t>
+          <t>兆易创新</t>
         </is>
       </c>
       <c r="F220" s="40" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>603986.SH</t>
         </is>
       </c>
       <c r="G220" s="41" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H220" s="41" t="inlineStr">
         <is>
-          <t>AI网络/存储接口芯片</t>
+          <t>NOR Flash/MCU</t>
         </is>
       </c>
       <c r="I220" s="42" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J220" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J220" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K220" s="13" t="inlineStr"/>
@@ -14153,11 +14113,7 @@
       <c r="N220" s="13" t="inlineStr"/>
       <c r="O220" s="13" t="inlineStr"/>
       <c r="P220" s="13" t="inlineStr"/>
-      <c r="Q220" s="14" t="inlineStr">
-        <is>
-          <t>增持</t>
-        </is>
-      </c>
+      <c r="Q220" s="13" t="inlineStr"/>
       <c r="R220" s="13" t="inlineStr"/>
       <c r="S220" s="13" t="inlineStr"/>
       <c r="T220" s="13" t="inlineStr"/>
@@ -14166,11 +14122,7 @@
     </row>
     <row r="221" ht="16" customHeight="1">
       <c r="A221" s="15" t="n"/>
-      <c r="B221" s="36" t="inlineStr">
-        <is>
-          <t>高速链接 Interconnect</t>
-        </is>
-      </c>
+      <c r="B221" s="15" t="n"/>
       <c r="C221" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14178,27 +14130,27 @@
       </c>
       <c r="D221" s="38" t="inlineStr">
         <is>
-          <t>AI服务器高速铜缆/连接器</t>
+          <t>NAND存储模组</t>
         </is>
       </c>
       <c r="E221" s="39" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>佰维存储</t>
         </is>
       </c>
       <c r="F221" s="40" t="inlineStr">
         <is>
-          <t>002475.SZ</t>
+          <t>688525.SH</t>
         </is>
       </c>
       <c r="G221" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所科创板</t>
         </is>
       </c>
       <c r="H221" s="41" t="inlineStr">
         <is>
-          <t>高速连接器/线缆</t>
+          <t>NAND存储模组</t>
         </is>
       </c>
       <c r="I221" s="42" t="inlineStr">
@@ -14206,9 +14158,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J221" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J221" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K221" s="13" t="inlineStr"/>
@@ -14217,16 +14169,8 @@
       <c r="N221" s="13" t="inlineStr"/>
       <c r="O221" s="13" t="inlineStr"/>
       <c r="P221" s="13" t="inlineStr"/>
-      <c r="Q221" s="14" t="inlineStr">
-        <is>
-          <t>增持</t>
-        </is>
-      </c>
-      <c r="R221" s="14" t="inlineStr">
-        <is>
-          <t>买入</t>
-        </is>
-      </c>
+      <c r="Q221" s="13" t="inlineStr"/>
+      <c r="R221" s="13" t="inlineStr"/>
       <c r="S221" s="13" t="inlineStr"/>
       <c r="T221" s="13" t="inlineStr"/>
       <c r="U221" s="13" t="inlineStr"/>
@@ -14242,27 +14186,27 @@
       </c>
       <c r="D222" s="38" t="inlineStr">
         <is>
-          <t>高速铜缆/连接器</t>
+          <t>NAND/eMMC存储</t>
         </is>
       </c>
       <c r="E222" s="39" t="inlineStr">
         <is>
-          <t>兆龙互连</t>
+          <t>江波龙</t>
         </is>
       </c>
       <c r="F222" s="40" t="inlineStr">
         <is>
-          <t>603557.SH</t>
+          <t>301308.SZ</t>
         </is>
       </c>
       <c r="G222" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H222" s="41" t="inlineStr">
         <is>
-          <t>高速铜缆/连接器</t>
+          <t>NAND/eMMC存储</t>
         </is>
       </c>
       <c r="I222" s="42" t="inlineStr">
@@ -14270,9 +14214,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J222" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J222" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K222" s="13" t="inlineStr"/>
@@ -14298,37 +14242,37 @@
       </c>
       <c r="D223" s="38" t="inlineStr">
         <is>
-          <t>高速线缆/热缩材料</t>
+          <t>全球DRAM/NAND/HBM龙头，AI训练核心</t>
         </is>
       </c>
       <c r="E223" s="39" t="inlineStr">
         <is>
-          <t>沃尔核材</t>
+          <t>三星电子 Samsung</t>
         </is>
       </c>
       <c r="F223" s="40" t="inlineStr">
         <is>
-          <t>002130.SZ</t>
+          <t>005930.KS</t>
         </is>
       </c>
       <c r="G223" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>韩国证交所</t>
         </is>
       </c>
       <c r="H223" s="41" t="inlineStr">
         <is>
-          <t>高速线缆/热缩材料</t>
+          <t>DRAM/NAND/HBM</t>
         </is>
       </c>
       <c r="I223" s="42" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="J223" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="J223" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K223" s="13" t="inlineStr"/>
@@ -14337,16 +14281,36 @@
       <c r="N223" s="13" t="inlineStr"/>
       <c r="O223" s="13" t="inlineStr"/>
       <c r="P223" s="13" t="inlineStr"/>
-      <c r="Q223" s="13" t="inlineStr"/>
-      <c r="R223" s="13" t="inlineStr"/>
-      <c r="S223" s="13" t="inlineStr"/>
-      <c r="T223" s="13" t="inlineStr"/>
+      <c r="Q223" s="14" t="inlineStr">
+        <is>
+          <t>买入,362000</t>
+        </is>
+      </c>
+      <c r="R223" s="14" t="inlineStr">
+        <is>
+          <t>买入,260000</t>
+        </is>
+      </c>
+      <c r="S223" s="14" t="inlineStr">
+        <is>
+          <t>买入,350000</t>
+        </is>
+      </c>
+      <c r="T223" s="14" t="inlineStr">
+        <is>
+          <t>买入,266000</t>
+        </is>
+      </c>
       <c r="U223" s="13" t="inlineStr"/>
-      <c r="V223" s="13" t="inlineStr"/>
+      <c r="V223" s="14" t="inlineStr">
+        <is>
+          <t>买入,362006</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="16" customHeight="1">
       <c r="A224" s="15" t="n"/>
-      <c r="B224" s="16" t="n"/>
+      <c r="B224" s="15" t="n"/>
       <c r="C224" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14354,37 +14318,37 @@
       </c>
       <c r="D224" s="38" t="inlineStr">
         <is>
-          <t>高速连接器</t>
+          <t>HBM3/DRAM全球第二，AI算力关键</t>
         </is>
       </c>
       <c r="E224" s="39" t="inlineStr">
         <is>
-          <t>鼎通科技</t>
+          <t>SK海力士 SK Hynix</t>
         </is>
       </c>
       <c r="F224" s="40" t="inlineStr">
         <is>
-          <t>301291.SZ</t>
+          <t>000660.KS</t>
         </is>
       </c>
       <c r="G224" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>韩国证交所</t>
         </is>
       </c>
       <c r="H224" s="41" t="inlineStr">
         <is>
-          <t>高速连接器</t>
+          <t>HBM/DRAM/NAND</t>
         </is>
       </c>
       <c r="I224" s="42" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="J224" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="J224" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K224" s="13" t="inlineStr"/>
@@ -14393,20 +14357,32 @@
       <c r="N224" s="13" t="inlineStr"/>
       <c r="O224" s="13" t="inlineStr"/>
       <c r="P224" s="13" t="inlineStr"/>
-      <c r="Q224" s="13" t="inlineStr"/>
-      <c r="R224" s="13" t="inlineStr"/>
-      <c r="S224" s="13" t="inlineStr"/>
-      <c r="T224" s="13" t="inlineStr"/>
+      <c r="Q224" s="14" t="inlineStr">
+        <is>
+          <t>增持,2900000</t>
+        </is>
+      </c>
+      <c r="R224" s="14" t="inlineStr">
+        <is>
+          <t>强力买入,1350000</t>
+        </is>
+      </c>
+      <c r="S224" s="14" t="inlineStr">
+        <is>
+          <t>买入,1450000</t>
+        </is>
+      </c>
+      <c r="T224" s="14" t="inlineStr">
+        <is>
+          <t>买入,1500000</t>
+        </is>
+      </c>
       <c r="U224" s="13" t="inlineStr"/>
       <c r="V224" s="13" t="inlineStr"/>
     </row>
     <row r="225" ht="16" customHeight="1">
       <c r="A225" s="15" t="n"/>
-      <c r="B225" s="36" t="inlineStr">
-        <is>
-          <t>液冷 Liquid Cooling</t>
-        </is>
-      </c>
+      <c r="B225" s="15" t="n"/>
       <c r="C225" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14414,37 +14390,37 @@
       </c>
       <c r="D225" s="38" t="inlineStr">
         <is>
-          <t>AI数据中心液冷散热，H100/H200热耗密度极高</t>
+          <t>DRAM/NAND存储，HBM3E量产</t>
         </is>
       </c>
       <c r="E225" s="39" t="inlineStr">
         <is>
-          <t>英维克</t>
+          <t>美光科技 Micron</t>
         </is>
       </c>
       <c r="F225" s="40" t="inlineStr">
         <is>
-          <t>002837.SZ</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="G225" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="H225" s="41" t="inlineStr">
         <is>
-          <t>液冷/机房热管理</t>
+          <t>DRAM/NAND/HBM</t>
         </is>
       </c>
       <c r="I225" s="42" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="J225" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J225" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K225" s="13" t="inlineStr"/>
@@ -14453,16 +14429,32 @@
       <c r="N225" s="13" t="inlineStr"/>
       <c r="O225" s="13" t="inlineStr"/>
       <c r="P225" s="13" t="inlineStr"/>
-      <c r="Q225" s="13" t="inlineStr"/>
-      <c r="R225" s="13" t="inlineStr"/>
+      <c r="Q225" s="14" t="inlineStr">
+        <is>
+          <t>买入首选,450</t>
+        </is>
+      </c>
+      <c r="R225" s="14" t="inlineStr">
+        <is>
+          <t>中性,360</t>
+        </is>
+      </c>
       <c r="S225" s="13" t="inlineStr"/>
-      <c r="T225" s="13" t="inlineStr"/>
-      <c r="U225" s="13" t="inlineStr"/>
+      <c r="T225" s="14" t="inlineStr">
+        <is>
+          <t>买入,535</t>
+        </is>
+      </c>
+      <c r="U225" s="14" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
       <c r="V225" s="13" t="inlineStr"/>
     </row>
     <row r="226" ht="16" customHeight="1">
       <c r="A226" s="15" t="n"/>
-      <c r="B226" s="15" t="n"/>
+      <c r="B226" s="16" t="n"/>
       <c r="C226" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14470,37 +14462,37 @@
       </c>
       <c r="D226" s="38" t="inlineStr">
         <is>
-          <t>液冷系统</t>
+          <t>AI存储接口/网络芯片，Marvell ASIC</t>
         </is>
       </c>
       <c r="E226" s="39" t="inlineStr">
         <is>
-          <t>高澜股份</t>
+          <t>美满电子 Marvell</t>
         </is>
       </c>
       <c r="F226" s="40" t="inlineStr">
         <is>
-          <t>300499.SZ</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="G226" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>NASDAQ</t>
         </is>
       </c>
       <c r="H226" s="41" t="inlineStr">
         <is>
-          <t>液冷系统</t>
+          <t>AI网络/存储接口芯片</t>
         </is>
       </c>
       <c r="I226" s="42" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="J226" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J226" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="K226" s="13" t="inlineStr"/>
@@ -14509,7 +14501,11 @@
       <c r="N226" s="13" t="inlineStr"/>
       <c r="O226" s="13" t="inlineStr"/>
       <c r="P226" s="13" t="inlineStr"/>
-      <c r="Q226" s="13" t="inlineStr"/>
+      <c r="Q226" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="R226" s="13" t="inlineStr"/>
       <c r="S226" s="13" t="inlineStr"/>
       <c r="T226" s="13" t="inlineStr"/>
@@ -14518,7 +14514,11 @@
     </row>
     <row r="227" ht="16" customHeight="1">
       <c r="A227" s="15" t="n"/>
-      <c r="B227" s="16" t="n"/>
+      <c r="B227" s="36" t="inlineStr">
+        <is>
+          <t>高速链接 Interconnect</t>
+        </is>
+      </c>
       <c r="C227" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14526,27 +14526,27 @@
       </c>
       <c r="D227" s="38" t="inlineStr">
         <is>
-          <t>液冷AI服务器/超算</t>
+          <t>AI服务器高速铜缆/连接器</t>
         </is>
       </c>
       <c r="E227" s="39" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="F227" s="40" t="inlineStr">
         <is>
-          <t>603019.SH</t>
+          <t>002475.SZ</t>
         </is>
       </c>
       <c r="G227" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H227" s="41" t="inlineStr">
         <is>
-          <t>液冷AI服务器/超算</t>
+          <t>高速连接器/线缆</t>
         </is>
       </c>
       <c r="I227" s="42" t="inlineStr">
@@ -14554,9 +14554,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J227" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J227" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K227" s="13" t="inlineStr"/>
@@ -14565,8 +14565,16 @@
       <c r="N227" s="13" t="inlineStr"/>
       <c r="O227" s="13" t="inlineStr"/>
       <c r="P227" s="13" t="inlineStr"/>
-      <c r="Q227" s="13" t="inlineStr"/>
-      <c r="R227" s="13" t="inlineStr"/>
+      <c r="Q227" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
+      <c r="R227" s="14" t="inlineStr">
+        <is>
+          <t>买入</t>
+        </is>
+      </c>
       <c r="S227" s="13" t="inlineStr"/>
       <c r="T227" s="13" t="inlineStr"/>
       <c r="U227" s="13" t="inlineStr"/>
@@ -14574,11 +14582,7 @@
     </row>
     <row r="228" ht="16" customHeight="1">
       <c r="A228" s="15" t="n"/>
-      <c r="B228" s="36" t="inlineStr">
-        <is>
-          <t>电源 Power Supply</t>
-        </is>
-      </c>
+      <c r="B228" s="15" t="n"/>
       <c r="C228" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14586,27 +14590,27 @@
       </c>
       <c r="D228" s="38" t="inlineStr">
         <is>
-          <t>数据中心电源/UPS</t>
+          <t>高速铜缆/连接器</t>
         </is>
       </c>
       <c r="E228" s="39" t="inlineStr">
         <is>
-          <t>中恒电气</t>
+          <t>兆龙互连</t>
         </is>
       </c>
       <c r="F228" s="40" t="inlineStr">
         <is>
-          <t>002364.SZ</t>
+          <t>603557.SH</t>
         </is>
       </c>
       <c r="G228" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H228" s="41" t="inlineStr">
         <is>
-          <t>数据中心电源</t>
+          <t>高速铜缆/连接器</t>
         </is>
       </c>
       <c r="I228" s="42" t="inlineStr">
@@ -14614,9 +14618,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J228" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J228" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K228" s="13" t="inlineStr"/>
@@ -14642,17 +14646,17 @@
       </c>
       <c r="D229" s="38" t="inlineStr">
         <is>
-          <t>UPS/储能电源</t>
+          <t>高速线缆/热缩材料</t>
         </is>
       </c>
       <c r="E229" s="39" t="inlineStr">
         <is>
-          <t>圣阳股份</t>
+          <t>沃尔核材</t>
         </is>
       </c>
       <c r="F229" s="40" t="inlineStr">
         <is>
-          <t>002580.SZ</t>
+          <t>002130.SZ</t>
         </is>
       </c>
       <c r="G229" s="41" t="inlineStr">
@@ -14662,7 +14666,7 @@
       </c>
       <c r="H229" s="41" t="inlineStr">
         <is>
-          <t>UPS/储能电源</t>
+          <t>高速线缆/热缩材料</t>
         </is>
       </c>
       <c r="I229" s="42" t="inlineStr">
@@ -14670,9 +14674,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J229" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J229" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K229" s="13" t="inlineStr"/>
@@ -14690,7 +14694,7 @@
     </row>
     <row r="230" ht="16" customHeight="1">
       <c r="A230" s="15" t="n"/>
-      <c r="B230" s="15" t="n"/>
+      <c r="B230" s="16" t="n"/>
       <c r="C230" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14698,27 +14702,27 @@
       </c>
       <c r="D230" s="38" t="inlineStr">
         <is>
-          <t>服务器电源</t>
+          <t>高速连接器</t>
         </is>
       </c>
       <c r="E230" s="39" t="inlineStr">
         <is>
-          <t>欧陆通</t>
+          <t>鼎通科技</t>
         </is>
       </c>
       <c r="F230" s="40" t="inlineStr">
         <is>
-          <t>300870.SZ</t>
+          <t>301291.SZ</t>
         </is>
       </c>
       <c r="G230" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H230" s="41" t="inlineStr">
         <is>
-          <t>服务器电源</t>
+          <t>高速连接器</t>
         </is>
       </c>
       <c r="I230" s="42" t="inlineStr">
@@ -14726,9 +14730,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J230" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J230" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K230" s="13" t="inlineStr"/>
@@ -14737,24 +14741,20 @@
       <c r="N230" s="13" t="inlineStr"/>
       <c r="O230" s="13" t="inlineStr"/>
       <c r="P230" s="13" t="inlineStr"/>
-      <c r="Q230" s="14" t="inlineStr">
-        <is>
-          <t>增持</t>
-        </is>
-      </c>
+      <c r="Q230" s="13" t="inlineStr"/>
       <c r="R230" s="13" t="inlineStr"/>
-      <c r="S230" s="14" t="inlineStr">
-        <is>
-          <t>增持</t>
-        </is>
-      </c>
+      <c r="S230" s="13" t="inlineStr"/>
       <c r="T230" s="13" t="inlineStr"/>
       <c r="U230" s="13" t="inlineStr"/>
       <c r="V230" s="13" t="inlineStr"/>
     </row>
     <row r="231" ht="16" customHeight="1">
       <c r="A231" s="15" t="n"/>
-      <c r="B231" s="16" t="n"/>
+      <c r="B231" s="36" t="inlineStr">
+        <is>
+          <t>液冷 Liquid Cooling</t>
+        </is>
+      </c>
       <c r="C231" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14762,17 +14762,17 @@
       </c>
       <c r="D231" s="38" t="inlineStr">
         <is>
-          <t>工业电源/服务器电源</t>
+          <t>AI数据中心液冷散热，H100/H200热耗密度极高</t>
         </is>
       </c>
       <c r="E231" s="39" t="inlineStr">
         <is>
-          <t>麦格米特</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="F231" s="40" t="inlineStr">
         <is>
-          <t>002851.SZ</t>
+          <t>002837.SZ</t>
         </is>
       </c>
       <c r="G231" s="41" t="inlineStr">
@@ -14782,7 +14782,7 @@
       </c>
       <c r="H231" s="41" t="inlineStr">
         <is>
-          <t>工业电源/服务器电源</t>
+          <t>液冷/机房热管理</t>
         </is>
       </c>
       <c r="I231" s="42" t="inlineStr">
@@ -14790,9 +14790,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J231" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J231" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K231" s="13" t="inlineStr"/>
@@ -14810,11 +14810,7 @@
     </row>
     <row r="232" ht="16" customHeight="1">
       <c r="A232" s="15" t="n"/>
-      <c r="B232" s="36" t="inlineStr">
-        <is>
-          <t>AIDC 数据中心</t>
-        </is>
-      </c>
+      <c r="B232" s="15" t="n"/>
       <c r="C232" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14822,27 +14818,27 @@
       </c>
       <c r="D232" s="38" t="inlineStr">
         <is>
-          <t>AI数据中心建设运营</t>
+          <t>液冷系统</t>
         </is>
       </c>
       <c r="E232" s="39" t="inlineStr">
         <is>
-          <t>润泽科技</t>
+          <t>高澜股份</t>
         </is>
       </c>
       <c r="F232" s="40" t="inlineStr">
         <is>
-          <t>300442.SZ</t>
+          <t>300499.SZ</t>
         </is>
       </c>
       <c r="G232" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H232" s="41" t="inlineStr">
         <is>
-          <t>AIDC建设运营</t>
+          <t>液冷系统</t>
         </is>
       </c>
       <c r="I232" s="42" t="inlineStr">
@@ -14850,9 +14846,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J232" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J232" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K232" s="13" t="inlineStr"/>
@@ -14870,7 +14866,7 @@
     </row>
     <row r="233" ht="16" customHeight="1">
       <c r="A233" s="15" t="n"/>
-      <c r="B233" s="15" t="n"/>
+      <c r="B233" s="16" t="n"/>
       <c r="C233" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14878,27 +14874,27 @@
       </c>
       <c r="D233" s="38" t="inlineStr">
         <is>
-          <t>CDN/AIDC</t>
+          <t>液冷AI服务器/超算</t>
         </is>
       </c>
       <c r="E233" s="39" t="inlineStr">
         <is>
-          <t>网宿科技</t>
+          <t>中科曙光</t>
         </is>
       </c>
       <c r="F233" s="40" t="inlineStr">
         <is>
-          <t>300017.SZ</t>
+          <t>603019.SH</t>
         </is>
       </c>
       <c r="G233" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H233" s="41" t="inlineStr">
         <is>
-          <t>CDN/AIDC</t>
+          <t>液冷AI服务器/超算</t>
         </is>
       </c>
       <c r="I233" s="42" t="inlineStr">
@@ -14906,9 +14902,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J233" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J233" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K233" s="13" t="inlineStr"/>
@@ -14926,7 +14922,11 @@
     </row>
     <row r="234" ht="16" customHeight="1">
       <c r="A234" s="15" t="n"/>
-      <c r="B234" s="15" t="n"/>
+      <c r="B234" s="36" t="inlineStr">
+        <is>
+          <t>电源 Power Supply</t>
+        </is>
+      </c>
       <c r="C234" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14934,27 +14934,27 @@
       </c>
       <c r="D234" s="38" t="inlineStr">
         <is>
-          <t>IDC/AIDC</t>
+          <t>数据中心电源/UPS</t>
         </is>
       </c>
       <c r="E234" s="39" t="inlineStr">
         <is>
-          <t>光环新网</t>
+          <t>中恒电气</t>
         </is>
       </c>
       <c r="F234" s="40" t="inlineStr">
         <is>
-          <t>300383.SZ</t>
+          <t>002364.SZ</t>
         </is>
       </c>
       <c r="G234" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H234" s="41" t="inlineStr">
         <is>
-          <t>IDC/AIDC</t>
+          <t>数据中心电源</t>
         </is>
       </c>
       <c r="I234" s="42" t="inlineStr">
@@ -14962,9 +14962,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J234" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J234" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K234" s="13" t="inlineStr"/>
@@ -14982,7 +14982,7 @@
     </row>
     <row r="235" ht="16" customHeight="1">
       <c r="A235" s="15" t="n"/>
-      <c r="B235" s="16" t="n"/>
+      <c r="B235" s="15" t="n"/>
       <c r="C235" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -14990,27 +14990,27 @@
       </c>
       <c r="D235" s="38" t="inlineStr">
         <is>
-          <t>IDC/AIDC建设运营</t>
+          <t>UPS/储能电源</t>
         </is>
       </c>
       <c r="E235" s="39" t="inlineStr">
         <is>
-          <t>数据港</t>
+          <t>圣阳股份</t>
         </is>
       </c>
       <c r="F235" s="40" t="inlineStr">
         <is>
-          <t>603881.SH</t>
+          <t>002580.SZ</t>
         </is>
       </c>
       <c r="G235" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H235" s="41" t="inlineStr">
         <is>
-          <t>IDC/AIDC建设运营</t>
+          <t>UPS/储能电源</t>
         </is>
       </c>
       <c r="I235" s="42" t="inlineStr">
@@ -15018,9 +15018,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J235" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J235" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K235" s="13" t="inlineStr"/>
@@ -15038,12 +15038,7 @@
     </row>
     <row r="236" ht="16" customHeight="1">
       <c r="A236" s="15" t="n"/>
-      <c r="B236" s="36" t="inlineStr">
-        <is>
-          <t>数据中心配电
-固态变压器</t>
-        </is>
-      </c>
+      <c r="B236" s="15" t="n"/>
       <c r="C236" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -15051,27 +15046,27 @@
       </c>
       <c r="D236" s="38" t="inlineStr">
         <is>
-          <t>数字化固态变压器，SiC功率器件核心应用，AIDC配电关键</t>
+          <t>服务器电源</t>
         </is>
       </c>
       <c r="E236" s="39" t="inlineStr">
         <is>
-          <t>四方股份</t>
+          <t>欧陆通</t>
         </is>
       </c>
       <c r="F236" s="40" t="inlineStr">
         <is>
-          <t>601126.SH</t>
+          <t>300870.SZ</t>
         </is>
       </c>
       <c r="G236" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H236" s="41" t="inlineStr">
         <is>
-          <t>固态变压器/继电保护</t>
+          <t>服务器电源</t>
         </is>
       </c>
       <c r="I236" s="42" t="inlineStr">
@@ -15079,9 +15074,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J236" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J236" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K236" s="13" t="inlineStr"/>
@@ -15090,16 +15085,24 @@
       <c r="N236" s="13" t="inlineStr"/>
       <c r="O236" s="13" t="inlineStr"/>
       <c r="P236" s="13" t="inlineStr"/>
-      <c r="Q236" s="13" t="inlineStr"/>
+      <c r="Q236" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="R236" s="13" t="inlineStr"/>
-      <c r="S236" s="13" t="inlineStr"/>
+      <c r="S236" s="14" t="inlineStr">
+        <is>
+          <t>增持</t>
+        </is>
+      </c>
       <c r="T236" s="13" t="inlineStr"/>
       <c r="U236" s="13" t="inlineStr"/>
       <c r="V236" s="13" t="inlineStr"/>
     </row>
     <row r="237" ht="16" customHeight="1">
       <c r="A237" s="15" t="n"/>
-      <c r="B237" s="15" t="n"/>
+      <c r="B237" s="16" t="n"/>
       <c r="C237" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -15107,27 +15110,27 @@
       </c>
       <c r="D237" s="38" t="inlineStr">
         <is>
-          <t>高压开关设备/固态变压器</t>
+          <t>工业电源/服务器电源</t>
         </is>
       </c>
       <c r="E237" s="39" t="inlineStr">
         <is>
-          <t>中国西电</t>
+          <t>麦格米特</t>
         </is>
       </c>
       <c r="F237" s="40" t="inlineStr">
         <is>
-          <t>601179.SH</t>
+          <t>002851.SZ</t>
         </is>
       </c>
       <c r="G237" s="41" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H237" s="41" t="inlineStr">
         <is>
-          <t>高压开关/固态变压器</t>
+          <t>工业电源/服务器电源</t>
         </is>
       </c>
       <c r="I237" s="42" t="inlineStr">
@@ -15135,9 +15138,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J237" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J237" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K237" s="13" t="inlineStr"/>
@@ -15155,7 +15158,11 @@
     </row>
     <row r="238" ht="16" customHeight="1">
       <c r="A238" s="15" t="n"/>
-      <c r="B238" s="15" t="n"/>
+      <c r="B238" s="36" t="inlineStr">
+        <is>
+          <t>AIDC 数据中心</t>
+        </is>
+      </c>
       <c r="C238" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -15163,17 +15170,17 @@
       </c>
       <c r="D238" s="38" t="inlineStr">
         <is>
-          <t>电源变压器/固态变压器/磁性元件</t>
+          <t>AI数据中心建设运营</t>
         </is>
       </c>
       <c r="E238" s="39" t="inlineStr">
         <is>
-          <t>伊戈尔</t>
+          <t>润泽科技</t>
         </is>
       </c>
       <c r="F238" s="40" t="inlineStr">
         <is>
-          <t>002922.SZ</t>
+          <t>300442.SZ</t>
         </is>
       </c>
       <c r="G238" s="41" t="inlineStr">
@@ -15183,7 +15190,7 @@
       </c>
       <c r="H238" s="41" t="inlineStr">
         <is>
-          <t>变压器/电源模块</t>
+          <t>AIDC建设运营</t>
         </is>
       </c>
       <c r="I238" s="42" t="inlineStr">
@@ -15191,9 +15198,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J238" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J238" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K238" s="13" t="inlineStr"/>
@@ -15211,7 +15218,7 @@
     </row>
     <row r="239" ht="16" customHeight="1">
       <c r="A239" s="15" t="n"/>
-      <c r="B239" s="16" t="n"/>
+      <c r="B239" s="15" t="n"/>
       <c r="C239" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -15219,27 +15226,27 @@
       </c>
       <c r="D239" s="38" t="inlineStr">
         <is>
-          <t>干式变压器/固态变压器，AIDC配电</t>
+          <t>CDN/AIDC</t>
         </is>
       </c>
       <c r="E239" s="39" t="inlineStr">
         <is>
-          <t>金盘科技</t>
+          <t>网宿科技</t>
         </is>
       </c>
       <c r="F239" s="40" t="inlineStr">
         <is>
-          <t>688676.SH</t>
+          <t>300017.SZ</t>
         </is>
       </c>
       <c r="G239" s="41" t="inlineStr">
         <is>
-          <t>上交所科创板</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H239" s="41" t="inlineStr">
         <is>
-          <t>干式/固态变压器</t>
+          <t>CDN/AIDC</t>
         </is>
       </c>
       <c r="I239" s="42" t="inlineStr">
@@ -15247,9 +15254,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J239" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J239" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K239" s="13" t="inlineStr"/>
@@ -15267,11 +15274,7 @@
     </row>
     <row r="240" ht="16" customHeight="1">
       <c r="A240" s="15" t="n"/>
-      <c r="B240" s="36" t="inlineStr">
-        <is>
-          <t>算电协同</t>
-        </is>
-      </c>
+      <c r="B240" s="15" t="n"/>
       <c r="C240" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -15279,27 +15282,27 @@
       </c>
       <c r="D240" s="38" t="inlineStr">
         <is>
-          <t>算力+电力协同，绿电支撑AI数据中心</t>
+          <t>IDC/AIDC</t>
         </is>
       </c>
       <c r="E240" s="39" t="inlineStr">
         <is>
-          <t>豫能控股</t>
+          <t>光环新网</t>
         </is>
       </c>
       <c r="F240" s="40" t="inlineStr">
         <is>
-          <t>001896.SZ</t>
+          <t>300383.SZ</t>
         </is>
       </c>
       <c r="G240" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>深交所创业板</t>
         </is>
       </c>
       <c r="H240" s="41" t="inlineStr">
         <is>
-          <t>电力/算力协同</t>
+          <t>IDC/AIDC</t>
         </is>
       </c>
       <c r="I240" s="42" t="inlineStr">
@@ -15307,9 +15310,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J240" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J240" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K240" s="13" t="inlineStr"/>
@@ -15327,7 +15330,7 @@
     </row>
     <row r="241" ht="16" customHeight="1">
       <c r="A241" s="15" t="n"/>
-      <c r="B241" s="15" t="n"/>
+      <c r="B241" s="16" t="n"/>
       <c r="C241" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -15335,27 +15338,27 @@
       </c>
       <c r="D241" s="38" t="inlineStr">
         <is>
-          <t>绿电/算力协同</t>
+          <t>IDC/AIDC建设运营</t>
         </is>
       </c>
       <c r="E241" s="39" t="inlineStr">
         <is>
-          <t>协鑫能科</t>
+          <t>数据港</t>
         </is>
       </c>
       <c r="F241" s="40" t="inlineStr">
         <is>
-          <t>002015.SZ</t>
+          <t>603881.SH</t>
         </is>
       </c>
       <c r="G241" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H241" s="41" t="inlineStr">
         <is>
-          <t>绿电/算力协同</t>
+          <t>IDC/AIDC建设运营</t>
         </is>
       </c>
       <c r="I241" s="42" t="inlineStr">
@@ -15363,9 +15366,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J241" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J241" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K241" s="13" t="inlineStr"/>
@@ -15383,7 +15386,12 @@
     </row>
     <row r="242" ht="16" customHeight="1">
       <c r="A242" s="15" t="n"/>
-      <c r="B242" s="16" t="n"/>
+      <c r="B242" s="36" t="inlineStr">
+        <is>
+          <t>数据中心配电
+固态变压器</t>
+        </is>
+      </c>
       <c r="C242" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -15391,27 +15399,27 @@
       </c>
       <c r="D242" s="38" t="inlineStr">
         <is>
-          <t>绿电/数字能源</t>
+          <t>数字化固态变压器，SiC功率器件核心应用，AIDC配电关键</t>
         </is>
       </c>
       <c r="E242" s="39" t="inlineStr">
         <is>
-          <t>韶能股份</t>
+          <t>四方股份</t>
         </is>
       </c>
       <c r="F242" s="40" t="inlineStr">
         <is>
-          <t>000601.SZ</t>
+          <t>601126.SH</t>
         </is>
       </c>
       <c r="G242" s="41" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="H242" s="41" t="inlineStr">
         <is>
-          <t>绿电/数字能源</t>
+          <t>固态变压器/继电保护</t>
         </is>
       </c>
       <c r="I242" s="42" t="inlineStr">
@@ -15419,9 +15427,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J242" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J242" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K242" s="13" t="inlineStr"/>
@@ -15439,11 +15447,7 @@
     </row>
     <row r="243" ht="16" customHeight="1">
       <c r="A243" s="15" t="n"/>
-      <c r="B243" s="36" t="inlineStr">
-        <is>
-          <t>算力租赁</t>
-        </is>
-      </c>
+      <c r="B243" s="15" t="n"/>
       <c r="C243" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -15451,17 +15455,17 @@
       </c>
       <c r="D243" s="38" t="inlineStr">
         <is>
-          <t>GPU云算力租赁</t>
+          <t>高压开关设备/固态变压器</t>
         </is>
       </c>
       <c r="E243" s="39" t="inlineStr">
         <is>
-          <t>利通电子</t>
+          <t>中国西电</t>
         </is>
       </c>
       <c r="F243" s="40" t="inlineStr">
         <is>
-          <t>603629.SH</t>
+          <t>601179.SH</t>
         </is>
       </c>
       <c r="G243" s="41" t="inlineStr">
@@ -15471,7 +15475,7 @@
       </c>
       <c r="H243" s="41" t="inlineStr">
         <is>
-          <t>算力租赁/GPU云</t>
+          <t>高压开关/固态变压器</t>
         </is>
       </c>
       <c r="I243" s="42" t="inlineStr">
@@ -15479,9 +15483,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J243" s="12" t="inlineStr">
-        <is>
-          <t>Top1</t>
+      <c r="J243" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K243" s="13" t="inlineStr"/>
@@ -15507,27 +15511,27 @@
       </c>
       <c r="D244" s="38" t="inlineStr">
         <is>
-          <t>算力/数据中心租赁</t>
+          <t>电源变压器/固态变压器/磁性元件</t>
         </is>
       </c>
       <c r="E244" s="39" t="inlineStr">
         <is>
-          <t>协创数据</t>
+          <t>伊戈尔</t>
         </is>
       </c>
       <c r="F244" s="40" t="inlineStr">
         <is>
-          <t>300857.SZ</t>
+          <t>002922.SZ</t>
         </is>
       </c>
       <c r="G244" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H244" s="41" t="inlineStr">
         <is>
-          <t>算力/数据中心租赁</t>
+          <t>变压器/电源模块</t>
         </is>
       </c>
       <c r="I244" s="42" t="inlineStr">
@@ -15535,9 +15539,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J244" s="32" t="inlineStr">
-        <is>
-          <t>Top2</t>
+      <c r="J244" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
         </is>
       </c>
       <c r="K244" s="13" t="inlineStr"/>
@@ -15555,7 +15559,7 @@
     </row>
     <row r="245" ht="16" customHeight="1">
       <c r="A245" s="15" t="n"/>
-      <c r="B245" s="15" t="n"/>
+      <c r="B245" s="16" t="n"/>
       <c r="C245" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -15563,17 +15567,17 @@
       </c>
       <c r="D245" s="38" t="inlineStr">
         <is>
-          <t>算力云/GPU租赁</t>
+          <t>干式变压器/固态变压器，AIDC配电</t>
         </is>
       </c>
       <c r="E245" s="39" t="inlineStr">
         <is>
-          <t>优刻得</t>
+          <t>金盘科技</t>
         </is>
       </c>
       <c r="F245" s="40" t="inlineStr">
         <is>
-          <t>688158.SH</t>
+          <t>688676.SH</t>
         </is>
       </c>
       <c r="G245" s="41" t="inlineStr">
@@ -15583,7 +15587,7 @@
       </c>
       <c r="H245" s="41" t="inlineStr">
         <is>
-          <t>算力云/GPU租赁</t>
+          <t>干式/固态变压器</t>
         </is>
       </c>
       <c r="I245" s="42" t="inlineStr">
@@ -15591,9 +15595,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J245" s="4" t="inlineStr">
-        <is>
-          <t>Top3</t>
+      <c r="J245" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
         </is>
       </c>
       <c r="K245" s="13" t="inlineStr"/>
@@ -15611,7 +15615,11 @@
     </row>
     <row r="246" ht="16" customHeight="1">
       <c r="A246" s="15" t="n"/>
-      <c r="B246" s="15" t="n"/>
+      <c r="B246" s="36" t="inlineStr">
+        <is>
+          <t>算电协同</t>
+        </is>
+      </c>
       <c r="C246" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -15619,27 +15627,27 @@
       </c>
       <c r="D246" s="38" t="inlineStr">
         <is>
-          <t>算力租赁/AI云服务</t>
+          <t>算力+电力协同，绿电支撑AI数据中心</t>
         </is>
       </c>
       <c r="E246" s="39" t="inlineStr">
         <is>
-          <t>宏景科技</t>
+          <t>豫能控股</t>
         </is>
       </c>
       <c r="F246" s="40" t="inlineStr">
         <is>
-          <t>301396.SZ</t>
+          <t>001896.SZ</t>
         </is>
       </c>
       <c r="G246" s="41" t="inlineStr">
         <is>
-          <t>深交所创业板</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H246" s="41" t="inlineStr">
         <is>
-          <t>算力租赁/AI云服务</t>
+          <t>电力/算力协同</t>
         </is>
       </c>
       <c r="I246" s="42" t="inlineStr">
@@ -15647,9 +15655,9 @@
           <t>CNY</t>
         </is>
       </c>
-      <c r="J246" s="43" t="inlineStr">
-        <is>
-          <t>Top4</t>
+      <c r="J246" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
         </is>
       </c>
       <c r="K246" s="13" t="inlineStr"/>
@@ -15666,8 +15674,8 @@
       <c r="V246" s="13" t="inlineStr"/>
     </row>
     <row r="247" ht="16" customHeight="1">
-      <c r="A247" s="16" t="n"/>
-      <c r="B247" s="16" t="n"/>
+      <c r="A247" s="15" t="n"/>
+      <c r="B247" s="15" t="n"/>
       <c r="C247" s="37" t="inlineStr">
         <is>
           <t>AI算力</t>
@@ -15675,37 +15683,37 @@
       </c>
       <c r="D247" s="38" t="inlineStr">
         <is>
-          <t>GPU云算力租赁，欧洲最大AI基础设施云平台，从Yandex拆分上市</t>
+          <t>绿电/算力协同</t>
         </is>
       </c>
       <c r="E247" s="39" t="inlineStr">
         <is>
-          <t>Nebius Group</t>
+          <t>协鑫能科</t>
         </is>
       </c>
       <c r="F247" s="40" t="inlineStr">
         <is>
-          <t>NBIS</t>
+          <t>002015.SZ</t>
         </is>
       </c>
       <c r="G247" s="41" t="inlineStr">
         <is>
-          <t>NASDAQ</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="H247" s="41" t="inlineStr">
         <is>
-          <t>GPU云/AI基础设施租赁</t>
+          <t>绿电/算力协同</t>
         </is>
       </c>
       <c r="I247" s="42" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="J247" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J247" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
         </is>
       </c>
       <c r="K247" s="13" t="inlineStr"/>
@@ -15721,37 +15729,379 @@
       <c r="U247" s="13" t="inlineStr"/>
       <c r="V247" s="13" t="inlineStr"/>
     </row>
+    <row r="248" ht="16" customHeight="1">
+      <c r="A248" s="15" t="n"/>
+      <c r="B248" s="16" t="n"/>
+      <c r="C248" s="37" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="D248" s="38" t="inlineStr">
+        <is>
+          <t>绿电/数字能源</t>
+        </is>
+      </c>
+      <c r="E248" s="39" t="inlineStr">
+        <is>
+          <t>韶能股份</t>
+        </is>
+      </c>
+      <c r="F248" s="40" t="inlineStr">
+        <is>
+          <t>000601.SZ</t>
+        </is>
+      </c>
+      <c r="G248" s="41" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="H248" s="41" t="inlineStr">
+        <is>
+          <t>绿电/数字能源</t>
+        </is>
+      </c>
+      <c r="I248" s="42" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J248" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
+        </is>
+      </c>
+      <c r="K248" s="13" t="inlineStr"/>
+      <c r="L248" s="13" t="inlineStr"/>
+      <c r="M248" s="13" t="inlineStr"/>
+      <c r="N248" s="13" t="inlineStr"/>
+      <c r="O248" s="13" t="inlineStr"/>
+      <c r="P248" s="13" t="inlineStr"/>
+      <c r="Q248" s="13" t="inlineStr"/>
+      <c r="R248" s="13" t="inlineStr"/>
+      <c r="S248" s="13" t="inlineStr"/>
+      <c r="T248" s="13" t="inlineStr"/>
+      <c r="U248" s="13" t="inlineStr"/>
+      <c r="V248" s="13" t="inlineStr"/>
+    </row>
+    <row r="249" ht="16" customHeight="1">
+      <c r="A249" s="15" t="n"/>
+      <c r="B249" s="36" t="inlineStr">
+        <is>
+          <t>算力租赁</t>
+        </is>
+      </c>
+      <c r="C249" s="37" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="D249" s="38" t="inlineStr">
+        <is>
+          <t>GPU云算力租赁</t>
+        </is>
+      </c>
+      <c r="E249" s="39" t="inlineStr">
+        <is>
+          <t>利通电子</t>
+        </is>
+      </c>
+      <c r="F249" s="40" t="inlineStr">
+        <is>
+          <t>603629.SH</t>
+        </is>
+      </c>
+      <c r="G249" s="41" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="H249" s="41" t="inlineStr">
+        <is>
+          <t>算力租赁/GPU云</t>
+        </is>
+      </c>
+      <c r="I249" s="42" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J249" s="12" t="inlineStr">
+        <is>
+          <t>Top1</t>
+        </is>
+      </c>
+      <c r="K249" s="13" t="inlineStr"/>
+      <c r="L249" s="13" t="inlineStr"/>
+      <c r="M249" s="13" t="inlineStr"/>
+      <c r="N249" s="13" t="inlineStr"/>
+      <c r="O249" s="13" t="inlineStr"/>
+      <c r="P249" s="13" t="inlineStr"/>
+      <c r="Q249" s="13" t="inlineStr"/>
+      <c r="R249" s="13" t="inlineStr"/>
+      <c r="S249" s="13" t="inlineStr"/>
+      <c r="T249" s="13" t="inlineStr"/>
+      <c r="U249" s="13" t="inlineStr"/>
+      <c r="V249" s="13" t="inlineStr"/>
+    </row>
+    <row r="250" ht="16" customHeight="1">
+      <c r="A250" s="15" t="n"/>
+      <c r="B250" s="15" t="n"/>
+      <c r="C250" s="37" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="D250" s="38" t="inlineStr">
+        <is>
+          <t>算力/数据中心租赁</t>
+        </is>
+      </c>
+      <c r="E250" s="39" t="inlineStr">
+        <is>
+          <t>协创数据</t>
+        </is>
+      </c>
+      <c r="F250" s="40" t="inlineStr">
+        <is>
+          <t>300857.SZ</t>
+        </is>
+      </c>
+      <c r="G250" s="41" t="inlineStr">
+        <is>
+          <t>深交所创业板</t>
+        </is>
+      </c>
+      <c r="H250" s="41" t="inlineStr">
+        <is>
+          <t>算力/数据中心租赁</t>
+        </is>
+      </c>
+      <c r="I250" s="42" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J250" s="32" t="inlineStr">
+        <is>
+          <t>Top2</t>
+        </is>
+      </c>
+      <c r="K250" s="13" t="inlineStr"/>
+      <c r="L250" s="13" t="inlineStr"/>
+      <c r="M250" s="13" t="inlineStr"/>
+      <c r="N250" s="13" t="inlineStr"/>
+      <c r="O250" s="13" t="inlineStr"/>
+      <c r="P250" s="13" t="inlineStr"/>
+      <c r="Q250" s="13" t="inlineStr"/>
+      <c r="R250" s="13" t="inlineStr"/>
+      <c r="S250" s="13" t="inlineStr"/>
+      <c r="T250" s="13" t="inlineStr"/>
+      <c r="U250" s="13" t="inlineStr"/>
+      <c r="V250" s="13" t="inlineStr"/>
+    </row>
+    <row r="251" ht="16" customHeight="1">
+      <c r="A251" s="15" t="n"/>
+      <c r="B251" s="15" t="n"/>
+      <c r="C251" s="37" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="D251" s="38" t="inlineStr">
+        <is>
+          <t>算力云/GPU租赁</t>
+        </is>
+      </c>
+      <c r="E251" s="39" t="inlineStr">
+        <is>
+          <t>优刻得</t>
+        </is>
+      </c>
+      <c r="F251" s="40" t="inlineStr">
+        <is>
+          <t>688158.SH</t>
+        </is>
+      </c>
+      <c r="G251" s="41" t="inlineStr">
+        <is>
+          <t>上交所科创板</t>
+        </is>
+      </c>
+      <c r="H251" s="41" t="inlineStr">
+        <is>
+          <t>算力云/GPU租赁</t>
+        </is>
+      </c>
+      <c r="I251" s="42" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J251" s="4" t="inlineStr">
+        <is>
+          <t>Top3</t>
+        </is>
+      </c>
+      <c r="K251" s="13" t="inlineStr"/>
+      <c r="L251" s="13" t="inlineStr"/>
+      <c r="M251" s="13" t="inlineStr"/>
+      <c r="N251" s="13" t="inlineStr"/>
+      <c r="O251" s="13" t="inlineStr"/>
+      <c r="P251" s="13" t="inlineStr"/>
+      <c r="Q251" s="13" t="inlineStr"/>
+      <c r="R251" s="13" t="inlineStr"/>
+      <c r="S251" s="13" t="inlineStr"/>
+      <c r="T251" s="13" t="inlineStr"/>
+      <c r="U251" s="13" t="inlineStr"/>
+      <c r="V251" s="13" t="inlineStr"/>
+    </row>
+    <row r="252" ht="16" customHeight="1">
+      <c r="A252" s="15" t="n"/>
+      <c r="B252" s="15" t="n"/>
+      <c r="C252" s="37" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="D252" s="38" t="inlineStr">
+        <is>
+          <t>算力租赁/AI云服务</t>
+        </is>
+      </c>
+      <c r="E252" s="39" t="inlineStr">
+        <is>
+          <t>宏景科技</t>
+        </is>
+      </c>
+      <c r="F252" s="40" t="inlineStr">
+        <is>
+          <t>301396.SZ</t>
+        </is>
+      </c>
+      <c r="G252" s="41" t="inlineStr">
+        <is>
+          <t>深交所创业板</t>
+        </is>
+      </c>
+      <c r="H252" s="41" t="inlineStr">
+        <is>
+          <t>算力租赁/AI云服务</t>
+        </is>
+      </c>
+      <c r="I252" s="42" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="J252" s="43" t="inlineStr">
+        <is>
+          <t>Top4</t>
+        </is>
+      </c>
+      <c r="K252" s="13" t="inlineStr"/>
+      <c r="L252" s="13" t="inlineStr"/>
+      <c r="M252" s="13" t="inlineStr"/>
+      <c r="N252" s="13" t="inlineStr"/>
+      <c r="O252" s="13" t="inlineStr"/>
+      <c r="P252" s="13" t="inlineStr"/>
+      <c r="Q252" s="13" t="inlineStr"/>
+      <c r="R252" s="13" t="inlineStr"/>
+      <c r="S252" s="13" t="inlineStr"/>
+      <c r="T252" s="13" t="inlineStr"/>
+      <c r="U252" s="13" t="inlineStr"/>
+      <c r="V252" s="13" t="inlineStr"/>
+    </row>
+    <row r="253" ht="16" customHeight="1">
+      <c r="A253" s="16" t="n"/>
+      <c r="B253" s="16" t="n"/>
+      <c r="C253" s="37" t="inlineStr">
+        <is>
+          <t>AI算力</t>
+        </is>
+      </c>
+      <c r="D253" s="38" t="inlineStr">
+        <is>
+          <t>GPU云算力租赁，欧洲最大AI基础设施云平台，从Yandex拆分上市</t>
+        </is>
+      </c>
+      <c r="E253" s="39" t="inlineStr">
+        <is>
+          <t>Nebius Group</t>
+        </is>
+      </c>
+      <c r="F253" s="40" t="inlineStr">
+        <is>
+          <t>NBIS</t>
+        </is>
+      </c>
+      <c r="G253" s="41" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="H253" s="41" t="inlineStr">
+        <is>
+          <t>GPU云/AI基础设施租赁</t>
+        </is>
+      </c>
+      <c r="I253" s="42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J253" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K253" s="13" t="inlineStr"/>
+      <c r="L253" s="13" t="inlineStr"/>
+      <c r="M253" s="13" t="inlineStr"/>
+      <c r="N253" s="13" t="inlineStr"/>
+      <c r="O253" s="13" t="inlineStr"/>
+      <c r="P253" s="13" t="inlineStr"/>
+      <c r="Q253" s="13" t="inlineStr"/>
+      <c r="R253" s="13" t="inlineStr"/>
+      <c r="S253" s="13" t="inlineStr"/>
+      <c r="T253" s="13" t="inlineStr"/>
+      <c r="U253" s="13" t="inlineStr"/>
+      <c r="V253" s="13" t="inlineStr"/>
+    </row>
   </sheetData>
   <autoFilter ref="A3:V3"/>
-  <mergeCells count="71">
+  <mergeCells count="73">
     <mergeCell ref="A2:V2"/>
+    <mergeCell ref="B215:B218"/>
     <mergeCell ref="B78:B82"/>
-    <mergeCell ref="B236:B239"/>
+    <mergeCell ref="B184:B187"/>
+    <mergeCell ref="B227:B230"/>
+    <mergeCell ref="B238:B241"/>
     <mergeCell ref="B30:B32"/>
-    <mergeCell ref="B213:B220"/>
-    <mergeCell ref="B170:B171"/>
     <mergeCell ref="B59:B62"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="B108:B110"/>
     <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B190:B195"/>
+    <mergeCell ref="B246:B248"/>
     <mergeCell ref="A27:A68"/>
     <mergeCell ref="B89:B91"/>
     <mergeCell ref="B129:B131"/>
+    <mergeCell ref="B242:B245"/>
     <mergeCell ref="B36:B38"/>
-    <mergeCell ref="A116:A177"/>
-    <mergeCell ref="B157:B165"/>
-    <mergeCell ref="B232:B235"/>
+    <mergeCell ref="B161:B162"/>
+    <mergeCell ref="B176:B177"/>
     <mergeCell ref="B132:B133"/>
     <mergeCell ref="B139:B141"/>
-    <mergeCell ref="B228:B231"/>
-    <mergeCell ref="A178:A247"/>
-    <mergeCell ref="B182:B185"/>
-    <mergeCell ref="B151:B156"/>
-    <mergeCell ref="B200:B204"/>
+    <mergeCell ref="B151:B152"/>
+    <mergeCell ref="B234:B237"/>
+    <mergeCell ref="B249:B253"/>
+    <mergeCell ref="B172:B175"/>
+    <mergeCell ref="B206:B210"/>
     <mergeCell ref="B119:B122"/>
+    <mergeCell ref="B154:B160"/>
+    <mergeCell ref="B219:B226"/>
     <mergeCell ref="B75:B77"/>
-    <mergeCell ref="B166:B169"/>
     <mergeCell ref="B40:B43"/>
     <mergeCell ref="B83:B84"/>
     <mergeCell ref="B127:B128"/>
@@ -15761,40 +16111,40 @@
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="B96:B98"/>
     <mergeCell ref="B69:B74"/>
-    <mergeCell ref="B178:B181"/>
-    <mergeCell ref="B196:B199"/>
-    <mergeCell ref="B205:B208"/>
+    <mergeCell ref="B211:B214"/>
+    <mergeCell ref="B178:B183"/>
+    <mergeCell ref="B196:B201"/>
+    <mergeCell ref="A116:A183"/>
     <mergeCell ref="B99:B100"/>
     <mergeCell ref="B134:B138"/>
     <mergeCell ref="B45:B53"/>
-    <mergeCell ref="B172:B177"/>
-    <mergeCell ref="B186:B189"/>
     <mergeCell ref="B15:B20"/>
     <mergeCell ref="B123:B124"/>
     <mergeCell ref="B92:B93"/>
     <mergeCell ref="B27:B29"/>
     <mergeCell ref="B145:B147"/>
     <mergeCell ref="B101:B103"/>
+    <mergeCell ref="A184:A253"/>
     <mergeCell ref="B111:B115"/>
     <mergeCell ref="B116:B118"/>
+    <mergeCell ref="B163:B171"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="A4:A20"/>
     <mergeCell ref="B148:B150"/>
     <mergeCell ref="A69:A95"/>
     <mergeCell ref="B55:B58"/>
-    <mergeCell ref="B240:B242"/>
+    <mergeCell ref="B188:B191"/>
+    <mergeCell ref="B192:B195"/>
     <mergeCell ref="B94:B95"/>
     <mergeCell ref="B104:B107"/>
     <mergeCell ref="B25:B26"/>
     <mergeCell ref="B9:B11"/>
-    <mergeCell ref="B225:B227"/>
-    <mergeCell ref="B209:B212"/>
+    <mergeCell ref="B231:B233"/>
     <mergeCell ref="B125:B126"/>
     <mergeCell ref="B85:B88"/>
-    <mergeCell ref="B243:B247"/>
     <mergeCell ref="B21:B22"/>
     <mergeCell ref="B63:B68"/>
-    <mergeCell ref="B221:B224"/>
+    <mergeCell ref="B202:B205"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
